--- a/Info/input/pr_model.xlsx
+++ b/Info/input/pr_model.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\10265696\Documents\AI Transformation\Skill\create-pr-cd\Info\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83EF60F5-2571-48B0-85A0-7BF9B233D1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF570C1-379E-4329-8CA7-F92FFFA580D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{089DC7BF-D48F-4FC9-B123-3E33291912E1}"/>
+    <workbookView xWindow="22932" yWindow="2592" windowWidth="23256" windowHeight="13896" xr2:uid="{089DC7BF-D48F-4FC9-B123-3E33291912E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="TX Line Item (After 20-Apr 26)" sheetId="1" r:id="rId1"/>
+    <sheet name="TX Line Item (After 21-Apr 26)" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
@@ -108,7 +108,6 @@
     <externalReference r:id="rId91"/>
     <externalReference r:id="rId92"/>
     <externalReference r:id="rId93"/>
-    <externalReference r:id="rId94"/>
   </externalReferences>
   <definedNames>
     <definedName name="\A">#REF!</definedName>
@@ -127,7 +126,7 @@
     <definedName name="\X">#REF!</definedName>
     <definedName name="\Y">#REF!</definedName>
     <definedName name="\Z">#REF!</definedName>
-    <definedName name="____a65554">'[2]2-Summary of Changes'!#REF!</definedName>
+    <definedName name="____a65554">'[1]2-Summary of Changes'!#REF!</definedName>
     <definedName name="____a65555">#REF!</definedName>
     <definedName name="____a65600">#REF!</definedName>
     <definedName name="____a65700">#REF!</definedName>
@@ -146,7 +145,7 @@
     <definedName name="____fac6">#REF!</definedName>
     <definedName name="____fac9">#REF!</definedName>
     <definedName name="___a65550">#REF!</definedName>
-    <definedName name="___a65554">'[2]2-Summary of Changes'!#REF!</definedName>
+    <definedName name="___a65554">'[1]2-Summary of Changes'!#REF!</definedName>
     <definedName name="___a65555">#REF!</definedName>
     <definedName name="___a65600">#REF!</definedName>
     <definedName name="___a65700">#REF!</definedName>
@@ -164,10 +163,10 @@
     <definedName name="___fac3">#REF!</definedName>
     <definedName name="___fac6">#REF!</definedName>
     <definedName name="___fac9">#REF!</definedName>
-    <definedName name="__123Graph_B" hidden="1">'[3]F&amp;F'!#REF!</definedName>
-    <definedName name="__123Graph_BCURRENT" hidden="1">'[3]F&amp;F'!#REF!</definedName>
+    <definedName name="__123Graph_B" hidden="1">'[2]F&amp;F'!#REF!</definedName>
+    <definedName name="__123Graph_BCURRENT" hidden="1">'[2]F&amp;F'!#REF!</definedName>
     <definedName name="__a65550">#REF!</definedName>
-    <definedName name="__a65554">'[2]2-Summary of Changes'!#REF!</definedName>
+    <definedName name="__a65554">'[1]2-Summary of Changes'!#REF!</definedName>
     <definedName name="__a65555">#REF!</definedName>
     <definedName name="__a65600">#REF!</definedName>
     <definedName name="__a65700">#REF!</definedName>
@@ -189,26 +188,26 @@
     <definedName name="__fac3">#REF!</definedName>
     <definedName name="__fac6">#REF!</definedName>
     <definedName name="__fac9">#REF!</definedName>
-    <definedName name="__No1">'[4]Bass Curve Calibration'!$B$8</definedName>
-    <definedName name="__p1">'[4]Bass Curve Calibration'!$B$5</definedName>
-    <definedName name="__q1">'[4]Bass Curve Calibration'!$B$6</definedName>
-    <definedName name="__RU1">[5]Optimised!#REF!</definedName>
-    <definedName name="__RU2">[5]Optimised!#REF!</definedName>
-    <definedName name="__RU3">[5]Optimised!#REF!</definedName>
-    <definedName name="__RU4">[5]Optimised!#REF!</definedName>
-    <definedName name="__SM1">[5]Optimised!#REF!</definedName>
-    <definedName name="__SM2">[5]Optimised!#REF!</definedName>
-    <definedName name="__SM3">[5]Optimised!#REF!</definedName>
-    <definedName name="__SM4">[5]Optimised!#REF!</definedName>
-    <definedName name="__to1">'[4]Bass Curve Calibration'!$B$7</definedName>
-    <definedName name="__URB1">[5]Optimised!#REF!</definedName>
-    <definedName name="__URB2">[5]Optimised!#REF!</definedName>
-    <definedName name="__URB3">[5]Optimised!#REF!</definedName>
-    <definedName name="__URB4">[5]Optimised!#REF!</definedName>
-    <definedName name="__YR1">[6]data!$C$2</definedName>
-    <definedName name="__YR2">[6]data!$C$3</definedName>
-    <definedName name="__YR3">[6]data!$C$4</definedName>
-    <definedName name="__YR4">[6]data!$C$5</definedName>
+    <definedName name="__No1">'[3]Bass Curve Calibration'!$B$8</definedName>
+    <definedName name="__p1">'[3]Bass Curve Calibration'!$B$5</definedName>
+    <definedName name="__q1">'[3]Bass Curve Calibration'!$B$6</definedName>
+    <definedName name="__RU1">[4]Optimised!#REF!</definedName>
+    <definedName name="__RU2">[4]Optimised!#REF!</definedName>
+    <definedName name="__RU3">[4]Optimised!#REF!</definedName>
+    <definedName name="__RU4">[4]Optimised!#REF!</definedName>
+    <definedName name="__SM1">[4]Optimised!#REF!</definedName>
+    <definedName name="__SM2">[4]Optimised!#REF!</definedName>
+    <definedName name="__SM3">[4]Optimised!#REF!</definedName>
+    <definedName name="__SM4">[4]Optimised!#REF!</definedName>
+    <definedName name="__to1">'[3]Bass Curve Calibration'!$B$7</definedName>
+    <definedName name="__URB1">[4]Optimised!#REF!</definedName>
+    <definedName name="__URB2">[4]Optimised!#REF!</definedName>
+    <definedName name="__URB3">[4]Optimised!#REF!</definedName>
+    <definedName name="__URB4">[4]Optimised!#REF!</definedName>
+    <definedName name="__YR1">[5]data!$C$2</definedName>
+    <definedName name="__YR2">[5]data!$C$3</definedName>
+    <definedName name="__YR3">[5]data!$C$4</definedName>
+    <definedName name="__YR4">[5]data!$C$5</definedName>
     <definedName name="_1">#REF!</definedName>
     <definedName name="_1_______123Graph_Bｸﾞﾗﾌ_7" hidden="1">#REF!</definedName>
     <definedName name="_10_____123Graph_Aｸﾞﾗﾌ_7" hidden="1">#REF!</definedName>
@@ -252,13 +251,13 @@
     <definedName name="_843">#REF!</definedName>
     <definedName name="_9______123Graph_Fｸﾞﾗﾌ_7" hidden="1">#REF!</definedName>
     <definedName name="_a65550">#REF!</definedName>
-    <definedName name="_a65554">'[2]2-Summary of Changes'!#REF!</definedName>
+    <definedName name="_a65554">'[1]2-Summary of Changes'!#REF!</definedName>
     <definedName name="_a65555">#REF!</definedName>
     <definedName name="_a65600">#REF!</definedName>
     <definedName name="_a65700">#REF!</definedName>
     <definedName name="_a65800">#REF!</definedName>
     <definedName name="_a66000">#REF!</definedName>
-    <definedName name="_a6785253">'[2]2-Summary of Changes'!#REF!</definedName>
+    <definedName name="_a6785253">'[1]2-Summary of Changes'!#REF!</definedName>
     <definedName name="_bsc240">#REF!</definedName>
     <definedName name="_bsc600">#REF!</definedName>
     <definedName name="_CIN1">#REF!</definedName>
@@ -276,42 +275,42 @@
     <definedName name="_fac6">#REF!</definedName>
     <definedName name="_fac9">#REF!</definedName>
     <definedName name="_Fill" hidden="1">#REF!</definedName>
-    <definedName name="_Key1" hidden="1">'[3]F&amp;F'!#REF!</definedName>
-    <definedName name="_Key2" hidden="1">'[3]F&amp;F'!#REF!</definedName>
+    <definedName name="_Key1" hidden="1">'[2]F&amp;F'!#REF!</definedName>
+    <definedName name="_Key2" hidden="1">'[2]F&amp;F'!#REF!</definedName>
     <definedName name="_L">#REF!</definedName>
     <definedName name="_MD5500">#REF!</definedName>
-    <definedName name="_No1">'[4]Bass Curve Calibration'!$B$8</definedName>
+    <definedName name="_No1">'[3]Bass Curve Calibration'!$B$8</definedName>
     <definedName name="_Order1" hidden="1">0</definedName>
     <definedName name="_Order2" hidden="1">255</definedName>
-    <definedName name="_p1">'[4]Bass Curve Calibration'!$B$5</definedName>
-    <definedName name="_q1">'[4]Bass Curve Calibration'!$B$6</definedName>
-    <definedName name="_RU1">[5]Optimised!#REF!</definedName>
-    <definedName name="_RU2">[5]Optimised!#REF!</definedName>
-    <definedName name="_RU3">[5]Optimised!#REF!</definedName>
-    <definedName name="_RU4">[5]Optimised!#REF!</definedName>
-    <definedName name="_SM1">[5]Optimised!#REF!</definedName>
-    <definedName name="_SM2">[5]Optimised!#REF!</definedName>
-    <definedName name="_SM3">[5]Optimised!#REF!</definedName>
-    <definedName name="_SM4">[5]Optimised!#REF!</definedName>
-    <definedName name="_Sort" hidden="1">'[3]F&amp;F'!#REF!</definedName>
-    <definedName name="_to1">'[4]Bass Curve Calibration'!$B$7</definedName>
+    <definedName name="_p1">'[3]Bass Curve Calibration'!$B$5</definedName>
+    <definedName name="_q1">'[3]Bass Curve Calibration'!$B$6</definedName>
+    <definedName name="_RU1">[4]Optimised!#REF!</definedName>
+    <definedName name="_RU2">[4]Optimised!#REF!</definedName>
+    <definedName name="_RU3">[4]Optimised!#REF!</definedName>
+    <definedName name="_RU4">[4]Optimised!#REF!</definedName>
+    <definedName name="_SM1">[4]Optimised!#REF!</definedName>
+    <definedName name="_SM2">[4]Optimised!#REF!</definedName>
+    <definedName name="_SM3">[4]Optimised!#REF!</definedName>
+    <definedName name="_SM4">[4]Optimised!#REF!</definedName>
+    <definedName name="_Sort" hidden="1">'[2]F&amp;F'!#REF!</definedName>
+    <definedName name="_to1">'[3]Bass Curve Calibration'!$B$7</definedName>
     <definedName name="_TRACKING_EUROROADS">#REF!</definedName>
-    <definedName name="_URB1">[5]Optimised!#REF!</definedName>
-    <definedName name="_URB2">[5]Optimised!#REF!</definedName>
-    <definedName name="_URB3">[5]Optimised!#REF!</definedName>
-    <definedName name="_URB4">[5]Optimised!#REF!</definedName>
-    <definedName name="_YR1">[6]data!$C$2</definedName>
-    <definedName name="_YR2">[6]data!$C$3</definedName>
-    <definedName name="_YR3">[6]data!$C$4</definedName>
-    <definedName name="_YR4">[6]data!$C$5</definedName>
-    <definedName name="a">[7]Inputs!$C$6</definedName>
+    <definedName name="_URB1">[4]Optimised!#REF!</definedName>
+    <definedName name="_URB2">[4]Optimised!#REF!</definedName>
+    <definedName name="_URB3">[4]Optimised!#REF!</definedName>
+    <definedName name="_URB4">[4]Optimised!#REF!</definedName>
+    <definedName name="_YR1">[5]data!$C$2</definedName>
+    <definedName name="_YR2">[5]data!$C$3</definedName>
+    <definedName name="_YR3">[5]data!$C$4</definedName>
+    <definedName name="_YR4">[5]data!$C$5</definedName>
+    <definedName name="a">[6]Inputs!$C$6</definedName>
     <definedName name="A_i">#REF!</definedName>
     <definedName name="aaaa" localSheetId="0" hidden="1">{"'Edit'!$A$1:$V$2277"}</definedName>
     <definedName name="aaaa" hidden="1">{"'Edit'!$A$1:$V$2277"}</definedName>
     <definedName name="AAAAAA">#REF!</definedName>
     <definedName name="AAAAAAAA">#REF!</definedName>
     <definedName name="AAAAAAAAAAAA">#REF!</definedName>
-    <definedName name="AAAAAAAAAAAAAAAAAA">'[2]2-Summary of Changes'!#REF!</definedName>
+    <definedName name="AAAAAAAAAAAAAAAAAA">'[1]2-Summary of Changes'!#REF!</definedName>
     <definedName name="AAAAAAAAAAAAAAAAAAAAA">#REF!</definedName>
     <definedName name="AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA">#REF!</definedName>
     <definedName name="abc" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"Sensitivity"}</definedName>
@@ -319,44 +318,44 @@
     <definedName name="Accelar_100">#REF!</definedName>
     <definedName name="Accelar_1000">#REF!</definedName>
     <definedName name="access">#REF!</definedName>
-    <definedName name="Access_Export_ECommerce">'[8]SAP-Referenz'!$A$1:$A$65536,'[8]SAP-Referenz'!$AP$1:$AX$65536</definedName>
+    <definedName name="Access_Export_ECommerce">'[7]SAP-Referenz'!$A$1:$A$65536,'[7]SAP-Referenz'!$AP$1:$AX$65536</definedName>
     <definedName name="ACCESS_STACK_NODE__ASN__SYSTEMS">#REF!</definedName>
     <definedName name="AccessDatabase" hidden="1">"C:\My Documents\current\Business case moc v2.0 .mdb"</definedName>
     <definedName name="actdetail">#REF!</definedName>
     <definedName name="Activation">#REF!</definedName>
-    <definedName name="Actual_MOU_ratio">[9]Assumptions!#REF!</definedName>
+    <definedName name="Actual_MOU_ratio">[8]Assumptions!#REF!</definedName>
     <definedName name="Add_Coef">#REF!</definedName>
     <definedName name="AgentName">#REF!</definedName>
-    <definedName name="Aggregation">[6]aggregation!$B$5:$E$107</definedName>
+    <definedName name="Aggregation">[5]aggregation!$B$5:$E$107</definedName>
     <definedName name="Alarm_box">#REF!</definedName>
     <definedName name="ALocalCoef">#REF!</definedName>
-    <definedName name="anabozo">[10]M_Cfg!$L$23</definedName>
-    <definedName name="Area">[11]国家维表!$A$2:$A$9</definedName>
+    <definedName name="anabozo">[9]M_Cfg!$L$23</definedName>
+    <definedName name="Area">[10]国家维表!$A$2:$A$9</definedName>
     <definedName name="AREATL">#REF!</definedName>
     <definedName name="AREAUSD">#REF!</definedName>
-    <definedName name="Armazenagem">'[12]Input Table'!#REF!</definedName>
+    <definedName name="Armazenagem">'[11]Input Table'!#REF!</definedName>
     <definedName name="asd">#REF!</definedName>
     <definedName name="asdfa" localSheetId="0" hidden="1">{"'Edit'!$A$1:$V$2277"}</definedName>
     <definedName name="asdfa" hidden="1">{"'Edit'!$A$1:$V$2277"}</definedName>
     <definedName name="ASellCoef">#REF!</definedName>
-    <definedName name="AUD">[6]graphs!$Y$6</definedName>
-    <definedName name="Ausblenden">[13]Faktoren!$A$15</definedName>
+    <definedName name="AUD">[5]graphs!$Y$6</definedName>
+    <definedName name="Ausblenden">[12]Faktoren!$A$15</definedName>
     <definedName name="Avg_Sub">#REF!</definedName>
     <definedName name="AvionLoc">#REF!</definedName>
     <definedName name="B">#REF!</definedName>
     <definedName name="BACKBONE_LINK_NODE__BLN__and_BACKBONE_CONCENTRATOR_NODE__BCN__SYSTEMS">#REF!</definedName>
-    <definedName name="Balance">[14]BS!#REF!</definedName>
+    <definedName name="Balance">[13]BS!#REF!</definedName>
     <definedName name="band">#REF!</definedName>
     <definedName name="band4">#REF!</definedName>
     <definedName name="band5">#REF!</definedName>
     <definedName name="band6">#REF!</definedName>
-    <definedName name="BASBSS">[15]MAIPLH!$H$57:$I$57,[15]MAIPLH!$O$57,[15]MAIPLH!$T$57,[15]MAIPLH!$I$60,[15]MAIPLH!$L$60</definedName>
-    <definedName name="BASBSSLEGU">[16]MAILEGUH!$H$57:$I$57,[16]MAILEGUH!$O$57,[16]MAILEGUH!$T$57,[16]MAILEGUH!$I$60,[16]MAILEGUH!$L$60</definedName>
+    <definedName name="BASBSS">[14]MAIPLH!$H$57:$I$57,[14]MAIPLH!$O$57,[14]MAIPLH!$T$57,[14]MAIPLH!$I$60,[14]MAIPLH!$L$60</definedName>
+    <definedName name="BASBSSLEGU">[15]MAILEGUH!$H$57:$I$57,[15]MAILEGUH!$O$57,[15]MAILEGUH!$T$57,[15]MAILEGUH!$I$60,[15]MAILEGUH!$L$60</definedName>
     <definedName name="base">#REF!</definedName>
-    <definedName name="BaseCase">[17]Scenarios!$C$164</definedName>
+    <definedName name="BaseCase">[16]Scenarios!$C$164</definedName>
     <definedName name="Basis_KPJ">#REF!</definedName>
-    <definedName name="BASNSS">[15]MAIPLH!$H$58:$I$58,[15]MAIPLH!$O$58,[15]MAIPLH!$T$58,[15]MAIPLH!$Q$60:$R$60,[15]MAIPLH!$U$60</definedName>
-    <definedName name="BASNSSLEGU">[16]MAILEGUH!$H$58:$I$58,[16]MAILEGUH!$O$58,[16]MAILEGUH!$T$58,[16]MAILEGUH!$Q$60:$R$60,[16]MAILEGUH!$U$60</definedName>
+    <definedName name="BASNSS">[14]MAIPLH!$H$58:$I$58,[14]MAIPLH!$O$58,[14]MAIPLH!$T$58,[14]MAIPLH!$Q$60:$R$60,[14]MAIPLH!$U$60</definedName>
+    <definedName name="BASNSSLEGU">[15]MAILEGUH!$H$58:$I$58,[15]MAILEGUH!$O$58,[15]MAILEGUH!$T$58,[15]MAILEGUH!$Q$60:$R$60,[15]MAILEGUH!$U$60</definedName>
     <definedName name="batt">#REF!</definedName>
     <definedName name="Battery">#REF!</definedName>
     <definedName name="BAYSTACK_ACCESS_NODE__AN__and_ACCESS_NODE_HUB__ANH__SYSTEMS">#REF!</definedName>
@@ -369,11 +368,11 @@
     <definedName name="bbu32p">#REF!</definedName>
     <definedName name="bbu64c">#REF!</definedName>
     <definedName name="bbu64p">#REF!</definedName>
-    <definedName name="bc">'[18]Total GSM  Market'!#REF!</definedName>
+    <definedName name="bc">'[17]Total GSM  Market'!#REF!</definedName>
     <definedName name="BDCA">#REF!</definedName>
     <definedName name="bdsf">#REF!</definedName>
     <definedName name="beg">#REF!</definedName>
-    <definedName name="begin_of_summary">[19]Summary!$A$8</definedName>
+    <definedName name="begin_of_summary">[18]Summary!$A$8</definedName>
     <definedName name="bidon" localSheetId="0" hidden="1">{"COST",#N/A,FALSE,"SYNTHESE";"MARGIN",#N/A,FALSE,"SYNTHESE";"LOT_COM",#N/A,FALSE,"SYNTHESE"}</definedName>
     <definedName name="bidon" hidden="1">{"COST",#N/A,FALSE,"SYNTHESE";"MARGIN",#N/A,FALSE,"SYNTHESE";"LOT_COM",#N/A,FALSE,"SYNTHESE"}</definedName>
     <definedName name="BLG_factors">#REF!</definedName>
@@ -395,25 +394,25 @@
     <definedName name="book">#REF!</definedName>
     <definedName name="boq_left">#REF!</definedName>
     <definedName name="boq_right">#REF!</definedName>
-    <definedName name="BRGE100">[16]FIXDATA!$C$12</definedName>
+    <definedName name="BRGE100">[15]FIXDATA!$C$12</definedName>
     <definedName name="bsctrc">#REF!</definedName>
-    <definedName name="BSGE100">[16]FIXDATA!$C$10</definedName>
+    <definedName name="BSGE100">[15]FIXDATA!$C$10</definedName>
     <definedName name="BSHEETALL">#REF!</definedName>
     <definedName name="bss">#REF!</definedName>
-    <definedName name="BTS_limit_per_OMC">'[20]Equip Dim'!$C$242</definedName>
-    <definedName name="Budget_Items">'[21]CAPEX Actual Form'!#REF!</definedName>
-    <definedName name="build_bal">'[3]F&amp;F'!#REF!</definedName>
-    <definedName name="Business_Manager">'[22]Network assumptions'!$D$3</definedName>
-    <definedName name="Buyer">[23]Buyers!$A$1:$A$15</definedName>
+    <definedName name="BTS_limit_per_OMC">'[19]Equip Dim'!$C$242</definedName>
+    <definedName name="Budget_Items">'[20]CAPEX Actual Form'!#REF!</definedName>
+    <definedName name="build_bal">'[2]F&amp;F'!#REF!</definedName>
+    <definedName name="Business_Manager">'[21]Network assumptions'!$D$3</definedName>
+    <definedName name="Buyer">[22]Buyers!$A$1:$A$15</definedName>
     <definedName name="C_">#REF!</definedName>
-    <definedName name="c_frais">[24]coef!$B$4</definedName>
+    <definedName name="c_frais">[23]coef!$B$4</definedName>
     <definedName name="Cable">#REF!</definedName>
-    <definedName name="Cambio">'[25]parametri di programmazione'!$B$2</definedName>
-    <definedName name="CaplVers">[26]M_Cfg!$L$23</definedName>
+    <definedName name="Cambio">'[24]parametri di programmazione'!$B$2</definedName>
+    <definedName name="CaplVers">[25]M_Cfg!$L$23</definedName>
     <definedName name="CASHFLOWALL">#REF!</definedName>
-    <definedName name="CashIn">[27]Companycode!$Q$7:$Q$19</definedName>
-    <definedName name="CashOut">[28]Companycode!$R$7:$R$14</definedName>
-    <definedName name="category_Level_1">'[29]category data'!$B$2:$K$2</definedName>
+    <definedName name="CashIn">[26]Companycode!$Q$7:$Q$19</definedName>
+    <definedName name="CashOut">[27]Companycode!$R$7:$R$14</definedName>
+    <definedName name="category_Level_1">'[28]category data'!$B$2:$K$2</definedName>
     <definedName name="CBIL1">#REF!</definedName>
     <definedName name="CBIL2">#REF!</definedName>
     <definedName name="ccc">#REF!</definedName>
@@ -430,7 +429,7 @@
     <definedName name="CCPANSSSEL2">#REF!</definedName>
     <definedName name="CCPANSSSEL3">#REF!</definedName>
     <definedName name="CCPANSSSEL4">#REF!</definedName>
-    <definedName name="CDMAlink_Version">[30]Planner!#REF!</definedName>
+    <definedName name="CDMAlink_Version">[29]Planner!#REF!</definedName>
     <definedName name="CECHO1">#REF!</definedName>
     <definedName name="CECHO2">#REF!</definedName>
     <definedName name="CEIR1">#REF!</definedName>
@@ -443,35 +442,35 @@
     <definedName name="CHLR2">#REF!</definedName>
     <definedName name="Churn">#REF!</definedName>
     <definedName name="churn1">#REF!</definedName>
-    <definedName name="CHW_Bal">'[3]F&amp;F'!#REF!</definedName>
+    <definedName name="CHW_Bal">'[2]F&amp;F'!#REF!</definedName>
     <definedName name="CINTER1">#REF!</definedName>
     <definedName name="CINTER2">#REF!</definedName>
-    <definedName name="cip">[31]Hypothèses!$B$12</definedName>
+    <definedName name="cip">[30]Hypothèses!$B$12</definedName>
     <definedName name="CIT_Marge">#REF!</definedName>
-    <definedName name="city_no">[32]Reference!#REF!</definedName>
+    <definedName name="city_no">[31]Reference!#REF!</definedName>
     <definedName name="CIV_F">#REF!</definedName>
     <definedName name="civils">#REF!</definedName>
     <definedName name="CIVR">#REF!</definedName>
-    <definedName name="clastdate">[27]BasicInfo!$G$10</definedName>
-    <definedName name="CLBSS">[15]MAIPLH!$H$9:$I$9,[15]MAIPLH!$I$11:$I$14,[15]MAIPLH!$H$12,[15]MAIPLH!$H$14,[15]MAIPLH!$I$16,[15]MAIPLH!$I$19,[15]MAIPLH!$H$22:$I$26,[15]MAIPLH!$H$28:$I$28,[15]MAIPLH!$H$31:$I$31,[15]MAIPLH!$H$45:$I$45,[15]MAIPLH!$H$48:$I$48,[15]MAIPLH!$H$51:$I$51,[15]MAIPLH!$H$54:$I$54</definedName>
-    <definedName name="CLBSSLEGU1">[16]MAILEGUH!$H$9:$I$9,[16]MAILEGUH!$I$11:$I$14,[16]MAILEGUH!$H$12,[16]MAILEGUH!$H$14,[16]MAILEGUH!$I$16,[16]MAILEGUH!$I$19,[16]MAILEGUH!$H$22:$I$26,[16]MAILEGUH!$H$28:$I$28,[16]MAILEGUH!$H$31:$I$31</definedName>
-    <definedName name="CLBSSLEGU2">[16]MAILEGUH!$H$34:$I$34,[16]MAILEGUH!$H$45:$I$45,[16]MAILEGUH!$H$48:$I$48,[16]MAILEGUH!$H$51:$I$51,[16]MAILEGUH!$H$54:$I$54</definedName>
-    <definedName name="CLEAN">[33]data!$B$217:$GG$416</definedName>
+    <definedName name="clastdate">[26]BasicInfo!$G$10</definedName>
+    <definedName name="CLBSS">[14]MAIPLH!$H$9:$I$9,[14]MAIPLH!$I$11:$I$14,[14]MAIPLH!$H$12,[14]MAIPLH!$H$14,[14]MAIPLH!$I$16,[14]MAIPLH!$I$19,[14]MAIPLH!$H$22:$I$26,[14]MAIPLH!$H$28:$I$28,[14]MAIPLH!$H$31:$I$31,[14]MAIPLH!$H$45:$I$45,[14]MAIPLH!$H$48:$I$48,[14]MAIPLH!$H$51:$I$51,[14]MAIPLH!$H$54:$I$54</definedName>
+    <definedName name="CLBSSLEGU1">[15]MAILEGUH!$H$9:$I$9,[15]MAILEGUH!$I$11:$I$14,[15]MAILEGUH!$H$12,[15]MAILEGUH!$H$14,[15]MAILEGUH!$I$16,[15]MAILEGUH!$I$19,[15]MAILEGUH!$H$22:$I$26,[15]MAILEGUH!$H$28:$I$28,[15]MAILEGUH!$H$31:$I$31</definedName>
+    <definedName name="CLBSSLEGU2">[15]MAILEGUH!$H$34:$I$34,[15]MAILEGUH!$H$45:$I$45,[15]MAILEGUH!$H$48:$I$48,[15]MAILEGUH!$H$51:$I$51,[15]MAILEGUH!$H$54:$I$54</definedName>
+    <definedName name="CLEAN">[32]data!$B$217:$GG$416</definedName>
     <definedName name="CLEI">#REF!</definedName>
-    <definedName name="Client">[27]Companycode!$F$7:$F$44</definedName>
+    <definedName name="Client">[26]Companycode!$F$7:$F$44</definedName>
     <definedName name="CLIENTE">#REF!</definedName>
-    <definedName name="CLIN">'[34]Name Ranges (DO NOT CHANGE)'!$A$14:$A$71</definedName>
-    <definedName name="CLMW">[15]MAIPLH!$Q$9:$R$9,[15]MAIPLH!$R$11:$R$14,[15]MAIPLH!$Q$12,[15]MAIPLH!$Q$14,[15]MAIPLH!$R$16,[15]MAIPLH!$R$19,[15]MAIPLH!$Q$22:$R$26,[15]MAIPLH!$Q$28:$R$28,[15]MAIPLH!$Q$31:$R$31,[15]MAIPLH!$Q$45:$R$45,[15]MAIPLH!$Q$48:$R$48,[15]MAIPLH!$Q$51:$R$51,[15]MAIPLH!$Q$54:$R$54</definedName>
-    <definedName name="CLMWLEGU1">[16]MAILEGUH!$Q$9:$R$9,[16]MAILEGUH!$R$11:$R$14,[16]MAILEGUH!$Q$12,[16]MAILEGUH!$Q$14,[16]MAILEGUH!$R$16,[16]MAILEGUH!$R$19,[16]MAILEGUH!$Q$22:$R$26,[16]MAILEGUH!$Q$28:$R$28,[16]MAILEGUH!$Q$31:$R$31</definedName>
-    <definedName name="CLMWLEGU2">[16]MAILEGUH!$Q$41:$R$41,[16]MAILEGUH!$Q$45:$R$45,[16]MAILEGUH!$Q$48:$R$48,[16]MAILEGUH!$Q$51:$R$51,[16]MAILEGUH!$Q$54:$R$54</definedName>
-    <definedName name="CLNCIT">[15]MAIPLH!$K$9:$L$9,[15]MAIPLH!$L$11:$L$14,[15]MAIPLH!$K$12,[15]MAIPLH!$K$14,[15]MAIPLH!$L$16,[15]MAIPLH!$L$19,[15]MAIPLH!$K$22:$L$26,[15]MAIPLH!$K$28:$L$28,[15]MAIPLH!$K$31:$L$31,[15]MAIPLH!$K$45:$L$45,[15]MAIPLH!$K$48:$L$48,[15]MAIPLH!$K$51:$L$51,[15]MAIPLH!$K$54:$L$54</definedName>
-    <definedName name="CLNCITLEGU1">[16]MAILEGUH!$K$9:$L$9,[16]MAILEGUH!$L$11:$L$14,[16]MAILEGUH!$K$12,[16]MAILEGUH!$K$14,[16]MAILEGUH!$L$16,[16]MAILEGUH!$L$19,[16]MAILEGUH!$K$22:$L$26,[16]MAILEGUH!$K$28:$L$28,[16]MAILEGUH!$K$31:$L$31</definedName>
-    <definedName name="CLNCITLEGU2">[16]MAILEGUH!$K$36:$L$36,[16]MAILEGUH!$K$45:$L$45,[16]MAILEGUH!$K$48:$L$48,[16]MAILEGUH!$K$51:$L$51,[16]MAILEGUH!$K$54:$L$54</definedName>
-    <definedName name="CLNSEL">[15]MAIPLH!$N$9:$O$9,[15]MAIPLH!$O$11:$O$14,[15]MAIPLH!$N$12,[15]MAIPLH!$N$14,[15]MAIPLH!$O$16,[15]MAIPLH!$O$19,[15]MAIPLH!$N$22:$O$26,[15]MAIPLH!$N$28:$O$28,[15]MAIPLH!$N$31:$O$31,[15]MAIPLH!$N$45:$O$45,[15]MAIPLH!$N$48:$O$48,[15]MAIPLH!$N$51:$O$51,[15]MAIPLH!$N$54:$O$54</definedName>
-    <definedName name="CLNSELLEGU1">[16]MAILEGUH!$N$9:$O$9,[16]MAILEGUH!$O$11:$O$14,[16]MAILEGUH!$N$12,[16]MAILEGUH!$N$14,[16]MAILEGUH!$O$16,[16]MAILEGUH!$O$19,[16]MAILEGUH!$N$22:$O$26,[16]MAILEGUH!$N$28:$O$28,[16]MAILEGUH!$N$31:$O$31</definedName>
-    <definedName name="CLNSELLEGU2">[16]MAILEGUH!$N$39:$O$39,[16]MAILEGUH!$N$45:$O$45,[16]MAILEGUH!$N$48:$O$48,[16]MAILEGUH!$N$51:$O$51,[16]MAILEGUH!$N$54:$O$54</definedName>
-    <definedName name="CLOT">[15]MAIPLH!$T$9:$U$9,[15]MAIPLH!$U$11:$U$14,[15]MAIPLH!$T$12,[15]MAIPLH!$T$14,[15]MAIPLH!$U$16,[15]MAIPLH!$U$19,[15]MAIPLH!$T$22:$U$26,[15]MAIPLH!$T$28:$U$28,[15]MAIPLH!$T$31:$U$31,[15]MAIPLH!$T$45:$U$45,[15]MAIPLH!$T$48:$U$48,[15]MAIPLH!$T$51:$U$51,[15]MAIPLH!$T$54:$U$54</definedName>
-    <definedName name="CLTOT">[35]MAIPLH!#REF!,[35]MAIPLH!#REF!,[35]MAIPLH!#REF!,[35]MAIPLH!#REF!,[35]MAIPLH!#REF!,[35]MAIPLH!#REF!,[35]MAIPLH!#REF!,[35]MAIPLH!#REF!,[35]MAIPLH!#REF!,[35]MAIPLH!#REF!,[35]MAIPLH!#REF!,[35]MAIPLH!#REF!,[35]MAIPLH!#REF!</definedName>
+    <definedName name="CLIN">'[33]Name Ranges (DO NOT CHANGE)'!$A$14:$A$71</definedName>
+    <definedName name="CLMW">[14]MAIPLH!$Q$9:$R$9,[14]MAIPLH!$R$11:$R$14,[14]MAIPLH!$Q$12,[14]MAIPLH!$Q$14,[14]MAIPLH!$R$16,[14]MAIPLH!$R$19,[14]MAIPLH!$Q$22:$R$26,[14]MAIPLH!$Q$28:$R$28,[14]MAIPLH!$Q$31:$R$31,[14]MAIPLH!$Q$45:$R$45,[14]MAIPLH!$Q$48:$R$48,[14]MAIPLH!$Q$51:$R$51,[14]MAIPLH!$Q$54:$R$54</definedName>
+    <definedName name="CLMWLEGU1">[15]MAILEGUH!$Q$9:$R$9,[15]MAILEGUH!$R$11:$R$14,[15]MAILEGUH!$Q$12,[15]MAILEGUH!$Q$14,[15]MAILEGUH!$R$16,[15]MAILEGUH!$R$19,[15]MAILEGUH!$Q$22:$R$26,[15]MAILEGUH!$Q$28:$R$28,[15]MAILEGUH!$Q$31:$R$31</definedName>
+    <definedName name="CLMWLEGU2">[15]MAILEGUH!$Q$41:$R$41,[15]MAILEGUH!$Q$45:$R$45,[15]MAILEGUH!$Q$48:$R$48,[15]MAILEGUH!$Q$51:$R$51,[15]MAILEGUH!$Q$54:$R$54</definedName>
+    <definedName name="CLNCIT">[14]MAIPLH!$K$9:$L$9,[14]MAIPLH!$L$11:$L$14,[14]MAIPLH!$K$12,[14]MAIPLH!$K$14,[14]MAIPLH!$L$16,[14]MAIPLH!$L$19,[14]MAIPLH!$K$22:$L$26,[14]MAIPLH!$K$28:$L$28,[14]MAIPLH!$K$31:$L$31,[14]MAIPLH!$K$45:$L$45,[14]MAIPLH!$K$48:$L$48,[14]MAIPLH!$K$51:$L$51,[14]MAIPLH!$K$54:$L$54</definedName>
+    <definedName name="CLNCITLEGU1">[15]MAILEGUH!$K$9:$L$9,[15]MAILEGUH!$L$11:$L$14,[15]MAILEGUH!$K$12,[15]MAILEGUH!$K$14,[15]MAILEGUH!$L$16,[15]MAILEGUH!$L$19,[15]MAILEGUH!$K$22:$L$26,[15]MAILEGUH!$K$28:$L$28,[15]MAILEGUH!$K$31:$L$31</definedName>
+    <definedName name="CLNCITLEGU2">[15]MAILEGUH!$K$36:$L$36,[15]MAILEGUH!$K$45:$L$45,[15]MAILEGUH!$K$48:$L$48,[15]MAILEGUH!$K$51:$L$51,[15]MAILEGUH!$K$54:$L$54</definedName>
+    <definedName name="CLNSEL">[14]MAIPLH!$N$9:$O$9,[14]MAIPLH!$O$11:$O$14,[14]MAIPLH!$N$12,[14]MAIPLH!$N$14,[14]MAIPLH!$O$16,[14]MAIPLH!$O$19,[14]MAIPLH!$N$22:$O$26,[14]MAIPLH!$N$28:$O$28,[14]MAIPLH!$N$31:$O$31,[14]MAIPLH!$N$45:$O$45,[14]MAIPLH!$N$48:$O$48,[14]MAIPLH!$N$51:$O$51,[14]MAIPLH!$N$54:$O$54</definedName>
+    <definedName name="CLNSELLEGU1">[15]MAILEGUH!$N$9:$O$9,[15]MAILEGUH!$O$11:$O$14,[15]MAILEGUH!$N$12,[15]MAILEGUH!$N$14,[15]MAILEGUH!$O$16,[15]MAILEGUH!$O$19,[15]MAILEGUH!$N$22:$O$26,[15]MAILEGUH!$N$28:$O$28,[15]MAILEGUH!$N$31:$O$31</definedName>
+    <definedName name="CLNSELLEGU2">[15]MAILEGUH!$N$39:$O$39,[15]MAILEGUH!$N$45:$O$45,[15]MAILEGUH!$N$48:$O$48,[15]MAILEGUH!$N$51:$O$51,[15]MAILEGUH!$N$54:$O$54</definedName>
+    <definedName name="CLOT">[14]MAIPLH!$T$9:$U$9,[14]MAIPLH!$U$11:$U$14,[14]MAIPLH!$T$12,[14]MAIPLH!$T$14,[14]MAIPLH!$U$16,[14]MAIPLH!$U$19,[14]MAIPLH!$T$22:$U$26,[14]MAIPLH!$T$28:$U$28,[14]MAIPLH!$T$31:$U$31,[14]MAIPLH!$T$45:$U$45,[14]MAIPLH!$T$48:$U$48,[14]MAIPLH!$T$51:$U$51,[14]MAIPLH!$T$54:$U$54</definedName>
+    <definedName name="CLTOT">[34]MAIPLH!#REF!,[34]MAIPLH!#REF!,[34]MAIPLH!#REF!,[34]MAIPLH!#REF!,[34]MAIPLH!#REF!,[34]MAIPLH!#REF!,[34]MAIPLH!#REF!,[34]MAIPLH!#REF!,[34]MAIPLH!#REF!,[34]MAIPLH!#REF!,[34]MAIPLH!#REF!,[34]MAIPLH!#REF!,[34]MAIPLH!#REF!</definedName>
     <definedName name="CMPF">#REF!</definedName>
     <definedName name="CMSC1">#REF!</definedName>
     <definedName name="CMSC2">#REF!</definedName>
@@ -507,38 +506,38 @@
     <definedName name="CNTRAIN2">#REF!</definedName>
     <definedName name="CNWAR1">#REF!</definedName>
     <definedName name="CNWAR2">#REF!</definedName>
-    <definedName name="Co_Ric">[6]company!$W$1</definedName>
+    <definedName name="Co_Ric">[5]company!$W$1</definedName>
     <definedName name="Coaxial">#REF!</definedName>
-    <definedName name="COcost">[32]Reference!#REF!</definedName>
-    <definedName name="coderegroup">'[36]NOMENCLATURE NMS'!#REF!</definedName>
+    <definedName name="COcost">[31]Reference!#REF!</definedName>
+    <definedName name="coderegroup">'[35]NOMENCLATURE NMS'!#REF!</definedName>
     <definedName name="coef">#REF!</definedName>
     <definedName name="Coef_Dilu">#REF!</definedName>
     <definedName name="CoefPVloc">#REF!</definedName>
     <definedName name="COFINS">#REF!</definedName>
     <definedName name="Col_Alias2">#REF!</definedName>
-    <definedName name="COL_NAME">[37]cfoa51!$B$2</definedName>
-    <definedName name="ColonnaListinoLP">'[25]parametri di programmazione'!$C$9</definedName>
-    <definedName name="colonnaQtyA">'[25]parametri di programmazione'!$G$9</definedName>
-    <definedName name="colonnaQtyB">'[25]parametri di programmazione'!$H$9</definedName>
-    <definedName name="colonnaQtyC">'[25]parametri di programmazione'!$I$9</definedName>
-    <definedName name="colonnaQtyD">'[25]parametri di programmazione'!$J$9</definedName>
+    <definedName name="COL_NAME">[36]cfoa51!$B$2</definedName>
+    <definedName name="ColonnaListinoLP">'[24]parametri di programmazione'!$C$9</definedName>
+    <definedName name="colonnaQtyA">'[24]parametri di programmazione'!$G$9</definedName>
+    <definedName name="colonnaQtyB">'[24]parametri di programmazione'!$H$9</definedName>
+    <definedName name="colonnaQtyC">'[24]parametri di programmazione'!$I$9</definedName>
+    <definedName name="colonnaQtyD">'[24]parametri di programmazione'!$J$9</definedName>
     <definedName name="COLUNM_WIDTH">#REF!</definedName>
     <definedName name="COMC1">#REF!</definedName>
     <definedName name="COMC2">#REF!</definedName>
     <definedName name="Commitment_discount">#REF!</definedName>
-    <definedName name="Compactage_2">'[38]price regular&amp;HA'!$B$9:$H$76</definedName>
-    <definedName name="company">'[39]Name Ranges (DO NOT CHANGE)'!$A$185:$A$196</definedName>
+    <definedName name="Compactage_2">'[37]price regular&amp;HA'!$B$9:$H$76</definedName>
+    <definedName name="company">'[38]Name Ranges (DO NOT CHANGE)'!$A$185:$A$196</definedName>
     <definedName name="companylist">#REF!</definedName>
     <definedName name="con">#REF!</definedName>
-    <definedName name="ConnectFee_decrease">[9]Assumptions!#REF!</definedName>
-    <definedName name="CONRATE">[16]Entry!$L$28</definedName>
-    <definedName name="Control_Link_1">'[17]Penetration Curve'!$H$58</definedName>
-    <definedName name="Control_Link_1Save">'[17]Penetration Curve'!$I$58</definedName>
+    <definedName name="ConnectFee_decrease">[8]Assumptions!#REF!</definedName>
+    <definedName name="CONRATE">[15]Entry!$L$28</definedName>
+    <definedName name="Control_Link_1">'[16]Penetration Curve'!$H$58</definedName>
+    <definedName name="Control_Link_1Save">'[16]Penetration Curve'!$I$58</definedName>
     <definedName name="Conver_TBL1">#REF!</definedName>
     <definedName name="Conver_TBL2">#REF!</definedName>
     <definedName name="COR_F">#REF!</definedName>
     <definedName name="CORBA_Interface">"Kontrollkästchen 23"</definedName>
-    <definedName name="COref_prc">[32]Reference!#REF!</definedName>
+    <definedName name="COref_prc">[31]Reference!#REF!</definedName>
     <definedName name="CORR">#REF!</definedName>
     <definedName name="cost_factor">#REF!</definedName>
     <definedName name="cost_reductions">#REF!</definedName>
@@ -560,38 +559,38 @@
     <definedName name="coutsalexpat">#REF!</definedName>
     <definedName name="cpackc">#REF!</definedName>
     <definedName name="cpackp">#REF!</definedName>
-    <definedName name="CPAOFCONT">[40]VARDATA!$C$27</definedName>
+    <definedName name="CPAOFCONT">[39]VARDATA!$C$27</definedName>
     <definedName name="Cpdetail">#REF!</definedName>
     <definedName name="CPMF">#REF!</definedName>
-    <definedName name="CRCIT">[16]Entry!$F$28</definedName>
-    <definedName name="CRCITE10">[16]Entry!$F$29</definedName>
-    <definedName name="CROT">[16]Entry!$F$32</definedName>
-    <definedName name="CRSEL">[16]Entry!$F$30</definedName>
-    <definedName name="CRTEL">[16]Entry!$F$31</definedName>
-    <definedName name="CS_Bal">'[3]F&amp;F'!#REF!</definedName>
-    <definedName name="cScenarioValuations">[17]Scenarios!$C$38:$D$64</definedName>
+    <definedName name="CRCIT">[15]Entry!$F$28</definedName>
+    <definedName name="CRCITE10">[15]Entry!$F$29</definedName>
+    <definedName name="CROT">[15]Entry!$F$32</definedName>
+    <definedName name="CRSEL">[15]Entry!$F$30</definedName>
+    <definedName name="CRTEL">[15]Entry!$F$31</definedName>
+    <definedName name="CS_Bal">'[2]F&amp;F'!#REF!</definedName>
+    <definedName name="cScenarioValuations">[16]Scenarios!$C$38:$D$64</definedName>
     <definedName name="CSMIM1">#REF!</definedName>
     <definedName name="CSMIM2">#REF!</definedName>
     <definedName name="CSPARE1">#REF!</definedName>
     <definedName name="CSPARE2">#REF!</definedName>
     <definedName name="CT">#REF!</definedName>
-    <definedName name="ctp_Install">[41]Data!$B$55</definedName>
-    <definedName name="cTrafficData">[17]Scenarios!$C$149:$N$150</definedName>
+    <definedName name="ctp_Install">[40]Data!$B$55</definedName>
+    <definedName name="cTrafficData">[16]Scenarios!$C$149:$N$150</definedName>
     <definedName name="CUMTL">#REF!</definedName>
     <definedName name="CUMUSD">#REF!</definedName>
-    <definedName name="CUR">[6]data!$F$1</definedName>
-    <definedName name="currency">[27]BasicInfo!$E$11</definedName>
-    <definedName name="Currency_Rate">[42]ORACLE!$F$6</definedName>
-    <definedName name="currencymargin">[15]Reference!#REF!</definedName>
+    <definedName name="CUR">[5]data!$F$1</definedName>
+    <definedName name="currency">[26]BasicInfo!$E$11</definedName>
+    <definedName name="Currency_Rate">[41]ORACLE!$F$6</definedName>
+    <definedName name="currencymargin">[14]Reference!#REF!</definedName>
     <definedName name="CurrencyName">#REF!</definedName>
-    <definedName name="CurrType">[26]Input!$A$1</definedName>
-    <definedName name="CUST">[16]Entry!$F$21</definedName>
-    <definedName name="CUSTCRY">[16]Entry!$F$20</definedName>
-    <definedName name="Custom_Rate">[43]Parameters!#REF!</definedName>
-    <definedName name="Custom_Rate2">[43]Parameters!#REF!</definedName>
+    <definedName name="CurrType">[25]Input!$A$1</definedName>
+    <definedName name="CUST">[15]Entry!$F$21</definedName>
+    <definedName name="CUSTCRY">[15]Entry!$F$20</definedName>
+    <definedName name="Custom_Rate">[42]Parameters!#REF!</definedName>
+    <definedName name="Custom_Rate2">[42]Parameters!#REF!</definedName>
     <definedName name="CUSTOMER">#REF!</definedName>
     <definedName name="CustomerName">#REF!</definedName>
-    <definedName name="cValuation">[17]Scenarios!$C$113</definedName>
+    <definedName name="cValuation">[16]Scenarios!$C$113</definedName>
     <definedName name="D">#REF!</definedName>
     <definedName name="DATA">#REF!</definedName>
     <definedName name="data_costredyr1">#REF!</definedName>
@@ -618,28 +617,28 @@
     <definedName name="data_mocyr7">#REF!</definedName>
     <definedName name="_xlnm.Database">#REF!</definedName>
     <definedName name="DATE">#REF!</definedName>
-    <definedName name="DATSAIS">[16]Entry!$L$19</definedName>
-    <definedName name="Datum_erstellt">[44]Parameters!$E$25</definedName>
-    <definedName name="Datum_geändert">[44]Parameters!$E$26</definedName>
+    <definedName name="DATSAIS">[15]Entry!$L$19</definedName>
+    <definedName name="Datum_erstellt">[43]Parameters!$E$25</definedName>
+    <definedName name="Datum_geändert">[43]Parameters!$E$26</definedName>
     <definedName name="DC">#REF!</definedName>
     <definedName name="DD">#REF!</definedName>
     <definedName name="DDF">#REF!</definedName>
-    <definedName name="DECTlink_Version">[30]Planner!#REF!</definedName>
-    <definedName name="DEEEEEE">[45]Parameters!$E$34</definedName>
+    <definedName name="DECTlink_Version">[29]Planner!#REF!</definedName>
+    <definedName name="DEEEEEE">[44]Parameters!$E$34</definedName>
     <definedName name="Delta_postpaid_ARPU">#REF!</definedName>
-    <definedName name="DEMeXToEUR" hidden="1">[46]EurotoolsXRates!$B$7</definedName>
-    <definedName name="DeploymentDicount">[15]Global!$BX$564</definedName>
+    <definedName name="DEMeXToEUR" hidden="1">[45]EurotoolsXRates!$B$7</definedName>
+    <definedName name="DeploymentDicount">[14]Global!$BX$564</definedName>
     <definedName name="deptlist">#REF!</definedName>
-    <definedName name="Despacho">'[12]Input Table'!#REF!</definedName>
+    <definedName name="Despacho">'[11]Input Table'!#REF!</definedName>
     <definedName name="df">#REF!</definedName>
     <definedName name="dfsaf" localSheetId="0" hidden="1">{"msc sw feat summary",#N/A,FALSE,"MSC SW Features v. 1.1."}</definedName>
     <definedName name="dfsaf" hidden="1">{"msc sw feat summary",#N/A,FALSE,"MSC SW Features v. 1.1."}</definedName>
     <definedName name="dfsaf2" localSheetId="0" hidden="1">{"msc sw feat summary",#N/A,FALSE,"MSC SW Features v. 1.1."}</definedName>
     <definedName name="dfsaf2" hidden="1">{"msc sw feat summary",#N/A,FALSE,"MSC SW Features v. 1.1."}</definedName>
-    <definedName name="DIC">'[47]Synth - INDENT 6'!$E$43</definedName>
+    <definedName name="DIC">'[46]Synth - INDENT 6'!$E$43</definedName>
     <definedName name="DIN">#REF!</definedName>
     <definedName name="DINAR">#REF!</definedName>
-    <definedName name="Dis_Spare">[48]DISCOUNT!$B$87</definedName>
+    <definedName name="Dis_Spare">[47]DISCOUNT!$B$87</definedName>
     <definedName name="DisAccommodation">#REF!</definedName>
     <definedName name="DisBattery">#REF!</definedName>
     <definedName name="DisBoard">#REF!</definedName>
@@ -684,14 +683,14 @@
     <definedName name="DisTransmit">#REF!</definedName>
     <definedName name="DISTRIBUTED_5000">#REF!</definedName>
     <definedName name="dl">#REF!</definedName>
-    <definedName name="DLC_Compl_A">[30]Planner!#REF!</definedName>
-    <definedName name="DLC_Compl_B">[30]Planner!#REF!</definedName>
-    <definedName name="DLC_Compl_C">[30]Planner!#REF!</definedName>
-    <definedName name="DLC_Compl_D">[30]Planner!#REF!</definedName>
-    <definedName name="DLC_Compl_E">[30]Planner!#REF!</definedName>
-    <definedName name="DLC_Compl_F">[30]Planner!#REF!</definedName>
-    <definedName name="dMonteCarloResults">[17]Scenarios!$C$187:$C$267</definedName>
-    <definedName name="dMonteCarloVariables">[17]Scenarios!$B$175:$B$178</definedName>
+    <definedName name="DLC_Compl_A">[29]Planner!#REF!</definedName>
+    <definedName name="DLC_Compl_B">[29]Planner!#REF!</definedName>
+    <definedName name="DLC_Compl_C">[29]Planner!#REF!</definedName>
+    <definedName name="DLC_Compl_D">[29]Planner!#REF!</definedName>
+    <definedName name="DLC_Compl_E">[29]Planner!#REF!</definedName>
+    <definedName name="DLC_Compl_F">[29]Planner!#REF!</definedName>
+    <definedName name="dMonteCarloResults">[16]Scenarios!$C$187:$C$267</definedName>
+    <definedName name="dMonteCarloVariables">[16]Scenarios!$B$175:$B$178</definedName>
     <definedName name="DNSSCIT">#REF!</definedName>
     <definedName name="DNSSSEL">#REF!</definedName>
     <definedName name="DOLAR">#REF!</definedName>
@@ -701,28 +700,28 @@
     <definedName name="drop_software">"Dropdown 3"</definedName>
     <definedName name="dsaf" localSheetId="0" hidden="1">{"'Edit'!$A$1:$V$2277"}</definedName>
     <definedName name="dsaf" hidden="1">{"'Edit'!$A$1:$V$2277"}</definedName>
-    <definedName name="dScenariosDefined">[17]Scenarios!$B$7:$F$33</definedName>
-    <definedName name="dScenarioValuations">[17]Scenarios!$F$119:$G$145</definedName>
+    <definedName name="dScenariosDefined">[16]Scenarios!$B$7:$F$33</definedName>
+    <definedName name="dScenarioValuations">[16]Scenarios!$F$119:$G$145</definedName>
     <definedName name="dsd" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"Discount";#N/A,#N/A,TRUE,"Sommaire";#N/A,#N/A,TRUE,"Services";#N/A,#N/A,TRUE,"RNP";#N/A,#N/A,TRUE,"Support";#N/A,#N/A,TRUE,"BSS";#N/A,#N/A,TRUE,"BTS";#N/A,#N/A,TRUE,"BSC";#N/A,#N/A,TRUE,"BSC1";#N/A,#N/A,TRUE,"TRANSCODER";#N/A,#N/A,TRUE,"OMC-R";#N/A,#N/A,TRUE,"MW";#N/A,#N/A,TRUE,"DIESEL";#N/A,#N/A,TRUE,"TOWERS";#N/A,#N/A,TRUE,"ANTENNAS";#N/A,#N/A,TRUE,"SHELTERS";#N/A,#N/A,TRUE,"SPARES";#N/A,#N/A,TRUE,"SP_item";#N/A,#N/A,TRUE,"TOOLS";#N/A,#N/A,TRUE,"DOC";#N/A,#N/A,TRUE,"Mobile"}</definedName>
     <definedName name="dsd" hidden="1">{#N/A,#N/A,TRUE,"Discount";#N/A,#N/A,TRUE,"Sommaire";#N/A,#N/A,TRUE,"Services";#N/A,#N/A,TRUE,"RNP";#N/A,#N/A,TRUE,"Support";#N/A,#N/A,TRUE,"BSS";#N/A,#N/A,TRUE,"BTS";#N/A,#N/A,TRUE,"BSC";#N/A,#N/A,TRUE,"BSC1";#N/A,#N/A,TRUE,"TRANSCODER";#N/A,#N/A,TRUE,"OMC-R";#N/A,#N/A,TRUE,"MW";#N/A,#N/A,TRUE,"DIESEL";#N/A,#N/A,TRUE,"TOWERS";#N/A,#N/A,TRUE,"ANTENNAS";#N/A,#N/A,TRUE,"SHELTERS";#N/A,#N/A,TRUE,"SPARES";#N/A,#N/A,TRUE,"SP_item";#N/A,#N/A,TRUE,"TOOLS";#N/A,#N/A,TRUE,"DOC";#N/A,#N/A,TRUE,"Mobile"}</definedName>
     <definedName name="DTN">#REF!</definedName>
-    <definedName name="dTrafficData">[17]Scenarios!$C$153:$N$154</definedName>
+    <definedName name="dTrafficData">[16]Scenarios!$C$153:$N$154</definedName>
     <definedName name="dual">#REF!</definedName>
-    <definedName name="dValuation">[17]Scenarios!$C$114</definedName>
-    <definedName name="dVariableSetting">[17]Scenarios!$E$187:$H$267</definedName>
+    <definedName name="dValuation">[16]Scenarios!$C$114</definedName>
+    <definedName name="dVariableSetting">[16]Scenarios!$E$187:$H$267</definedName>
     <definedName name="dxc">#REF!</definedName>
     <definedName name="dxp">#REF!</definedName>
     <definedName name="E">#REF!</definedName>
     <definedName name="E1_Channels">30</definedName>
     <definedName name="EAT">#REF!</definedName>
     <definedName name="EDE">#REF!</definedName>
-    <definedName name="EDOF">[16]Entry!$F$24</definedName>
-    <definedName name="ee">[49]MD5500!$A$15:$M$168</definedName>
+    <definedName name="EDOF">[15]Entry!$F$24</definedName>
+    <definedName name="ee">[48]MD5500!$A$15:$M$168</definedName>
     <definedName name="eedd">#REF!</definedName>
     <definedName name="eee">#REF!</definedName>
     <definedName name="EICON_TECHNOLOGY">#REF!</definedName>
-    <definedName name="end_of_summary">[19]Summary!$A$11</definedName>
-    <definedName name="ENTCONT">[16]Entry!$F$19</definedName>
+    <definedName name="end_of_summary">[18]Summary!$A$11</definedName>
+    <definedName name="ENTCONT">[15]Entry!$F$19</definedName>
     <definedName name="eq_deu_cp113cr">#REF!</definedName>
     <definedName name="eqtp">#REF!</definedName>
     <definedName name="er" localSheetId="0" hidden="1">{"msc sw feat summary",#N/A,FALSE,"MSC SW Features v. 1.1."}</definedName>
@@ -732,42 +731,42 @@
     <definedName name="ERL_SUBS">#REF!</definedName>
     <definedName name="ETM">#REF!</definedName>
     <definedName name="eu">#REF!</definedName>
-    <definedName name="eur">[50]Currency!$B$6</definedName>
+    <definedName name="eur">[49]Currency!$B$6</definedName>
     <definedName name="EURO">#REF!</definedName>
     <definedName name="Euro__1.1.99">#REF!</definedName>
-    <definedName name="Euro_Test">[51]Vorlage_8!#REF!</definedName>
-    <definedName name="Euro_Test2">[52]Promotions!#REF!</definedName>
+    <definedName name="Euro_Test">[50]Vorlage_8!#REF!</definedName>
+    <definedName name="Euro_Test2">[51]Promotions!#REF!</definedName>
     <definedName name="ewrewre">#REF!</definedName>
-    <definedName name="Exchange_Rate">'[12]Input Table'!#REF!</definedName>
-    <definedName name="ExchRate">[53]Factors!$C$15</definedName>
+    <definedName name="Exchange_Rate">'[11]Input Table'!#REF!</definedName>
+    <definedName name="ExchRate">[52]Factors!$C$15</definedName>
     <definedName name="expected_nodeB">#REF!</definedName>
     <definedName name="F">#REF!</definedName>
     <definedName name="FAC">#REF!</definedName>
     <definedName name="FACEU">#REF!</definedName>
-    <definedName name="fact">[54]total!#REF!</definedName>
+    <definedName name="fact">[53]total!#REF!</definedName>
     <definedName name="FACUSD">#REF!</definedName>
-    <definedName name="Faktor">[53]Factors!$D$5</definedName>
-    <definedName name="Faktor_auf_BHK">[55]Basis_für_Preise_und_Texte!#REF!</definedName>
-    <definedName name="faktor_auf_service">[55]Basis_für_Preise_und_Texte!#REF!</definedName>
-    <definedName name="Faktor_auf_Training">[55]Basis_für_Preise_und_Texte!#REF!</definedName>
+    <definedName name="Faktor">[52]Factors!$D$5</definedName>
+    <definedName name="Faktor_auf_BHK">[54]Basis_für_Preise_und_Texte!#REF!</definedName>
+    <definedName name="faktor_auf_service">[54]Basis_für_Preise_und_Texte!#REF!</definedName>
+    <definedName name="Faktor_auf_Training">[54]Basis_für_Preise_und_Texte!#REF!</definedName>
     <definedName name="Faktor_VGK_AGK">#REF!</definedName>
     <definedName name="fd" localSheetId="0" hidden="1">{"COST",#N/A,FALSE,"SYNTHESE";"MARGIN",#N/A,FALSE,"SYNTHESE";"LOT_COM",#N/A,FALSE,"SYNTHESE"}</definedName>
     <definedName name="fd" hidden="1">{"COST",#N/A,FALSE,"SYNTHESE";"MARGIN",#N/A,FALSE,"SYNTHESE";"LOT_COM",#N/A,FALSE,"SYNTHESE"}</definedName>
     <definedName name="fdr">#REF!</definedName>
     <definedName name="Fee">#REF!</definedName>
-    <definedName name="FF_Bal">'[3]F&amp;F'!#REF!</definedName>
+    <definedName name="FF_Bal">'[2]F&amp;F'!#REF!</definedName>
     <definedName name="FFFFF">#REF!</definedName>
     <definedName name="FFFFFFFFFFF">#REF!</definedName>
     <definedName name="FFFFFFFFFFFFFF">#REF!</definedName>
     <definedName name="FFFFFFFFFFFFFFFFFFFF">#REF!</definedName>
     <definedName name="ffs">#REF!</definedName>
     <definedName name="fg">#REF!</definedName>
-    <definedName name="FinalVersion">[56]Kalkulation!$C$28</definedName>
+    <definedName name="FinalVersion">[55]Kalkulation!$C$28</definedName>
     <definedName name="findetial">#REF!</definedName>
-    <definedName name="FN">[26]Input!$P$3</definedName>
+    <definedName name="FN">[25]Input!$P$3</definedName>
     <definedName name="fob_bss">#REF!</definedName>
     <definedName name="FOBLIST" hidden="1">#REF!</definedName>
-    <definedName name="forbid">[57]change!$C$3</definedName>
+    <definedName name="forbid">[56]change!$C$3</definedName>
     <definedName name="FormatFile">"WEB.CHANGE.889.FMT"</definedName>
     <definedName name="fr">#REF!</definedName>
     <definedName name="FRAIS">#REF!</definedName>
@@ -776,41 +775,41 @@
     <definedName name="freq">#REF!</definedName>
     <definedName name="Frrr" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"Discount";#N/A,#N/A,TRUE,"Sommaire";#N/A,#N/A,TRUE,"Services";#N/A,#N/A,TRUE,"RNP";#N/A,#N/A,TRUE,"Support";#N/A,#N/A,TRUE,"BSS";#N/A,#N/A,TRUE,"BTS";#N/A,#N/A,TRUE,"BSC";#N/A,#N/A,TRUE,"BSC1";#N/A,#N/A,TRUE,"TRANSCODER";#N/A,#N/A,TRUE,"OMC-R";#N/A,#N/A,TRUE,"MW";#N/A,#N/A,TRUE,"DIESEL";#N/A,#N/A,TRUE,"TOWERS";#N/A,#N/A,TRUE,"ANTENNAS";#N/A,#N/A,TRUE,"SHELTERS";#N/A,#N/A,TRUE,"SPARES";#N/A,#N/A,TRUE,"SP_item";#N/A,#N/A,TRUE,"TOOLS";#N/A,#N/A,TRUE,"DOC";#N/A,#N/A,TRUE,"Mobile"}</definedName>
     <definedName name="Frrr" hidden="1">{#N/A,#N/A,TRUE,"Discount";#N/A,#N/A,TRUE,"Sommaire";#N/A,#N/A,TRUE,"Services";#N/A,#N/A,TRUE,"RNP";#N/A,#N/A,TRUE,"Support";#N/A,#N/A,TRUE,"BSS";#N/A,#N/A,TRUE,"BTS";#N/A,#N/A,TRUE,"BSC";#N/A,#N/A,TRUE,"BSC1";#N/A,#N/A,TRUE,"TRANSCODER";#N/A,#N/A,TRUE,"OMC-R";#N/A,#N/A,TRUE,"MW";#N/A,#N/A,TRUE,"DIESEL";#N/A,#N/A,TRUE,"TOWERS";#N/A,#N/A,TRUE,"ANTENNAS";#N/A,#N/A,TRUE,"SHELTERS";#N/A,#N/A,TRUE,"SPARES";#N/A,#N/A,TRUE,"SP_item";#N/A,#N/A,TRUE,"TOOLS";#N/A,#N/A,TRUE,"DOC";#N/A,#N/A,TRUE,"Mobile"}</definedName>
-    <definedName name="FullAvTabls">[58]KB!$A$2:$C$24</definedName>
+    <definedName name="FullAvTabls">[57]KB!$A$2:$C$24</definedName>
     <definedName name="fullview">#REF!</definedName>
     <definedName name="FX">#REF!</definedName>
     <definedName name="FXR">#REF!</definedName>
     <definedName name="G">#REF!</definedName>
     <definedName name="g_a">0.215</definedName>
-    <definedName name="gc">'[18]Total GSM  Market'!#REF!</definedName>
+    <definedName name="gc">'[17]Total GSM  Market'!#REF!</definedName>
     <definedName name="gfgf">#REF!</definedName>
     <definedName name="GGGGGGGGG">#REF!</definedName>
     <definedName name="GGGGGGGGGG">#REF!</definedName>
     <definedName name="GGGGGGGGGGGGGG">#REF!</definedName>
     <definedName name="GGGGGGGGGGGGGGGGGGGGGGG">#REF!</definedName>
-    <definedName name="ggpb">'[59]Angebotskalkulation (€)'!#REF!</definedName>
-    <definedName name="ggpf">'[59]Angebotskalkulation (€)'!#REF!</definedName>
-    <definedName name="ggpl">'[59]Angebotskalkulation (€)'!#REF!</definedName>
+    <definedName name="ggpb">'[58]Angebotskalkulation (€)'!#REF!</definedName>
+    <definedName name="ggpf">'[58]Angebotskalkulation (€)'!#REF!</definedName>
+    <definedName name="ggpl">'[58]Angebotskalkulation (€)'!#REF!</definedName>
     <definedName name="ghhj" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
     <definedName name="ghhj" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
     <definedName name="ghj" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
     <definedName name="ghj" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
     <definedName name="gjv" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"Discount";#N/A,#N/A,TRUE,"Sommaire";#N/A,#N/A,TRUE,"Services";#N/A,#N/A,TRUE,"RNP";#N/A,#N/A,TRUE,"Support";#N/A,#N/A,TRUE,"BSS";#N/A,#N/A,TRUE,"BTS";#N/A,#N/A,TRUE,"BSC";#N/A,#N/A,TRUE,"BSC1";#N/A,#N/A,TRUE,"TRANSCODER";#N/A,#N/A,TRUE,"OMC-R";#N/A,#N/A,TRUE,"MW";#N/A,#N/A,TRUE,"DIESEL";#N/A,#N/A,TRUE,"TOWERS";#N/A,#N/A,TRUE,"ANTENNAS";#N/A,#N/A,TRUE,"SHELTERS";#N/A,#N/A,TRUE,"SPARES";#N/A,#N/A,TRUE,"SP_item";#N/A,#N/A,TRUE,"TOOLS";#N/A,#N/A,TRUE,"DOC";#N/A,#N/A,TRUE,"Mobile"}</definedName>
     <definedName name="gjv" hidden="1">{#N/A,#N/A,TRUE,"Discount";#N/A,#N/A,TRUE,"Sommaire";#N/A,#N/A,TRUE,"Services";#N/A,#N/A,TRUE,"RNP";#N/A,#N/A,TRUE,"Support";#N/A,#N/A,TRUE,"BSS";#N/A,#N/A,TRUE,"BTS";#N/A,#N/A,TRUE,"BSC";#N/A,#N/A,TRUE,"BSC1";#N/A,#N/A,TRUE,"TRANSCODER";#N/A,#N/A,TRUE,"OMC-R";#N/A,#N/A,TRUE,"MW";#N/A,#N/A,TRUE,"DIESEL";#N/A,#N/A,TRUE,"TOWERS";#N/A,#N/A,TRUE,"ANTENNAS";#N/A,#N/A,TRUE,"SHELTERS";#N/A,#N/A,TRUE,"SPARES";#N/A,#N/A,TRUE,"SP_item";#N/A,#N/A,TRUE,"TOOLS";#N/A,#N/A,TRUE,"DOC";#N/A,#N/A,TRUE,"Mobile"}</definedName>
-    <definedName name="gkp">'[59]Angebotskalkulation (€)'!#REF!</definedName>
-    <definedName name="gkpm">'[59]Angebotskalkulation (€)'!#REF!</definedName>
+    <definedName name="gkp">'[58]Angebotskalkulation (€)'!#REF!</definedName>
+    <definedName name="gkpm">'[58]Angebotskalkulation (€)'!#REF!</definedName>
     <definedName name="GPRS_percentage">#REF!</definedName>
     <definedName name="gprs2001">#REF!</definedName>
     <definedName name="gprshw">#REF!</definedName>
     <definedName name="gprssw">#REF!</definedName>
-    <definedName name="Gradetype">[60]main!$B$1</definedName>
-    <definedName name="Gradetypecol">[60]main!$B$1:$B$65535</definedName>
+    <definedName name="Gradetype">[59]main!$B$1</definedName>
+    <definedName name="Gradetypecol">[59]main!$B$1:$B$65535</definedName>
     <definedName name="Graphics">#REF!</definedName>
     <definedName name="GSM_DCS">#REF!</definedName>
     <definedName name="H">#REF!</definedName>
-    <definedName name="HalfRate">[26]Input!#REF!</definedName>
-    <definedName name="Handset_depr">[9]Assumptions!#REF!</definedName>
-    <definedName name="Handset_subsidy">[9]Assumptions!#REF!</definedName>
+    <definedName name="HalfRate">[25]Input!#REF!</definedName>
+    <definedName name="Handset_depr">[8]Assumptions!#REF!</definedName>
+    <definedName name="Handset_subsidy">[8]Assumptions!#REF!</definedName>
     <definedName name="hardware_revtotal">#REF!</definedName>
     <definedName name="hardwarerevyr1">#REF!</definedName>
     <definedName name="hardwarerevyr2">#REF!</definedName>
@@ -819,21 +818,21 @@
     <definedName name="hardwarerevyr5">#REF!</definedName>
     <definedName name="hardwarerevyr6">#REF!</definedName>
     <definedName name="hardwarerevyr7">#REF!</definedName>
-    <definedName name="heavy">[42]ORACLE!$G$8</definedName>
+    <definedName name="heavy">[41]ORACLE!$G$8</definedName>
     <definedName name="hello" localSheetId="0" hidden="1">{"COST",#N/A,FALSE,"SYNTHESE";"MARGIN",#N/A,FALSE,"SYNTHESE";"LOT_COM",#N/A,FALSE,"SYNTHESE"}</definedName>
     <definedName name="hello" hidden="1">{"COST",#N/A,FALSE,"SYNTHESE";"MARGIN",#N/A,FALSE,"SYNTHESE";"LOT_COM",#N/A,FALSE,"SYNTHESE"}</definedName>
     <definedName name="help">#REF!</definedName>
-    <definedName name="HHHHHHHHH">'[3]F&amp;F'!#REF!</definedName>
+    <definedName name="HHHHHHHHH">'[2]F&amp;F'!#REF!</definedName>
     <definedName name="HHHHHHHHHHHH">#REF!</definedName>
     <definedName name="HHHHHHHHHHHHH">#REF!</definedName>
     <definedName name="HHHHHHHHHHHHHHHHHHHH">#REF!</definedName>
     <definedName name="HHHHHHHHHHHHHHHHHHHHH">#REF!</definedName>
     <definedName name="HHHHHHHHHHHHHHHHHHHHHHHH">#REF!</definedName>
     <definedName name="HHHHHHHHHHHHHHHHHHHHHHHHHH">#REF!</definedName>
-    <definedName name="hig">[42]ORACLE!$G$8</definedName>
+    <definedName name="hig">[41]ORACLE!$G$8</definedName>
     <definedName name="HIGH">#REF!</definedName>
-    <definedName name="HighValue">[17]Scenarios!$C$162</definedName>
-    <definedName name="HK">[6]graphs!$I$6</definedName>
+    <definedName name="HighValue">[16]Scenarios!$C$162</definedName>
+    <definedName name="HK">[5]graphs!$I$6</definedName>
     <definedName name="HOJE">#REF!</definedName>
     <definedName name="HR">#REF!</definedName>
     <definedName name="HTML_CodePage" hidden="1">1252</definedName>
@@ -853,76 +852,76 @@
     <definedName name="HTML_Title" hidden="1">"Master Edit List"</definedName>
     <definedName name="HUX_F">#REF!</definedName>
     <definedName name="HUXR">#REF!</definedName>
-    <definedName name="HW__Eigenbezug__Faktor_auf_OP">[55]Basis_für_Preise_und_Texte!#REF!</definedName>
-    <definedName name="HW__PC__SW__Faktor_auf_OP">[55]Basis_für_Preise_und_Texte!#REF!</definedName>
+    <definedName name="HW__Eigenbezug__Faktor_auf_OP">[54]Basis_für_Preise_und_Texte!#REF!</definedName>
+    <definedName name="HW__PC__SW__Faktor_auf_OP">[54]Basis_für_Preise_und_Texte!#REF!</definedName>
     <definedName name="I">#REF!</definedName>
-    <definedName name="i_AlarmRoutMultDest">[61]Input!$C$80</definedName>
-    <definedName name="i_BasicOSR4Upg">[61]Input!$C$76</definedName>
-    <definedName name="i_BasisOSR3Upg">[61]Input!$C$72</definedName>
-    <definedName name="i_ChargAdminIF">[61]Input!$C$69</definedName>
-    <definedName name="i_FaultManagIF">[61]Input!$C$68</definedName>
-    <definedName name="i_FlexFilterOfAlarms">[61]Input!$C$79</definedName>
-    <definedName name="i_ForeignTermA">[61]Input!$C$66</definedName>
-    <definedName name="i_FTAM_ChargFiles">[61]Input!$C$71</definedName>
-    <definedName name="i_FTAM_TM_Data">[61]Input!$C$73</definedName>
-    <definedName name="i_MF_Intercep">[61]Input!$C$77</definedName>
-    <definedName name="i_Spots4.0">[61]Input!$C$82</definedName>
-    <definedName name="i_Spots4.1">[61]Input!$C$84</definedName>
-    <definedName name="i_Spots5.1">[61]Input!$C$90</definedName>
-    <definedName name="i_SpotsApplSW">[61]Input!$C$74</definedName>
-    <definedName name="i_SpotsUpgr4.0">[61]Input!$C$83</definedName>
-    <definedName name="i_SpotsUpgr4.1">[61]Input!$C$85</definedName>
-    <definedName name="i_SpotsUpgr5.1">[61]Input!$C$91</definedName>
-    <definedName name="i_SubsAdmIFR2">[61]Input!$C$64</definedName>
-    <definedName name="i_SubsAdmIFR3Upg">[61]Input!$C$70</definedName>
-    <definedName name="i_SubsAdmIFR4Upg">[61]Input!$C$81</definedName>
-    <definedName name="i_SupportIN">[61]Input!$C$78</definedName>
-    <definedName name="i_SysStatusDisp">[61]Input!$C$65</definedName>
+    <definedName name="i_AlarmRoutMultDest">[60]Input!$C$80</definedName>
+    <definedName name="i_BasicOSR4Upg">[60]Input!$C$76</definedName>
+    <definedName name="i_BasisOSR3Upg">[60]Input!$C$72</definedName>
+    <definedName name="i_ChargAdminIF">[60]Input!$C$69</definedName>
+    <definedName name="i_FaultManagIF">[60]Input!$C$68</definedName>
+    <definedName name="i_FlexFilterOfAlarms">[60]Input!$C$79</definedName>
+    <definedName name="i_ForeignTermA">[60]Input!$C$66</definedName>
+    <definedName name="i_FTAM_ChargFiles">[60]Input!$C$71</definedName>
+    <definedName name="i_FTAM_TM_Data">[60]Input!$C$73</definedName>
+    <definedName name="i_MF_Intercep">[60]Input!$C$77</definedName>
+    <definedName name="i_Spots4.0">[60]Input!$C$82</definedName>
+    <definedName name="i_Spots4.1">[60]Input!$C$84</definedName>
+    <definedName name="i_Spots5.1">[60]Input!$C$90</definedName>
+    <definedName name="i_SpotsApplSW">[60]Input!$C$74</definedName>
+    <definedName name="i_SpotsUpgr4.0">[60]Input!$C$83</definedName>
+    <definedName name="i_SpotsUpgr4.1">[60]Input!$C$85</definedName>
+    <definedName name="i_SpotsUpgr5.1">[60]Input!$C$91</definedName>
+    <definedName name="i_SubsAdmIFR2">[60]Input!$C$64</definedName>
+    <definedName name="i_SubsAdmIFR3Upg">[60]Input!$C$70</definedName>
+    <definedName name="i_SubsAdmIFR4Upg">[60]Input!$C$81</definedName>
+    <definedName name="i_SupportIN">[60]Input!$C$78</definedName>
+    <definedName name="i_SysStatusDisp">[60]Input!$C$65</definedName>
     <definedName name="IBS" localSheetId="0" hidden="1">{"'Planner Cell based'!$A$1:$H$142"}</definedName>
     <definedName name="IBS" hidden="1">{"'Planner Cell based'!$A$1:$H$142"}</definedName>
-    <definedName name="ICMS_Cable_modem">'[12]Input Table'!#REF!</definedName>
-    <definedName name="ICMS_Headend">'[12]Input Table'!#REF!</definedName>
-    <definedName name="ICMS_Hubs">'[12]Input Table'!#REF!</definedName>
-    <definedName name="ICMS_Partes_Peças">'[12]Input Table'!#REF!</definedName>
+    <definedName name="ICMS_Cable_modem">'[11]Input Table'!#REF!</definedName>
+    <definedName name="ICMS_Headend">'[11]Input Table'!#REF!</definedName>
+    <definedName name="ICMS_Hubs">'[11]Input Table'!#REF!</definedName>
+    <definedName name="ICMS_Partes_Peças">'[11]Input Table'!#REF!</definedName>
     <definedName name="ICMS_PPB">#REF!</definedName>
-    <definedName name="ICMS_RAS">'[12]Input Table'!#REF!</definedName>
-    <definedName name="ICMS_Routers">'[12]Input Table'!#REF!</definedName>
-    <definedName name="ICMS_Switch">'[12]Input Table'!#REF!</definedName>
-    <definedName name="IF_CBC">[26]Input!#REF!</definedName>
-    <definedName name="II_Cable_modem">'[12]Input Table'!#REF!</definedName>
-    <definedName name="II_Headend">'[12]Input Table'!#REF!</definedName>
-    <definedName name="II_Hubs">'[12]Input Table'!#REF!</definedName>
-    <definedName name="II_Partes_Peças">'[12]Input Table'!#REF!</definedName>
-    <definedName name="II_RAS">'[12]Input Table'!#REF!</definedName>
-    <definedName name="II_Routers">'[12]Input Table'!#REF!</definedName>
-    <definedName name="II_Switch">'[12]Input Table'!#REF!</definedName>
+    <definedName name="ICMS_RAS">'[11]Input Table'!#REF!</definedName>
+    <definedName name="ICMS_Routers">'[11]Input Table'!#REF!</definedName>
+    <definedName name="ICMS_Switch">'[11]Input Table'!#REF!</definedName>
+    <definedName name="IF_CBC">[25]Input!#REF!</definedName>
+    <definedName name="II_Cable_modem">'[11]Input Table'!#REF!</definedName>
+    <definedName name="II_Headend">'[11]Input Table'!#REF!</definedName>
+    <definedName name="II_Hubs">'[11]Input Table'!#REF!</definedName>
+    <definedName name="II_Partes_Peças">'[11]Input Table'!#REF!</definedName>
+    <definedName name="II_RAS">'[11]Input Table'!#REF!</definedName>
+    <definedName name="II_Routers">'[11]Input Table'!#REF!</definedName>
+    <definedName name="II_Switch">'[11]Input Table'!#REF!</definedName>
     <definedName name="Importador">#REF!</definedName>
     <definedName name="IN">#REF!</definedName>
     <definedName name="InclDefferal">#REF!</definedName>
-    <definedName name="Included">[17]Scenarios!$C$166</definedName>
-    <definedName name="indica_name">[44]Parameters!$C$31</definedName>
-    <definedName name="indica_orga">[44]Parameters!$C$32</definedName>
+    <definedName name="Included">[16]Scenarios!$C$166</definedName>
+    <definedName name="indica_name">[43]Parameters!$C$31</definedName>
+    <definedName name="indica_orga">[43]Parameters!$C$32</definedName>
     <definedName name="IndLoc">#REF!</definedName>
     <definedName name="Infr_Shar">#REF!</definedName>
-    <definedName name="INR">[6]graphs!$O$6</definedName>
+    <definedName name="INR">[5]graphs!$O$6</definedName>
     <definedName name="installation">#REF!</definedName>
     <definedName name="INSTANT_INTERNET">#REF!</definedName>
     <definedName name="Insurance">#REF!</definedName>
     <definedName name="Interconnect_Paid_Rate">#N/A</definedName>
     <definedName name="Internal_Price_List__Export_">#REF!</definedName>
-    <definedName name="IPI_Cable_modem">'[12]Input Table'!#REF!</definedName>
-    <definedName name="IPI_Headend">'[12]Input Table'!#REF!</definedName>
-    <definedName name="IPI_Hubs">'[12]Input Table'!#REF!</definedName>
-    <definedName name="IPI_Partes_Peças">'[12]Input Table'!#REF!</definedName>
+    <definedName name="IPI_Cable_modem">'[11]Input Table'!#REF!</definedName>
+    <definedName name="IPI_Headend">'[11]Input Table'!#REF!</definedName>
+    <definedName name="IPI_Hubs">'[11]Input Table'!#REF!</definedName>
+    <definedName name="IPI_Partes_Peças">'[11]Input Table'!#REF!</definedName>
     <definedName name="IPI_PPB">#REF!</definedName>
-    <definedName name="IPI_RAS">'[12]Input Table'!#REF!</definedName>
-    <definedName name="IPI_Routers">'[12]Input Table'!#REF!</definedName>
-    <definedName name="IPI_Switch">'[12]Input Table'!#REF!</definedName>
+    <definedName name="IPI_RAS">'[11]Input Table'!#REF!</definedName>
+    <definedName name="IPI_Routers">'[11]Input Table'!#REF!</definedName>
+    <definedName name="IPI_Switch">'[11]Input Table'!#REF!</definedName>
     <definedName name="IPIS" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
     <definedName name="IPIS" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
     <definedName name="IR">#REF!</definedName>
     <definedName name="ISS">#REF!</definedName>
-    <definedName name="Issue">[44]Definitions!$B$373</definedName>
+    <definedName name="Issue">[43]Definitions!$B$373</definedName>
     <definedName name="J">#REF!</definedName>
     <definedName name="james">#REF!</definedName>
     <definedName name="jaspher" localSheetId="0" hidden="1">{"msc sw feat summary",#N/A,FALSE,"MSC SW Features v. 1.1."}</definedName>
@@ -933,7 +932,7 @@
     <definedName name="jj" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"Sensitivity"}</definedName>
     <definedName name="jj" hidden="1">{#N/A,#N/A,FALSE,"Sensitivity"}</definedName>
     <definedName name="Johritsu">#REF!</definedName>
-    <definedName name="JPY">[6]graphs!$AA$6</definedName>
+    <definedName name="JPY">[5]graphs!$AA$6</definedName>
     <definedName name="Jumper">#REF!</definedName>
     <definedName name="JV">#REF!</definedName>
     <definedName name="K">#REF!</definedName>
@@ -960,21 +959,21 @@
     <definedName name="KHY_F">#REF!</definedName>
     <definedName name="KHYR">#REF!</definedName>
     <definedName name="Komm_Risk_Proz">#REF!</definedName>
-    <definedName name="kp">'[59]Angebotskalkulation (€)'!#REF!</definedName>
+    <definedName name="kp">'[58]Angebotskalkulation (€)'!#REF!</definedName>
     <definedName name="Kpect1">#REF!</definedName>
     <definedName name="KPP">#REF!</definedName>
-    <definedName name="kpv">[62]kpv!$B$7</definedName>
+    <definedName name="kpv">[61]kpv!$B$7</definedName>
     <definedName name="Kserv">#REF!</definedName>
     <definedName name="KUB">#REF!</definedName>
-    <definedName name="Kurs">[55]Basis_für_Preise_und_Texte!#REF!</definedName>
-    <definedName name="L3_Sub_category_L3">[23]Categories!$A$3:$A$58</definedName>
+    <definedName name="Kurs">[54]Basis_für_Preise_und_Texte!#REF!</definedName>
+    <definedName name="L3_Sub_category_L3">[22]Categories!$A$3:$A$58</definedName>
     <definedName name="labor">#REF!</definedName>
-    <definedName name="lastdate">[27]BasicInfo!$E$10</definedName>
+    <definedName name="lastdate">[26]BasicInfo!$E$10</definedName>
     <definedName name="LD">#REF!</definedName>
-    <definedName name="Level">[27]Companycode!$G$7:$G$14</definedName>
+    <definedName name="Level">[26]Companycode!$G$7:$G$14</definedName>
     <definedName name="Level_discount">#REF!</definedName>
-    <definedName name="LHimp_Bal">'[3]F&amp;F'!#REF!</definedName>
-    <definedName name="linked">[32]Sheet2!#REF!</definedName>
+    <definedName name="LHimp_Bal">'[2]F&amp;F'!#REF!</definedName>
+    <definedName name="linked">[31]Sheet2!#REF!</definedName>
     <definedName name="List_of_Material">#REF!</definedName>
     <definedName name="List1">#REF!</definedName>
     <definedName name="LIST16">#REF!</definedName>
@@ -986,15 +985,15 @@
     <definedName name="LLyr5">#REF!</definedName>
     <definedName name="LLyr6">#REF!</definedName>
     <definedName name="LLyr7">#REF!</definedName>
-    <definedName name="LMD">[63]Reference!$B$2</definedName>
+    <definedName name="LMD">[62]Reference!$B$2</definedName>
     <definedName name="Local_Freight_Insur">#REF!</definedName>
     <definedName name="LOCAL_MYSQL_DATE_FORMAT" localSheetId="0" hidden="1">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
     <definedName name="LOCAL_MYSQL_DATE_FORMAT" hidden="1">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
-    <definedName name="Location">'[64]Name Ranges (DO NOT CHANGE)'!$A$183:$A$199</definedName>
+    <definedName name="Location">'[63]Name Ranges (DO NOT CHANGE)'!$A$183:$A$199</definedName>
     <definedName name="Logistic">#REF!</definedName>
-    <definedName name="lohn">'[59]Angebotskalkulation (€)'!#REF!</definedName>
+    <definedName name="lohn">'[58]Angebotskalkulation (€)'!#REF!</definedName>
     <definedName name="LOW">#REF!</definedName>
-    <definedName name="LowValue">[17]Scenarios!$C$161</definedName>
+    <definedName name="LowValue">[16]Scenarios!$C$161</definedName>
     <definedName name="LPDhw">#REF!</definedName>
     <definedName name="LPDsw">#REF!</definedName>
     <definedName name="LPDucu">#REF!</definedName>
@@ -1068,10 +1067,10 @@
     <definedName name="LUSPSPARE">#REF!</definedName>
     <definedName name="LUSPVM">#REF!</definedName>
     <definedName name="M">#REF!</definedName>
-    <definedName name="M10M5">'[65]Config M20'!#REF!</definedName>
-    <definedName name="M10M5Spares">'[65]Config M20'!#REF!</definedName>
-    <definedName name="M160M40eSpares">'[65]Config M20'!#REF!</definedName>
-    <definedName name="M40Spares">'[65]Config M20'!#REF!</definedName>
+    <definedName name="M10M5">'[64]Config M20'!#REF!</definedName>
+    <definedName name="M10M5Spares">'[64]Config M20'!#REF!</definedName>
+    <definedName name="M160M40eSpares">'[64]Config M20'!#REF!</definedName>
+    <definedName name="M40Spares">'[64]Config M20'!#REF!</definedName>
     <definedName name="Macro113">#N/A</definedName>
     <definedName name="mainpage">#REF!</definedName>
     <definedName name="MAINTENANCE_PR_CO">#REF!</definedName>
@@ -1081,36 +1080,36 @@
     <definedName name="MARKETING98">#REF!</definedName>
     <definedName name="MARKETINGALL">#REF!</definedName>
     <definedName name="MARR">#REF!</definedName>
-    <definedName name="mat_clu_anz">[44]Parameters!$D$174</definedName>
-    <definedName name="mat_equ_anz">[44]Parameters!$D$267</definedName>
-    <definedName name="mat_gd_anz">[44]Parameters!$D$240</definedName>
-    <definedName name="mat_inclan_anz">[44]Parameters!$D$277</definedName>
-    <definedName name="mat_incs_anz">[44]Parameters!$D$180</definedName>
-    <definedName name="mat_lasprnt_anz">[44]Parameters!$D$258</definedName>
-    <definedName name="mat_pcm30_anz">[44]Parameters!$D$297</definedName>
-    <definedName name="mat_protprnt_anz">[44]Parameters!$D$254</definedName>
-    <definedName name="mat_sc_anz">[44]Parameters!$D$233</definedName>
-    <definedName name="mat_scp_anz">[44]Parameters!$D$139</definedName>
-    <definedName name="mat_smp_anz">[44]Parameters!$D$97</definedName>
-    <definedName name="mat_sum_anz">[44]Parameters!$D$229</definedName>
-    <definedName name="mat_voms_50k_anz">[44]Parameters!#REF!</definedName>
-    <definedName name="mat_webc_anz">[44]Parameters!$D$214</definedName>
-    <definedName name="mat_webs_anz">[44]Parameters!$D$208</definedName>
+    <definedName name="mat_clu_anz">[43]Parameters!$D$174</definedName>
+    <definedName name="mat_equ_anz">[43]Parameters!$D$267</definedName>
+    <definedName name="mat_gd_anz">[43]Parameters!$D$240</definedName>
+    <definedName name="mat_inclan_anz">[43]Parameters!$D$277</definedName>
+    <definedName name="mat_incs_anz">[43]Parameters!$D$180</definedName>
+    <definedName name="mat_lasprnt_anz">[43]Parameters!$D$258</definedName>
+    <definedName name="mat_pcm30_anz">[43]Parameters!$D$297</definedName>
+    <definedName name="mat_protprnt_anz">[43]Parameters!$D$254</definedName>
+    <definedName name="mat_sc_anz">[43]Parameters!$D$233</definedName>
+    <definedName name="mat_scp_anz">[43]Parameters!$D$139</definedName>
+    <definedName name="mat_smp_anz">[43]Parameters!$D$97</definedName>
+    <definedName name="mat_sum_anz">[43]Parameters!$D$229</definedName>
+    <definedName name="mat_voms_50k_anz">[43]Parameters!#REF!</definedName>
+    <definedName name="mat_webc_anz">[43]Parameters!$D$214</definedName>
+    <definedName name="mat_webs_anz">[43]Parameters!$D$208</definedName>
     <definedName name="matrix">#REF!</definedName>
-    <definedName name="Max_penetration">[66]Assumptions!$D$12</definedName>
-    <definedName name="Max_Telco_Spend">[66]Assumptions!$D$11</definedName>
-    <definedName name="md5500c">[49]MD5500!$A$15:$M$168</definedName>
+    <definedName name="Max_penetration">[65]Assumptions!$D$12</definedName>
+    <definedName name="Max_Telco_Spend">[65]Assumptions!$D$11</definedName>
+    <definedName name="md5500c">[48]MD5500!$A$15:$M$168</definedName>
     <definedName name="MEH_F">#REF!</definedName>
     <definedName name="MEHR">#REF!</definedName>
     <definedName name="microwave">#REF!</definedName>
-    <definedName name="mildates">'[67]Name Ranges (DO NOT CHANGE)'!#REF!</definedName>
-    <definedName name="Milestone">[27]Companycode!$V$7:$V$13</definedName>
+    <definedName name="mildates">'[66]Name Ranges (DO NOT CHANGE)'!#REF!</definedName>
+    <definedName name="Milestone">[26]Companycode!$V$7:$V$13</definedName>
     <definedName name="Milestone_List">#REF!</definedName>
     <definedName name="Milestones">#REF!</definedName>
-    <definedName name="MinSpend_decrease">[9]Assumptions!#REF!</definedName>
+    <definedName name="MinSpend_decrease">[8]Assumptions!#REF!</definedName>
     <definedName name="MKT">#REF!</definedName>
-    <definedName name="Mkt_churn">[9]Assumptions!#REF!</definedName>
-    <definedName name="MkupCW">[7]Inputs!$C$6</definedName>
+    <definedName name="Mkt_churn">[8]Assumptions!#REF!</definedName>
+    <definedName name="MkupCW">[6]Inputs!$C$6</definedName>
     <definedName name="mocuplift">#REF!</definedName>
     <definedName name="mocyr1">#REF!</definedName>
     <definedName name="mocyr2">#REF!</definedName>
@@ -1119,73 +1118,73 @@
     <definedName name="mocyr5">#REF!</definedName>
     <definedName name="mocyr6">#REF!</definedName>
     <definedName name="mocyr7">#REF!</definedName>
-    <definedName name="Model">'[68]Model Paramter(WL+MW+NE)0313'!$B$4:$B$17</definedName>
-    <definedName name="moderate">[57]change!$C$5</definedName>
+    <definedName name="Model">'[67]Model Paramter(WL+MW+NE)0313'!$B$4:$B$17</definedName>
+    <definedName name="moderate">[56]change!$C$5</definedName>
     <definedName name="MOLoc">#REF!</definedName>
     <definedName name="Montant_Contrat">#REF!</definedName>
-    <definedName name="month">'[34]Name Ranges (DO NOT CHANGE)'!$A$201:$A$212</definedName>
+    <definedName name="month">'[33]Name Ranges (DO NOT CHANGE)'!$A$201:$A$212</definedName>
     <definedName name="monthcount">#REF!</definedName>
     <definedName name="Months">#REF!</definedName>
-    <definedName name="morph1_not_used">[20]Inputs!$C$38,[20]Inputs!$C$44,[20]Inputs!$C$63,[20]Inputs!$C$64,[20]Inputs!$C$65,[20]Inputs!$C$66,[20]Inputs!$C$84,[20]Inputs!$C$91,[20]Inputs!$C$92,[20]Inputs!$C$93,[20]Inputs!$C$114,[20]Inputs!$C$122</definedName>
-    <definedName name="morph1_zeros">[20]Inputs!$G$38:$U$38,[20]Inputs!$G$44:$U$44,[20]Inputs!$G$63:$U$66,[20]Inputs!$G$91:$U$93,[20]Inputs!$G$114:$U$114</definedName>
-    <definedName name="morph2_not_used">[20]Inputs!$C$39,[20]Inputs!$C$45,[20]Inputs!$C$67,[20]Inputs!$C$68,[20]Inputs!$C$69,[20]Inputs!$C$70,[20]Inputs!$C$85,[20]Inputs!$C$94,[20]Inputs!$C$95,[20]Inputs!$C$96,[20]Inputs!$C$115,[20]Inputs!$C$123</definedName>
-    <definedName name="morph2_zeros">[20]Inputs!$G$39:$U$39,[20]Inputs!$G$45:$U$45,[20]Inputs!$G$67:$U$70,[20]Inputs!$G$94:$U$96,[20]Inputs!$G$115:$U$115</definedName>
-    <definedName name="morph3_not_used">[20]Inputs!$C$40,[20]Inputs!$C$46,[20]Inputs!$C$71,[20]Inputs!$C$72,[20]Inputs!$C$73,[20]Inputs!$C$74,[20]Inputs!$C$86,[20]Inputs!$C$97,[20]Inputs!$C$98,[20]Inputs!$C$99,[20]Inputs!$C$116,[20]Inputs!$C$124</definedName>
-    <definedName name="morph3_zeros">[20]Inputs!$G$40:$U$40,[20]Inputs!$G$46:$U$46,[20]Inputs!$G$71:$U$74,[20]Inputs!$G$97:$U$99,[20]Inputs!$G$116:$U$116</definedName>
-    <definedName name="morph4_not_used">[20]Inputs!$C$41,[20]Inputs!$C$47,[20]Inputs!$C$75,[20]Inputs!$C$76,[20]Inputs!$C$77,[20]Inputs!$C$78,[20]Inputs!$C$87,[20]Inputs!$C$100,[20]Inputs!$C$101,[20]Inputs!$C$102,[20]Inputs!$C$117,[20]Inputs!$C$125</definedName>
-    <definedName name="morph4_zeros">[20]Inputs!$G$41:$U$41,[20]Inputs!$G$47:$U$47,[20]Inputs!$G$75:$U$78,[20]Inputs!$G$100:$U$102,[20]Inputs!$G$117:$U$117</definedName>
-    <definedName name="morph5_not_used">[20]Inputs!$C$42,[20]Inputs!$C$48,[20]Inputs!$C$79,[20]Inputs!$C$80,[20]Inputs!$C$81,[20]Inputs!$C$82,[20]Inputs!$C$88,[20]Inputs!$C$103,[20]Inputs!$C$104,[20]Inputs!$C$105,[20]Inputs!$C$118,[20]Inputs!$C$126</definedName>
-    <definedName name="morph5_zeros">[20]Inputs!$G$42:$U$42,[20]Inputs!$G$48:$U$48,[20]Inputs!$G$79:$U$82,[20]Inputs!$G$103:$U$105,[20]Inputs!$G$118:$U$118</definedName>
-    <definedName name="mpl">'[69]Master Price List'!$A$8:$M$87</definedName>
-    <definedName name="Ms">'[18]Total GSM  Market'!#REF!</definedName>
+    <definedName name="morph1_not_used">[19]Inputs!$C$38,[19]Inputs!$C$44,[19]Inputs!$C$63,[19]Inputs!$C$64,[19]Inputs!$C$65,[19]Inputs!$C$66,[19]Inputs!$C$84,[19]Inputs!$C$91,[19]Inputs!$C$92,[19]Inputs!$C$93,[19]Inputs!$C$114,[19]Inputs!$C$122</definedName>
+    <definedName name="morph1_zeros">[19]Inputs!$G$38:$U$38,[19]Inputs!$G$44:$U$44,[19]Inputs!$G$63:$U$66,[19]Inputs!$G$91:$U$93,[19]Inputs!$G$114:$U$114</definedName>
+    <definedName name="morph2_not_used">[19]Inputs!$C$39,[19]Inputs!$C$45,[19]Inputs!$C$67,[19]Inputs!$C$68,[19]Inputs!$C$69,[19]Inputs!$C$70,[19]Inputs!$C$85,[19]Inputs!$C$94,[19]Inputs!$C$95,[19]Inputs!$C$96,[19]Inputs!$C$115,[19]Inputs!$C$123</definedName>
+    <definedName name="morph2_zeros">[19]Inputs!$G$39:$U$39,[19]Inputs!$G$45:$U$45,[19]Inputs!$G$67:$U$70,[19]Inputs!$G$94:$U$96,[19]Inputs!$G$115:$U$115</definedName>
+    <definedName name="morph3_not_used">[19]Inputs!$C$40,[19]Inputs!$C$46,[19]Inputs!$C$71,[19]Inputs!$C$72,[19]Inputs!$C$73,[19]Inputs!$C$74,[19]Inputs!$C$86,[19]Inputs!$C$97,[19]Inputs!$C$98,[19]Inputs!$C$99,[19]Inputs!$C$116,[19]Inputs!$C$124</definedName>
+    <definedName name="morph3_zeros">[19]Inputs!$G$40:$U$40,[19]Inputs!$G$46:$U$46,[19]Inputs!$G$71:$U$74,[19]Inputs!$G$97:$U$99,[19]Inputs!$G$116:$U$116</definedName>
+    <definedName name="morph4_not_used">[19]Inputs!$C$41,[19]Inputs!$C$47,[19]Inputs!$C$75,[19]Inputs!$C$76,[19]Inputs!$C$77,[19]Inputs!$C$78,[19]Inputs!$C$87,[19]Inputs!$C$100,[19]Inputs!$C$101,[19]Inputs!$C$102,[19]Inputs!$C$117,[19]Inputs!$C$125</definedName>
+    <definedName name="morph4_zeros">[19]Inputs!$G$41:$U$41,[19]Inputs!$G$47:$U$47,[19]Inputs!$G$75:$U$78,[19]Inputs!$G$100:$U$102,[19]Inputs!$G$117:$U$117</definedName>
+    <definedName name="morph5_not_used">[19]Inputs!$C$42,[19]Inputs!$C$48,[19]Inputs!$C$79,[19]Inputs!$C$80,[19]Inputs!$C$81,[19]Inputs!$C$82,[19]Inputs!$C$88,[19]Inputs!$C$103,[19]Inputs!$C$104,[19]Inputs!$C$105,[19]Inputs!$C$118,[19]Inputs!$C$126</definedName>
+    <definedName name="morph5_zeros">[19]Inputs!$G$42:$U$42,[19]Inputs!$G$48:$U$48,[19]Inputs!$G$79:$U$82,[19]Inputs!$G$103:$U$105,[19]Inputs!$G$118:$U$118</definedName>
+    <definedName name="mpl">'[68]Master Price List'!$A$8:$M$87</definedName>
+    <definedName name="Ms">'[17]Total GSM  Market'!#REF!</definedName>
     <definedName name="msc">#REF!</definedName>
-    <definedName name="MUCIT">[16]Entry!$H$28</definedName>
-    <definedName name="MUCITE10">[16]Entry!$H$29</definedName>
-    <definedName name="MultiUnit">[27]Companycode!$T$7:$T$14</definedName>
-    <definedName name="MUSEL">[16]Entry!$H$30</definedName>
-    <definedName name="MUTEL">[16]Entry!$H$31</definedName>
-    <definedName name="MYR">[6]graphs!$W$6</definedName>
+    <definedName name="MUCIT">[15]Entry!$H$28</definedName>
+    <definedName name="MUCITE10">[15]Entry!$H$29</definedName>
+    <definedName name="MultiUnit">[26]Companycode!$T$7:$T$14</definedName>
+    <definedName name="MUSEL">[15]Entry!$H$30</definedName>
+    <definedName name="MUTEL">[15]Entry!$H$31</definedName>
+    <definedName name="MYR">[5]graphs!$W$6</definedName>
     <definedName name="N">#REF!</definedName>
-    <definedName name="nachk">'[59]Angebotskalkulation (€)'!#REF!</definedName>
-    <definedName name="naswenas">[10]Input!#REF!</definedName>
+    <definedName name="nachk">'[58]Angebotskalkulation (€)'!#REF!</definedName>
+    <definedName name="naswenas">[9]Input!#REF!</definedName>
     <definedName name="NAUTICA_SERIES">#REF!</definedName>
     <definedName name="nb_jours">#REF!</definedName>
     <definedName name="nb_links">#REF!</definedName>
     <definedName name="nb_links2">#REF!</definedName>
-    <definedName name="nb_trx">[70]Reference!#REF!</definedName>
-    <definedName name="nb8trx">[70]Reference!#REF!</definedName>
-    <definedName name="NBILCIT100">[16]FIXDATA!$C$18</definedName>
-    <definedName name="NBILSEL100">[16]FIXDATA!$C$28</definedName>
+    <definedName name="nb_trx">[69]Reference!#REF!</definedName>
+    <definedName name="nb8trx">[69]Reference!#REF!</definedName>
+    <definedName name="NBILCIT100">[15]FIXDATA!$C$18</definedName>
+    <definedName name="NBILSEL100">[15]FIXDATA!$C$28</definedName>
     <definedName name="Nego_Marge">#REF!</definedName>
     <definedName name="NETWORK_MANAGEMENT_CONSOLE_AND_SOFTWARE_PRODUCTS">#REF!</definedName>
     <definedName name="ngukaoslgkcusht" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
     <definedName name="ngukaoslgkcusht" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
-    <definedName name="NINCIT100">[16]FIXDATA!$C$20</definedName>
-    <definedName name="NINSEL100">[16]FIXDATA!$C$30</definedName>
+    <definedName name="NINCIT100">[15]FIXDATA!$C$20</definedName>
+    <definedName name="NINSEL100">[15]FIXDATA!$C$30</definedName>
     <definedName name="nn" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"Sensitivity"}</definedName>
     <definedName name="nn" hidden="1">{#N/A,#N/A,FALSE,"Sensitivity"}</definedName>
-    <definedName name="No">'[18]Total GSM  Market'!#REF!</definedName>
+    <definedName name="No">'[17]Total GSM  Market'!#REF!</definedName>
     <definedName name="NoBSC">#REF!</definedName>
     <definedName name="NoBTS">#REF!</definedName>
     <definedName name="NoBTS_Site">#REF!</definedName>
-    <definedName name="Noc">'[18]Total GSM  Market'!#REF!</definedName>
-    <definedName name="nom_for_ih_indic">[71]Training!$H$238</definedName>
+    <definedName name="Noc">'[17]Total GSM  Market'!#REF!</definedName>
+    <definedName name="nom_for_ih_indic">[70]Training!$H$238</definedName>
     <definedName name="none">#REF!</definedName>
-    <definedName name="NotActive">[17]Scenarios!$C$163</definedName>
-    <definedName name="NotIncluded">[17]Scenarios!$C$167</definedName>
-    <definedName name="NOUVCIT">[16]Entry!$A$28</definedName>
-    <definedName name="NOUVCITE10">[16]Entry!$A$29</definedName>
-    <definedName name="NOUVOT">[16]Entry!$A$32</definedName>
-    <definedName name="NOUVSEL">[16]Entry!$A$30</definedName>
-    <definedName name="NOUVTEL">[16]Entry!$A$31</definedName>
-    <definedName name="NRCIT100">[16]FIXDATA!$C$16</definedName>
-    <definedName name="NRSEL100">[16]FIXDATA!$C$26</definedName>
+    <definedName name="NotActive">[16]Scenarios!$C$163</definedName>
+    <definedName name="NotIncluded">[16]Scenarios!$C$167</definedName>
+    <definedName name="NOUVCIT">[15]Entry!$A$28</definedName>
+    <definedName name="NOUVCITE10">[15]Entry!$A$29</definedName>
+    <definedName name="NOUVOT">[15]Entry!$A$32</definedName>
+    <definedName name="NOUVSEL">[15]Entry!$A$30</definedName>
+    <definedName name="NOUVTEL">[15]Entry!$A$31</definedName>
+    <definedName name="NRCIT100">[15]FIXDATA!$C$16</definedName>
+    <definedName name="NRSEL100">[15]FIXDATA!$C$26</definedName>
     <definedName name="NRYRTU1">#REF!</definedName>
     <definedName name="NRYRTU2">#REF!</definedName>
-    <definedName name="NSCIT100">[16]FIXDATA!$C$14</definedName>
+    <definedName name="NSCIT100">[15]FIXDATA!$C$14</definedName>
     <definedName name="NSSCAT1">#REF!</definedName>
     <definedName name="NSSCAT2">#REF!</definedName>
-    <definedName name="NSSEL100">[16]FIXDATA!$C$24</definedName>
+    <definedName name="NSSEL100">[15]FIXDATA!$C$24</definedName>
     <definedName name="NT2COEFCIT">#REF!</definedName>
     <definedName name="NT2COEFSEL">#REF!</definedName>
     <definedName name="NT2COSTCIT">#REF!</definedName>
@@ -1198,7 +1197,7 @@
     <definedName name="NTCOSTSEL">#REF!</definedName>
     <definedName name="NTPRICECIT">#REF!</definedName>
     <definedName name="NTPRICESEL">#REF!</definedName>
-    <definedName name="NUMOF">[16]Entry!$F$23</definedName>
+    <definedName name="NUMOF">[15]Entry!$F$23</definedName>
     <definedName name="NW">#REF!</definedName>
     <definedName name="NWS400E60_BAS_jbx_anz">#REF!</definedName>
     <definedName name="NWS400E60_BAS_mhd1">#REF!</definedName>
@@ -1211,9 +1210,9 @@
     <definedName name="OASCU_MOC">#REF!</definedName>
     <definedName name="odc">#REF!</definedName>
     <definedName name="odp">#REF!</definedName>
-    <definedName name="OE_Bal">'[3]F&amp;F'!#REF!</definedName>
-    <definedName name="Off">[72]Config!$C$3:$C$8</definedName>
-    <definedName name="OFOUCONT">[16]VARDATA!$C$33</definedName>
+    <definedName name="OE_Bal">'[2]F&amp;F'!#REF!</definedName>
+    <definedName name="Off">[71]Config!$C$3:$C$8</definedName>
+    <definedName name="OFOUCONT">[15]VARDATA!$C$33</definedName>
     <definedName name="OOOOOO">#REF!</definedName>
     <definedName name="OOOOOOOOO">#REF!</definedName>
     <definedName name="OOOOOOOOOOOO">#REF!</definedName>
@@ -1231,37 +1230,37 @@
     <definedName name="optional_otherservices">#REF!</definedName>
     <definedName name="optional_third">#REF!</definedName>
     <definedName name="optional_transmission">#REF!</definedName>
-    <definedName name="ORACLE7">[73]ORACLE7!$E$4:$J$44</definedName>
+    <definedName name="ORACLE7">[72]ORACLE7!$E$4:$J$44</definedName>
     <definedName name="ORIGEM">#REF!</definedName>
-    <definedName name="Other">[74]catalog2!$B$4:$P$1286</definedName>
+    <definedName name="Other">[73]catalog2!$B$4:$P$1286</definedName>
     <definedName name="otherproducts">#REF!</definedName>
     <definedName name="otherservices">#REF!</definedName>
-    <definedName name="Over_65">[66]Data!$C$23</definedName>
-    <definedName name="overview">[33]overview!$B$6:$GV$161</definedName>
+    <definedName name="Over_65">[65]Data!$C$23</definedName>
+    <definedName name="overview">[32]overview!$B$6:$GV$161</definedName>
     <definedName name="P">#REF!</definedName>
     <definedName name="P_F">#REF!</definedName>
     <definedName name="p_margin_b">#REF!</definedName>
     <definedName name="p_margin_m">#REF!</definedName>
     <definedName name="p_margin_n">#REF!</definedName>
     <definedName name="Patch">#REF!</definedName>
-    <definedName name="Pc">'[18]Total GSM  Market'!#REF!</definedName>
-    <definedName name="PCoef">[75]Tables!$B$6</definedName>
-    <definedName name="PCURCIT">[16]Entry!$D$28</definedName>
-    <definedName name="PCURCITE10">[16]Entry!$D$29</definedName>
-    <definedName name="PCUROT">[16]Entry!$D$32</definedName>
-    <definedName name="PCURSEL">[16]Entry!$D$30</definedName>
-    <definedName name="PCURTEL">[16]Entry!$D$31</definedName>
-    <definedName name="PEInterfaces">'[65]Config M20'!#REF!</definedName>
+    <definedName name="Pc">'[17]Total GSM  Market'!#REF!</definedName>
+    <definedName name="PCoef">[74]Tables!$B$6</definedName>
+    <definedName name="PCURCIT">[15]Entry!$D$28</definedName>
+    <definedName name="PCURCITE10">[15]Entry!$D$29</definedName>
+    <definedName name="PCUROT">[15]Entry!$D$32</definedName>
+    <definedName name="PCURSEL">[15]Entry!$D$30</definedName>
+    <definedName name="PCURTEL">[15]Entry!$D$31</definedName>
+    <definedName name="PEInterfaces">'[64]Config M20'!#REF!</definedName>
     <definedName name="PENRIL">#REF!</definedName>
-    <definedName name="PERC_CH">[33]datastream!$B$250:$S$449</definedName>
-    <definedName name="Period">[27]Companycode!$P$7:$P$10</definedName>
+    <definedName name="PERC_CH">[32]datastream!$B$250:$S$449</definedName>
+    <definedName name="Period">[26]Companycode!$P$7:$P$10</definedName>
     <definedName name="PHASE61" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
     <definedName name="PHASE61" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
     <definedName name="pi" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
     <definedName name="pi" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
-    <definedName name="pippo">[30]Planner!#REF!</definedName>
-    <definedName name="pippo1">[30]Planner!#REF!</definedName>
-    <definedName name="pippo2">[30]Planner!#REF!</definedName>
+    <definedName name="pippo">[29]Planner!#REF!</definedName>
+    <definedName name="pippo1">[29]Planner!#REF!</definedName>
+    <definedName name="pippo2">[29]Planner!#REF!</definedName>
     <definedName name="PIS">#REF!</definedName>
     <definedName name="PM">#REF!</definedName>
     <definedName name="PNRS_1">#REF!</definedName>
@@ -1269,16 +1268,16 @@
     <definedName name="PNRS_3">#REF!</definedName>
     <definedName name="PNRS_4">#REF!</definedName>
     <definedName name="PNRS_5">#REF!</definedName>
-    <definedName name="PopCache_PA_FP_WEBADI_UPLOAD_INF_DELETE_FLAG" hidden="1">[76]PopCache!$A$1:$A$2</definedName>
+    <definedName name="PopCache_PA_FP_WEBADI_UPLOAD_INF_DELETE_FLAG" hidden="1">[75]PopCache!$A$1:$A$2</definedName>
     <definedName name="POT_F">#REF!</definedName>
     <definedName name="POTR">#REF!</definedName>
     <definedName name="power_supply">#REF!</definedName>
-    <definedName name="ppfee">'[77]TY01 CPFF'!$I$339</definedName>
+    <definedName name="ppfee">'[76]TY01 CPFF'!$I$339</definedName>
     <definedName name="PPPPPPPP">#REF!</definedName>
     <definedName name="PPPPPPPPPPPPP">#REF!</definedName>
     <definedName name="PPPPPPPPPPPPPPP">#REF!</definedName>
     <definedName name="PPPPPPPPPPPPPPPP">#REF!</definedName>
-    <definedName name="PPPPPPPPPPPPPPPPPPPPPP">[30]Planner!#REF!</definedName>
+    <definedName name="PPPPPPPPPPPPPPPPPPPPPP">[29]Planner!#REF!</definedName>
     <definedName name="PPPPPPPPPPPPPPPPPPPPPPPPP">#REF!</definedName>
     <definedName name="PPPPPPPPPPPPPPPPPPPPPPPPPPPPPPPPPPPPP">#REF!</definedName>
     <definedName name="PPPPPPPPPPPPPPPPPPPPPPPPPPPPPPPPPPPPPP">#REF!</definedName>
@@ -1288,15 +1287,15 @@
     <definedName name="price_factor">#REF!</definedName>
     <definedName name="Price_OP">#REF!</definedName>
     <definedName name="Price_PK">#REF!</definedName>
-    <definedName name="PriceBook">'[78]Price book '!$A$3:$AF$256</definedName>
+    <definedName name="PriceBook">'[77]Price book '!$A$3:$AF$256</definedName>
     <definedName name="pricechanges">#REF!</definedName>
-    <definedName name="PriceListAP">[79]PriceListAP!$A$2:$I$648</definedName>
+    <definedName name="PriceListAP">[78]PriceListAP!$A$2:$I$648</definedName>
     <definedName name="print__Area">#REF!</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="print_ares">#REF!</definedName>
     <definedName name="Print_Terms_Tatene">"Text 2"</definedName>
     <definedName name="Print_Titles_MI">#REF!</definedName>
-    <definedName name="PrjType">[27]Companycode!$H$7:$H$8</definedName>
+    <definedName name="PrjType">[26]Companycode!$H$7:$H$8</definedName>
     <definedName name="PROD1">#REF!</definedName>
     <definedName name="PROD10">#REF!</definedName>
     <definedName name="PROD2">#REF!</definedName>
@@ -1325,24 +1324,24 @@
     <definedName name="PROFITALL">#REF!</definedName>
     <definedName name="PROJECT">#REF!</definedName>
     <definedName name="PROJETO">#REF!</definedName>
-    <definedName name="PROJTIT">[16]Entry!$F$22</definedName>
+    <definedName name="PROJTIT">[15]Entry!$F$22</definedName>
     <definedName name="PROPOSAL">#REF!</definedName>
     <definedName name="PS_Faktor">#REF!</definedName>
-    <definedName name="PurchaseLand">[27]Companycode!$O$7:$O$8</definedName>
+    <definedName name="PurchaseLand">[26]Companycode!$O$7:$O$8</definedName>
     <definedName name="PWD">"happyworking"</definedName>
     <definedName name="Pwrdetial">#REF!</definedName>
     <definedName name="Q">#REF!</definedName>
-    <definedName name="Qc">'[18]Total GSM  Market'!#REF!</definedName>
-    <definedName name="QF_SYS_CURRENCY1">[80]Parameters!$E$34</definedName>
-    <definedName name="QF_SYS_EXCHANGE">[81]Parameters!$B$81</definedName>
-    <definedName name="QF_SYS_NOT_TRADE_DESC1">[82]Parameters!$J$15</definedName>
-    <definedName name="QF_SYS_QUOTATION_NO">[82]Parameters!$E$13</definedName>
-    <definedName name="QF_SYS_QUOTATION_PONUMBER">[82]Parameters!$E$15</definedName>
-    <definedName name="QF_SYS_ROUNDUP_DECIMAL">[81]Parameters!$B$95</definedName>
+    <definedName name="Qc">'[17]Total GSM  Market'!#REF!</definedName>
+    <definedName name="QF_SYS_CURRENCY1">[79]Parameters!$E$34</definedName>
+    <definedName name="QF_SYS_EXCHANGE">[80]Parameters!$B$81</definedName>
+    <definedName name="QF_SYS_NOT_TRADE_DESC1">[81]Parameters!$J$15</definedName>
+    <definedName name="QF_SYS_QUOTATION_NO">[81]Parameters!$E$13</definedName>
+    <definedName name="QF_SYS_QUOTATION_PONUMBER">[81]Parameters!$E$15</definedName>
+    <definedName name="QF_SYS_ROUNDUP_DECIMAL">[80]Parameters!$B$95</definedName>
     <definedName name="QF_SYS_SERVICE_ONLY">0</definedName>
-    <definedName name="QF_SYS_SPDISCOUNT">[81]Parameters!$B$83</definedName>
-    <definedName name="QF_SYS_TRADE_DESC1">[82]Parameters!$J$14</definedName>
-    <definedName name="QF_SYS_USED_CONTRACT_PRICE">[81]Parameters!$B$98</definedName>
+    <definedName name="QF_SYS_SPDISCOUNT">[80]Parameters!$B$83</definedName>
+    <definedName name="QF_SYS_TRADE_DESC1">[81]Parameters!$J$14</definedName>
+    <definedName name="QF_SYS_USED_CONTRACT_PRICE">[80]Parameters!$B$98</definedName>
     <definedName name="QFLAG_00002_EQUIPMENT_2_TOTALDISCOUNTPRICE">#REF!</definedName>
     <definedName name="QFLAG_00002_EQUIPMENT_2_TOTALLISTPRICE">#REF!</definedName>
     <definedName name="QFLAG_00002_EQUIPMENT_2_TOTALLOCALPRICE">#REF!</definedName>
@@ -1381,24 +1380,24 @@
     <definedName name="Rack23_Title">#REF!</definedName>
     <definedName name="Rack42_Title">#REF!</definedName>
     <definedName name="range">#REF!</definedName>
-    <definedName name="range_cfo">[37]cfoa51!$A:$IV</definedName>
-    <definedName name="RangeTargia">'[25]parametri di programmazione'!$B$9</definedName>
+    <definedName name="range_cfo">[36]cfoa51!$A:$IV</definedName>
+    <definedName name="RangeTargia">'[24]parametri di programmazione'!$B$9</definedName>
     <definedName name="rate">#REF!</definedName>
     <definedName name="rect">#REF!</definedName>
-    <definedName name="RECTOT">[35]MAIPLH!#REF!</definedName>
+    <definedName name="RECTOT">[34]MAIPLH!#REF!</definedName>
     <definedName name="REF">#REF!</definedName>
-    <definedName name="refno">'[22]Network assumptions'!$D$4</definedName>
-    <definedName name="Region">[27]Companycode!$AH$6:$DD$6</definedName>
-    <definedName name="Remark">[44]Definitions!$B$364</definedName>
-    <definedName name="Remark1">[44]Definitions!$B$366</definedName>
-    <definedName name="Remark2">[44]Definitions!$B$367</definedName>
-    <definedName name="Remark3">[44]Definitions!$B$368</definedName>
+    <definedName name="refno">'[21]Network assumptions'!$D$4</definedName>
+    <definedName name="Region">[26]Companycode!$AH$6:$DD$6</definedName>
+    <definedName name="Remark">[43]Definitions!$B$364</definedName>
+    <definedName name="Remark1">[43]Definitions!$B$366</definedName>
+    <definedName name="Remark2">[43]Definitions!$B$367</definedName>
+    <definedName name="Remark3">[43]Definitions!$B$368</definedName>
     <definedName name="REMOTE_ANNEX_SERIES">#REF!</definedName>
-    <definedName name="Remote_Inv">[26]Input!#REF!</definedName>
-    <definedName name="Represent">[27]Companycode!$AG$8:$AG$56</definedName>
-    <definedName name="Resource">'[39]Name Ranges (DO NOT CHANGE)'!$A$134:$A$180</definedName>
-    <definedName name="resourceid">'[39]Name Ranges (DO NOT CHANGE)'!$A$133:$C$180</definedName>
-    <definedName name="Revenue_interconnect">[83]Data!$C$24</definedName>
+    <definedName name="Remote_Inv">[25]Input!#REF!</definedName>
+    <definedName name="Represent">[26]Companycode!$AG$8:$AG$56</definedName>
+    <definedName name="Resource">'[38]Name Ranges (DO NOT CHANGE)'!$A$134:$A$180</definedName>
+    <definedName name="resourceid">'[38]Name Ranges (DO NOT CHANGE)'!$A$133:$C$180</definedName>
+    <definedName name="Revenue_interconnect">[82]Data!$C$24</definedName>
     <definedName name="revenuetype">#REF!</definedName>
     <definedName name="revyear1">#REF!</definedName>
     <definedName name="revyear2">#REF!</definedName>
@@ -1409,17 +1408,17 @@
     <definedName name="revyear7">#REF!</definedName>
     <definedName name="rew">#REF!</definedName>
     <definedName name="REWRE">#REF!</definedName>
-    <definedName name="RFBSS">[15]FCOC!$G$14,[15]FCOC!$G$16,[15]FCOC!$G$20,[15]FCOC!$G$23:$G$25,[15]FCOC!$G$27,[15]FCOC!$G$29,[15]FCOC!$G$31:$G$34,[15]FCOC!$G$36,[15]FCOC!$G$38:$G$47,[15]FCOC!$G$51,[15]FCOC!$G$54:$G$56,[15]FCOC!$G$58,[15]FCOC!$G$62:$G$63</definedName>
-    <definedName name="RFMW">[15]FCOC!$M$14,[15]FCOC!$M$16,[15]FCOC!$M$20,[15]FCOC!$M$23:$M$25,[15]FCOC!$M$27,[15]FCOC!$M$29,[15]FCOC!$M$31:$M$34,[15]FCOC!$M$36,[15]FCOC!$M$38:$M$47,[15]FCOC!$M$51,[15]FCOC!$M$54:$M$56,[15]FCOC!$M$58,[15]FCOC!$M$62:$M$63</definedName>
-    <definedName name="RFNCIT">[15]FCOC!$I$14,[15]FCOC!$I$16,[15]FCOC!$I$20,[15]FCOC!$I$23:$I$25,[15]FCOC!$I$27,[15]FCOC!$I$29,[15]FCOC!$I$31:$I$34,[15]FCOC!$I$36,[15]FCOC!$I$38:$I$47,[15]FCOC!$I$51,[15]FCOC!$I$54:$I$56,[15]FCOC!$I$58,[15]FCOC!$I$62:$I$63</definedName>
-    <definedName name="RFNSEL">[15]FCOC!$K$14,[15]FCOC!$K$16,[15]FCOC!$K$20,[15]FCOC!$K$23:$K$25,[15]FCOC!$K$27,[15]FCOC!$K$29,[15]FCOC!$K$31:$K$34,[15]FCOC!$K$36,[15]FCOC!$K$38:$K$47,[15]FCOC!$K$51,[15]FCOC!$K$54:$K$56,[15]FCOC!$K$58,[15]FCOC!$K$62:$K$63</definedName>
-    <definedName name="RFOT">[15]FCOC!$O$14,[15]FCOC!$O$16,[15]FCOC!$O$20,[15]FCOC!$O$23:$O$25,[15]FCOC!$O$27,[15]FCOC!$O$29,[15]FCOC!$O$31:$O$34,[15]FCOC!$O$36,[15]FCOC!$O$38:$O$47,[15]FCOC!$O$51,[15]FCOC!$O$54:$O$56,[15]FCOC!$O$58,[15]FCOC!$O$62:$O$63</definedName>
-    <definedName name="RNC_limit_per_OMC">'[20]Equip Dim'!$C$241</definedName>
+    <definedName name="RFBSS">[14]FCOC!$G$14,[14]FCOC!$G$16,[14]FCOC!$G$20,[14]FCOC!$G$23:$G$25,[14]FCOC!$G$27,[14]FCOC!$G$29,[14]FCOC!$G$31:$G$34,[14]FCOC!$G$36,[14]FCOC!$G$38:$G$47,[14]FCOC!$G$51,[14]FCOC!$G$54:$G$56,[14]FCOC!$G$58,[14]FCOC!$G$62:$G$63</definedName>
+    <definedName name="RFMW">[14]FCOC!$M$14,[14]FCOC!$M$16,[14]FCOC!$M$20,[14]FCOC!$M$23:$M$25,[14]FCOC!$M$27,[14]FCOC!$M$29,[14]FCOC!$M$31:$M$34,[14]FCOC!$M$36,[14]FCOC!$M$38:$M$47,[14]FCOC!$M$51,[14]FCOC!$M$54:$M$56,[14]FCOC!$M$58,[14]FCOC!$M$62:$M$63</definedName>
+    <definedName name="RFNCIT">[14]FCOC!$I$14,[14]FCOC!$I$16,[14]FCOC!$I$20,[14]FCOC!$I$23:$I$25,[14]FCOC!$I$27,[14]FCOC!$I$29,[14]FCOC!$I$31:$I$34,[14]FCOC!$I$36,[14]FCOC!$I$38:$I$47,[14]FCOC!$I$51,[14]FCOC!$I$54:$I$56,[14]FCOC!$I$58,[14]FCOC!$I$62:$I$63</definedName>
+    <definedName name="RFNSEL">[14]FCOC!$K$14,[14]FCOC!$K$16,[14]FCOC!$K$20,[14]FCOC!$K$23:$K$25,[14]FCOC!$K$27,[14]FCOC!$K$29,[14]FCOC!$K$31:$K$34,[14]FCOC!$K$36,[14]FCOC!$K$38:$K$47,[14]FCOC!$K$51,[14]FCOC!$K$54:$K$56,[14]FCOC!$K$58,[14]FCOC!$K$62:$K$63</definedName>
+    <definedName name="RFOT">[14]FCOC!$O$14,[14]FCOC!$O$16,[14]FCOC!$O$20,[14]FCOC!$O$23:$O$25,[14]FCOC!$O$27,[14]FCOC!$O$29,[14]FCOC!$O$31:$O$34,[14]FCOC!$O$36,[14]FCOC!$O$38:$O$47,[14]FCOC!$O$51,[14]FCOC!$O$54:$O$56,[14]FCOC!$O$58,[14]FCOC!$O$62:$O$63</definedName>
+    <definedName name="RNC_limit_per_OMC">'[19]Equip Dim'!$C$241</definedName>
     <definedName name="Rollout" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
     <definedName name="Rollout" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
-    <definedName name="Runden">[53]Factors!$A$16</definedName>
+    <definedName name="Runden">[52]Factors!$A$16</definedName>
     <definedName name="S">#REF!</definedName>
-    <definedName name="Sale">'[12]Input Table'!#REF!</definedName>
+    <definedName name="Sale">'[11]Input Table'!#REF!</definedName>
     <definedName name="sas" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"Profit &amp; Loss statement"}</definedName>
     <definedName name="sas" hidden="1">{#N/A,#N/A,FALSE,"Profit &amp; Loss statement"}</definedName>
     <definedName name="sce">#REF!</definedName>
@@ -1445,12 +1444,12 @@
     <definedName name="SCPE60_8P_ss7">#REF!</definedName>
     <definedName name="sd">#REF!</definedName>
     <definedName name="SDDDDDDDDDDDD">#REF!</definedName>
-    <definedName name="search_rel2.2">'[73]IN Platforms Details'!$D$3:$I$2413</definedName>
-    <definedName name="search_ss7">'[73]SS7 Details New pricing'!$D$1:$I$852</definedName>
+    <definedName name="search_rel2.2">'[72]IN Platforms Details'!$D$3:$I$2413</definedName>
+    <definedName name="search_ss7">'[72]SS7 Details New pricing'!$D$1:$I$852</definedName>
     <definedName name="sect">#REF!</definedName>
     <definedName name="Select_Product">#REF!</definedName>
-    <definedName name="SelectedComp">[27]BasicInfo!$E$18:$E$23</definedName>
-    <definedName name="SelectedPdt">[27]Companycode!$AF$6:$AF$7</definedName>
+    <definedName name="SelectedComp">[26]BasicInfo!$E$18:$E$23</definedName>
+    <definedName name="SelectedPdt">[26]Companycode!$AF$6:$AF$7</definedName>
     <definedName name="Sens" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"Sensitivity"}</definedName>
     <definedName name="Sens" hidden="1">{#N/A,#N/A,FALSE,"Sensitivity"}</definedName>
     <definedName name="serge">#REF!</definedName>
@@ -1471,8 +1470,8 @@
     <definedName name="servicesrevyr5">#REF!</definedName>
     <definedName name="servicesrevyr6">#REF!</definedName>
     <definedName name="servicesrevyr7">#REF!</definedName>
-    <definedName name="ServiceType">[27]Companycode!$W$7:$W$27</definedName>
-    <definedName name="SGD">[6]graphs!$S$6</definedName>
+    <definedName name="ServiceType">[26]Companycode!$W$7:$W$27</definedName>
+    <definedName name="SGD">[5]graphs!$S$6</definedName>
     <definedName name="sgptotal_feeder">#REF!</definedName>
     <definedName name="sing">#REF!</definedName>
     <definedName name="sitenumber">#REF!</definedName>
@@ -1490,9 +1489,9 @@
     <definedName name="softwarerevyr5">#REF!</definedName>
     <definedName name="softwarerevyr6">#REF!</definedName>
     <definedName name="softwarerevyr7">#REF!</definedName>
-    <definedName name="Sous_Total_Bati">[84]Configurations!#REF!</definedName>
+    <definedName name="Sous_Total_Bati">[83]Configurations!#REF!</definedName>
     <definedName name="South">#REF!</definedName>
-    <definedName name="sow">'[67]Name Ranges (DO NOT CHANGE)'!#REF!</definedName>
+    <definedName name="sow">'[66]Name Ranges (DO NOT CHANGE)'!#REF!</definedName>
     <definedName name="SP" localSheetId="0" hidden="1">{"COST",#N/A,FALSE,"SYNTHESE";"MARGIN",#N/A,FALSE,"SYNTHESE";"LOT_COM",#N/A,FALSE,"SYNTHESE"}</definedName>
     <definedName name="SP" hidden="1">{"COST",#N/A,FALSE,"SYNTHESE";"MARGIN",#N/A,FALSE,"SYNTHESE";"LOT_COM",#N/A,FALSE,"SYNTHESE"}</definedName>
     <definedName name="spanne">#REF!</definedName>
@@ -1500,10 +1499,10 @@
     <definedName name="SPBIL2">#REF!</definedName>
     <definedName name="SPECHO1">#REF!</definedName>
     <definedName name="SPECHO2">#REF!</definedName>
-    <definedName name="Special1">[44]Definitions!$B$376</definedName>
-    <definedName name="Special2">[44]Definitions!$B$377</definedName>
-    <definedName name="Special6">[44]Definitions!$B$381</definedName>
-    <definedName name="Speech_kbps">[20]Defaults!$G$5</definedName>
+    <definedName name="Special1">[43]Definitions!$B$376</definedName>
+    <definedName name="Special2">[43]Definitions!$B$377</definedName>
+    <definedName name="Special6">[43]Definitions!$B$381</definedName>
+    <definedName name="Speech_kbps">[19]Defaults!$G$5</definedName>
     <definedName name="SPEIR1">#REF!</definedName>
     <definedName name="SPEIR2">#REF!</definedName>
     <definedName name="SPENVE1">#REF!</definedName>
@@ -1564,82 +1563,82 @@
     <definedName name="SPTVASSEL">#REF!</definedName>
     <definedName name="SPVM1">#REF!</definedName>
     <definedName name="SPVM2">#REF!</definedName>
-    <definedName name="SSC_price_percentage">[85]Parameters!$B$5</definedName>
+    <definedName name="SSC_price_percentage">[84]Parameters!$B$5</definedName>
     <definedName name="staffing">#REF!</definedName>
-    <definedName name="stand_desc">'[86]Project Data'!$B$1:$B$65536</definedName>
+    <definedName name="stand_desc">'[85]Project Data'!$B$1:$B$65536</definedName>
     <definedName name="Stand_Faktor">#REF!</definedName>
     <definedName name="START">#REF!</definedName>
-    <definedName name="startdate">[27]BasicInfo!$C$10</definedName>
+    <definedName name="startdate">[26]BasicInfo!$C$10</definedName>
     <definedName name="Status">#REF!</definedName>
-    <definedName name="STM1_Cap">'[20]Link Dim'!$C$36</definedName>
+    <definedName name="STM1_Cap">'[19]Link Dim'!$C$36</definedName>
     <definedName name="Storage">#REF!</definedName>
     <definedName name="Stück">#REF!</definedName>
     <definedName name="SUBNR1">#REF!</definedName>
     <definedName name="SUBNR2">#REF!</definedName>
-    <definedName name="Sum">[87]Products!$K$6</definedName>
-    <definedName name="SUPNSS">[16]VARDATA!$C$6</definedName>
-    <definedName name="SVC">'[12]Input Table'!$B$24</definedName>
-    <definedName name="SW__Eigenbezug_Faktor_auf_OP">[55]Basis_für_Preise_und_Texte!#REF!</definedName>
+    <definedName name="Sum">[86]Products!$K$6</definedName>
+    <definedName name="SUPNSS">[15]VARDATA!$C$6</definedName>
+    <definedName name="SVC">'[11]Input Table'!$B$24</definedName>
+    <definedName name="SW__Eigenbezug_Faktor_auf_OP">[54]Basis_für_Preise_und_Texte!#REF!</definedName>
     <definedName name="swbbu32">#REF!</definedName>
     <definedName name="swbbu64">#REF!</definedName>
     <definedName name="Switch_postpaid_ARPU">#REF!</definedName>
     <definedName name="sxc">#REF!</definedName>
     <definedName name="sxp">#REF!</definedName>
-    <definedName name="Synth">[74]Synth!$C$9:$V$991</definedName>
+    <definedName name="Synth">[73]Synth!$C$9:$V$991</definedName>
     <definedName name="SYSTEM_2000">#REF!</definedName>
     <definedName name="SYSTEM_3000">#REF!</definedName>
     <definedName name="SYSTEM_5000">#REF!</definedName>
     <definedName name="SYSTEMS">#REF!</definedName>
     <definedName name="T">#REF!</definedName>
     <definedName name="TAB8BTS">#REF!</definedName>
-    <definedName name="TABLE_ERLANG">[88]Erlang!$C$43:$J$56</definedName>
-    <definedName name="TAIWD">[6]graphs!$K$6</definedName>
+    <definedName name="TABLE_ERLANG">[87]Erlang!$C$43:$J$56</definedName>
+    <definedName name="TAIWD">[5]graphs!$K$6</definedName>
     <definedName name="TAT_1">#REF!</definedName>
     <definedName name="TAT_2">#REF!</definedName>
     <definedName name="TAT_3">#REF!</definedName>
     <definedName name="TAT_4">#REF!</definedName>
     <definedName name="TAT_5">#REF!</definedName>
     <definedName name="Taxa_do_Dólar">#REF!</definedName>
-    <definedName name="TB">[16]VARDATA!$C$16</definedName>
+    <definedName name="TB">[15]VARDATA!$C$16</definedName>
     <definedName name="tdta_SortTransferOFFIT">#REF!</definedName>
     <definedName name="Techn_Risk_Proz">#REF!</definedName>
     <definedName name="Teqddu">#REF!</definedName>
-    <definedName name="THB">[6]graphs!$Q$6</definedName>
+    <definedName name="THB">[5]graphs!$Q$6</definedName>
     <definedName name="third">#REF!</definedName>
     <definedName name="thirdparty">#REF!</definedName>
     <definedName name="threeg">#REF!</definedName>
     <definedName name="TM">#REF!</definedName>
-    <definedName name="To">'[18]Total GSM  Market'!#REF!</definedName>
-    <definedName name="Toc">'[18]Total GSM  Market'!#REF!</definedName>
+    <definedName name="To">'[17]Total GSM  Market'!#REF!</definedName>
+    <definedName name="Toc">'[17]Total GSM  Market'!#REF!</definedName>
     <definedName name="Total_Authorized_Gross_Profit_Rate">#REF!</definedName>
     <definedName name="Total_Contribution_Profit_after_Risk">#REF!</definedName>
     <definedName name="Total_Contribution_Profit_Rate_after_Risk">#REF!</definedName>
     <definedName name="Total_Gross_Profit">#REF!</definedName>
     <definedName name="Total_Gross_Profit_Rate">#REF!</definedName>
     <definedName name="Total_Net_Sales_Revenue">#REF!</definedName>
-    <definedName name="Total_of">[44]Definitions!$B$374</definedName>
+    <definedName name="Total_of">[43]Definitions!$B$374</definedName>
     <definedName name="Total_Proposed_Price">#REF!</definedName>
     <definedName name="Total_Risk_Contigency">#REF!</definedName>
     <definedName name="Total_Sales_Cost_and_Direct_Expense">#REF!</definedName>
     <definedName name="Total_Target_Gross_Profit_Rate">#REF!</definedName>
     <definedName name="TotalPriceColumeName">#REF!</definedName>
     <definedName name="totalrev_feeder">#REF!</definedName>
-    <definedName name="TPROD">[16]VARDATA!$C$21</definedName>
+    <definedName name="TPROD">[15]VARDATA!$C$21</definedName>
     <definedName name="tr">#REF!</definedName>
     <definedName name="TRANSCEIVERS__CABLES">#REF!</definedName>
     <definedName name="transmission">#REF!</definedName>
     <definedName name="trc">#REF!</definedName>
     <definedName name="tri">#REF!</definedName>
     <definedName name="tt">#REF!</definedName>
-    <definedName name="type">[60]main!$A$1</definedName>
-    <definedName name="typecol">[60]main!$A$1:$A$65535</definedName>
-    <definedName name="u">'[4]Bass Curve Calibration'!$B$11</definedName>
-    <definedName name="UM">[23]UM!$A$2:$A$50</definedName>
-    <definedName name="Under_14">[66]Data!$C$22</definedName>
-    <definedName name="Unit">'[68]Model Paramter(WL+MW+NE)0313'!$K$4:$K$4</definedName>
-    <definedName name="Unit_Prices">[89]UnitPrices!$B$12:$W$528</definedName>
+    <definedName name="type">[59]main!$A$1</definedName>
+    <definedName name="typecol">[59]main!$A$1:$A$65535</definedName>
+    <definedName name="u">'[3]Bass Curve Calibration'!$B$11</definedName>
+    <definedName name="UM">[22]UM!$A$2:$A$50</definedName>
+    <definedName name="Under_14">[65]Data!$C$22</definedName>
+    <definedName name="Unit">'[67]Model Paramter(WL+MW+NE)0313'!$K$4:$K$4</definedName>
+    <definedName name="Unit_Prices">[88]UnitPrices!$B$12:$W$528</definedName>
     <definedName name="UnitPriceColumeName">#REF!</definedName>
-    <definedName name="uom">[86]UOM!$A$2:$A$67</definedName>
+    <definedName name="uom">[85]UOM!$A$2:$A$67</definedName>
     <definedName name="urcc">#REF!</definedName>
     <definedName name="urcp">#REF!</definedName>
     <definedName name="US">#REF!</definedName>
@@ -1647,15 +1646,15 @@
     <definedName name="uyew" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"Sensitivity"}</definedName>
     <definedName name="uyew" hidden="1">{#N/A,#N/A,FALSE,"Sensitivity"}</definedName>
     <definedName name="V_F">#REF!</definedName>
-    <definedName name="VALDOL">[16]FIXDATA!$C$8</definedName>
-    <definedName name="Veh_Bal">'[3]F&amp;F'!#REF!</definedName>
-    <definedName name="Vendor">'[23]Supplier data'!$A$1:$A$28</definedName>
+    <definedName name="VALDOL">[15]FIXDATA!$C$8</definedName>
+    <definedName name="Veh_Bal">'[2]F&amp;F'!#REF!</definedName>
+    <definedName name="Vendor">'[22]Supplier data'!$A$1:$A$28</definedName>
     <definedName name="VPN_on_NE1">"Kontrollkästchen 19"</definedName>
     <definedName name="VR">#REF!</definedName>
     <definedName name="W">#REF!</definedName>
-    <definedName name="w1111111111111">'[90]Project Data'!$A$1:$A$65536</definedName>
+    <definedName name="w1111111111111">'[89]Project Data'!$A$1:$A$65536</definedName>
     <definedName name="WA">#REF!</definedName>
-    <definedName name="Waehrung">[55]Basis_für_Preise_und_Texte!#REF!</definedName>
+    <definedName name="Waehrung">[54]Basis_für_Preise_und_Texte!#REF!</definedName>
     <definedName name="wbs">#REF!</definedName>
     <definedName name="wbsid">#REF!</definedName>
     <definedName name="WEQ">#REF!</definedName>
@@ -1664,9 +1663,9 @@
     <definedName name="what" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"Profit &amp; Loss statement"}</definedName>
     <definedName name="what" hidden="1">{#N/A,#N/A,FALSE,"Profit &amp; Loss statement"}</definedName>
     <definedName name="WI">#REF!</definedName>
-    <definedName name="Widelink_Version">[30]Planner!#REF!</definedName>
+    <definedName name="Widelink_Version">[29]Planner!#REF!</definedName>
     <definedName name="Windetial">#REF!</definedName>
-    <definedName name="WON">[6]graphs!$M$6</definedName>
+    <definedName name="WON">[5]graphs!$M$6</definedName>
     <definedName name="WORKINGSALL">#REF!</definedName>
     <definedName name="wrn" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
     <definedName name="wrn" hidden="1">{#N/A,#N/A,TRUE,"Config1";#N/A,#N/A,TRUE,"Config2";#N/A,#N/A,TRUE,"Config3";#N/A,#N/A,TRUE,"Config4";#N/A,#N/A,TRUE,"Config5";#N/A,#N/A,TRUE,"Config6";#N/A,#N/A,TRUE,"Config7"}</definedName>
@@ -1702,27 +1701,27 @@
     <definedName name="WrnDevSynthese" hidden="1">{"COST",#N/A,FALSE,"SYNTHESE";"MARGIN",#N/A,FALSE,"SYNTHESE";"LOT_COM",#N/A,FALSE,"SYNTHESE"}</definedName>
     <definedName name="WrnDevSynthese2" localSheetId="0" hidden="1">{"COST",#N/A,FALSE,"SYNTHESE";"MARGIN",#N/A,FALSE,"SYNTHESE";"LOT_COM",#N/A,FALSE,"SYNTHESE"}</definedName>
     <definedName name="WrnDevSynthese2" hidden="1">{"COST",#N/A,FALSE,"SYNTHESE";"MARGIN",#N/A,FALSE,"SYNTHESE";"LOT_COM",#N/A,FALSE,"SYNTHESE"}</definedName>
-    <definedName name="ww">[49]MD5500!$A$15:$M$168</definedName>
+    <definedName name="ww">[48]MD5500!$A$15:$M$168</definedName>
     <definedName name="WWQ">#REF!</definedName>
-    <definedName name="Xedia_Mbps">'[91]Equip Dim'!#REF!</definedName>
-    <definedName name="Xedia_shelf_1">'[91]Equip Dim'!#REF!</definedName>
-    <definedName name="Xedia_shelf_2">'[91]Equip Dim'!#REF!</definedName>
-    <definedName name="Xedia_shelf_3">'[91]Equip Dim'!#REF!</definedName>
-    <definedName name="year">'[34]Name Ranges (DO NOT CHANGE)'!$B$201:$B$210</definedName>
+    <definedName name="Xedia_Mbps">'[90]Equip Dim'!#REF!</definedName>
+    <definedName name="Xedia_shelf_1">'[90]Equip Dim'!#REF!</definedName>
+    <definedName name="Xedia_shelf_2">'[90]Equip Dim'!#REF!</definedName>
+    <definedName name="Xedia_shelf_3">'[90]Equip Dim'!#REF!</definedName>
+    <definedName name="year">'[33]Name Ranges (DO NOT CHANGE)'!$B$201:$B$210</definedName>
     <definedName name="Z">#REF!</definedName>
     <definedName name="Zone_Hierarchie1">#REF!</definedName>
-    <definedName name="交付件标准名称">[92]说明!$A$2:$A$24</definedName>
+    <definedName name="交付件标准名称">[91]说明!$A$2:$A$24</definedName>
     <definedName name="人力费率">#REF!</definedName>
     <definedName name="任务_表">#REF!</definedName>
     <definedName name="光放寒假">#REF!</definedName>
     <definedName name="合作费率">#REF!</definedName>
     <definedName name="呃呃呃呃呃呃呃呃呃呃呃呃呃呃呃呃">#REF!</definedName>
-    <definedName name="天线">'[93]工时（含系数）、操作步骤、工具、物料、客户要求导入'!$N$204:$N$208,'[93]工时（含系数）、操作步骤、工具、物料、客户要求导入'!$N$212:$N$215,'[93]工时（含系数）、操作步骤、工具、物料、客户要求导入'!$N$222:$N$223,'[93]工时（含系数）、操作步骤、工具、物料、客户要求导入'!$N$228:$N$229</definedName>
+    <definedName name="天线">'[92]工时（含系数）、操作步骤、工具、物料、客户要求导入'!$N$204:$N$208,'[92]工时（含系数）、操作步骤、工具、物料、客户要求导入'!$N$212:$N$215,'[92]工时（含系数）、操作步骤、工具、物料、客户要求导入'!$N$222:$N$223,'[92]工时（含系数）、操作步骤、工具、物料、客户要求导入'!$N$228:$N$229</definedName>
     <definedName name="日日日日日">#REF!</definedName>
     <definedName name="李岩">#REF!</definedName>
     <definedName name="汇率">#REF!</definedName>
     <definedName name="汇率表">#REF!</definedName>
-    <definedName name="而">[5]Optimised!#REF!</definedName>
+    <definedName name="而">[4]Optimised!#REF!</definedName>
     <definedName name="资源_表">#REF!</definedName>
     <definedName name="酒店住宿" localSheetId="0" hidden="1">{#N/A,#N/A,TRUE,"Discount";#N/A,#N/A,TRUE,"Sommaire";#N/A,#N/A,TRUE,"Services";#N/A,#N/A,TRUE,"RNP";#N/A,#N/A,TRUE,"Support";#N/A,#N/A,TRUE,"BSS";#N/A,#N/A,TRUE,"BTS";#N/A,#N/A,TRUE,"BSC";#N/A,#N/A,TRUE,"BSC1";#N/A,#N/A,TRUE,"TRANSCODER";#N/A,#N/A,TRUE,"OMC-R";#N/A,#N/A,TRUE,"MW";#N/A,#N/A,TRUE,"DIESEL";#N/A,#N/A,TRUE,"TOWERS";#N/A,#N/A,TRUE,"ANTENNAS";#N/A,#N/A,TRUE,"SHELTERS";#N/A,#N/A,TRUE,"SPARES";#N/A,#N/A,TRUE,"SP_item";#N/A,#N/A,TRUE,"TOOLS";#N/A,#N/A,TRUE,"DOC";#N/A,#N/A,TRUE,"Mobile"}</definedName>
     <definedName name="酒店住宿" hidden="1">{#N/A,#N/A,TRUE,"Discount";#N/A,#N/A,TRUE,"Sommaire";#N/A,#N/A,TRUE,"Services";#N/A,#N/A,TRUE,"RNP";#N/A,#N/A,TRUE,"Support";#N/A,#N/A,TRUE,"BSS";#N/A,#N/A,TRUE,"BTS";#N/A,#N/A,TRUE,"BSC";#N/A,#N/A,TRUE,"BSC1";#N/A,#N/A,TRUE,"TRANSCODER";#N/A,#N/A,TRUE,"OMC-R";#N/A,#N/A,TRUE,"MW";#N/A,#N/A,TRUE,"DIESEL";#N/A,#N/A,TRUE,"TOWERS";#N/A,#N/A,TRUE,"ANTENNAS";#N/A,#N/A,TRUE,"SHELTERS";#N/A,#N/A,TRUE,"SPARES";#N/A,#N/A,TRUE,"SP_item";#N/A,#N/A,TRUE,"TOOLS";#N/A,#N/A,TRUE,"DOC";#N/A,#N/A,TRUE,"Mobile"}</definedName>
@@ -1734,9 +1733,9 @@
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
       <x15:slicerCaches xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+        <x14:slicerCache r:id="rId94"/>
         <x14:slicerCache r:id="rId95"/>
         <x14:slicerCache r:id="rId96"/>
-        <x14:slicerCache r:id="rId97"/>
       </x15:slicerCaches>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2272,7 +2271,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d/mmm/yy;@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3050,8 +3049,8 @@
   <xdr:absoluteAnchor>
     <xdr:pos x="190500" y="9524"/>
     <xdr:ext cx="6575249" cy="1057275"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="TSS Model 2">
@@ -3074,7 +3073,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3118,8 +3117,8 @@
   <xdr:absoluteAnchor>
     <xdr:pos x="6770368" y="9525"/>
     <xdr:ext cx="6743460" cy="1049656"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="TI Model 4">
@@ -3142,7 +3141,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3186,8 +3185,8 @@
   <xdr:absoluteAnchor>
     <xdr:pos x="13491204" y="7620"/>
     <xdr:ext cx="2827023" cy="1051200"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+      <mc:Choice Requires="sle15">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="Add PR Line Item Model">
@@ -3210,7 +3209,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3257,55 +3256,15 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="TX Line Item (Before 11-Jul 24)"/>
-      <sheetName val="PBOM (Before 11-Jul 24)"/>
-      <sheetName val="TX Line Item (After 11-Jul 24)"/>
-      <sheetName val="PBOM (After 11-Jul 24)"/>
-      <sheetName val="Jendela TX Migration"/>
-      <sheetName val="Add PR Line Item"/>
-      <sheetName val="MW Decom"/>
-      <sheetName val="TX SOW Overview"/>
-      <sheetName val="TX Line Item (After 20-Apr 26)"/>
-      <sheetName val="PBOM (After 20-Apr 26)"/>
-      <sheetName val="MW Decom (After 20-Apr 26"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="M_Cfg"/>
-      <sheetName val="IsoCode"/>
-      <sheetName val="Input"/>
-      <sheetName val="PD_Data"/>
-      <sheetName val="PD"/>
-      <sheetName val="S_PD"/>
-      <sheetName val="FO"/>
-      <sheetName val="FO_Data"/>
-      <sheetName val="FU"/>
-      <sheetName val="FU_SST"/>
-      <sheetName val="Assumptions"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="2-Summary of Changes"/>
+      <sheetName val="2_SummaryofChanges"/>
+      <sheetName val="2-Summary_of_Changes"/>
+      <sheetName val="Validation"/>
+      <sheetName val="Budget Line items"/>
+      <sheetName val="2_Summary of Changes"/>
+      <sheetName val="Planner"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -3316,17 +3275,17 @@
       <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6" refreshError="1"/>
       <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="首页说明"/>
       <sheetName val="国家维表"/>
@@ -3357,7 +3316,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3384,7 +3343,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3419,7 +3378,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3500,7 +3459,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3583,7 +3542,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3648,7 +3607,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3763,7 +3722,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3816,7 +3775,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3835,34 +3794,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="2-Summary of Changes"/>
-      <sheetName val="2_SummaryofChanges"/>
-      <sheetName val="2-Summary_of_Changes"/>
-      <sheetName val="Validation"/>
-      <sheetName val="Budget Line items"/>
-      <sheetName val="2_Summary of Changes"/>
-      <sheetName val="Planner"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3949,7 +3881,32 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="XXXX"/>
+      <sheetName val="B"/>
+      <sheetName val="F&amp;F"/>
+      <sheetName val="CS"/>
+      <sheetName val="LI"/>
+      <sheetName val="OE"/>
+      <sheetName val="CH"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3996,7 +3953,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4029,9 +3986,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="RFQ"/>
       <sheetName val="SOW &amp; BOQ"/>
@@ -4052,7 +4012,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4101,7 +4061,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4142,7 +4102,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4175,9 +4135,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="BudgetGuide"/>
       <sheetName val="ARCGuide"/>
@@ -4246,9 +4209,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="BudgetGuide"/>
       <sheetName val="ARCGuide"/>
@@ -4299,9 +4265,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="template"/>
       <sheetName val="version_information"/>
@@ -4320,32 +4289,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="XXXX"/>
-      <sheetName val="B"/>
-      <sheetName val="F&amp;F"/>
-      <sheetName val="CS"/>
-      <sheetName val="LI"/>
-      <sheetName val="OE"/>
-      <sheetName val="CH"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4372,436 +4316,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="CFO931"/>
-      <sheetName val="PFO"/>
-      <sheetName val="Hypothèses"/>
-      <sheetName val="UnitPrices"/>
-      <sheetName val="BOQ"/>
-      <sheetName val="margin"/>
-      <sheetName val="CTRL"/>
-      <sheetName val="OGCAT-01"/>
-      <sheetName val="OGCAT-02"/>
-      <sheetName val="OGCAT-03"/>
-      <sheetName val="Spare-Price"/>
-      <sheetName val="OGCAT-04"/>
-      <sheetName val="Nokia FlexiHopper PDH"/>
-      <sheetName val="Catalogue A5070 SSG"/>
-      <sheetName val="Planner"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Historique"/>
-      <sheetName val="GFA-pricelist"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Breakdown"/>
-      <sheetName val="Synth"/>
-      <sheetName val="Dim"/>
-      <sheetName val="Global"/>
-      <sheetName val="Reference"/>
-      <sheetName val="Phase 1"/>
-      <sheetName val="Incoterm"/>
-      <sheetName val="Rates"/>
-      <sheetName val="DirectMarg"/>
-      <sheetName val="OP"/>
-      <sheetName val="IPIS"/>
-      <sheetName val="Phase 2"/>
-      <sheetName val="Phase 3"/>
-      <sheetName val="Phase 4"/>
-      <sheetName val="Phase 5"/>
-      <sheetName val="Phase 6"/>
-      <sheetName val="Phase 7"/>
-      <sheetName val="Phase Total"/>
-      <sheetName val="Erlang"/>
-      <sheetName val="Country Geozone Table"/>
-      <sheetName val="Evolutions"/>
-      <sheetName val="Hypothèses"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="FrontPage"/>
-      <sheetName val="aggregation"/>
-      <sheetName val="company"/>
-      <sheetName val="datastream"/>
-      <sheetName val="charts"/>
-      <sheetName val="analysts"/>
-      <sheetName val="definitions"/>
-      <sheetName val="graphs"/>
-      <sheetName val="overview"/>
-      <sheetName val="data"/>
-      <sheetName val="Reference"/>
-      <sheetName val="Sheet2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="INSTRUCTIONS! READ THIS FIRST!!"/>
-      <sheetName val="WBS"/>
-      <sheetName val="BOE Labor"/>
-      <sheetName val="Travel Inputs"/>
-      <sheetName val="ODC Inputs"/>
-      <sheetName val="Estimator Notes"/>
-      <sheetName val="Notes"/>
-      <sheetName val="Name Ranges (DO NOT CHANGE)"/>
-      <sheetName val="Import Template"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Breakdown"/>
-      <sheetName val="Synth"/>
-      <sheetName val="Global"/>
-      <sheetName val="CPABSS"/>
-      <sheetName val="MAIPLH"/>
-      <sheetName val="FCOC"/>
-      <sheetName val="DIM"/>
-      <sheetName val="RTU"/>
-      <sheetName val="OMC-R"/>
-      <sheetName val="Power"/>
-      <sheetName val="Customer"/>
-      <sheetName val="Reference"/>
-      <sheetName val="Erlang"/>
-      <sheetName val="CPFO"/>
-      <sheetName val="Training"/>
-      <sheetName val="Rfrce"/>
-      <sheetName val="Global_foreign"/>
-      <sheetName val="Global_local"/>
-      <sheetName val="Other"/>
-      <sheetName val="Sub"/>
-      <sheetName val="IPIS_TOTAL"/>
-      <sheetName val="DMarg_total"/>
-      <sheetName val="DMarg_foreign"/>
-      <sheetName val="DMarg_local"/>
-      <sheetName val="OP_foreign"/>
-      <sheetName val="OP_local"/>
-      <sheetName val="Synth_foreign"/>
-      <sheetName val="Synth_local"/>
-      <sheetName val="IPISN"/>
-      <sheetName val="IPISN+1"/>
-      <sheetName val="IPISN+2"/>
-      <sheetName val="IPISN+3"/>
-      <sheetName val="IPISN+4"/>
-      <sheetName val="IPISN+5"/>
-      <sheetName val="IPISN+6"/>
-      <sheetName val="Rates"/>
-      <sheetName val="BER CAL"/>
-      <sheetName val="data"/>
-      <sheetName val="overview"/>
-      <sheetName val="datastream"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-      <sheetData sheetId="33" refreshError="1"/>
-      <sheetData sheetId="34" refreshError="1"/>
-      <sheetData sheetId="35" refreshError="1"/>
-      <sheetData sheetId="36" refreshError="1"/>
-      <sheetData sheetId="37" refreshError="1"/>
-      <sheetData sheetId="38" refreshError="1"/>
-      <sheetData sheetId="39" refreshError="1"/>
-      <sheetData sheetId="40" refreshError="1"/>
-      <sheetData sheetId="41" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="NOMENCLATURE NMS"/>
-      <sheetName val="Grouping MGT"/>
-      <sheetName val="Grouping Audit"/>
-      <sheetName val="Parts Form"/>
-      <sheetName val="Cabinets"/>
-      <sheetName val="ONUs"/>
-      <sheetName val="Input Data"/>
-      <sheetName val="Sort"/>
-      <sheetName val="MAIPLH"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Commercial"/>
-      <sheetName val="Tools"/>
-      <sheetName val="BOQ"/>
-      <sheetName val="Quotation"/>
-      <sheetName val="Margin"/>
-      <sheetName val="Maintenance"/>
-      <sheetName val="Data"/>
-      <sheetName val="cfoa51"/>
-      <sheetName val="Bordereau"/>
-      <sheetName val="NOMENCLATURE NMS"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="version"/>
-      <sheetName val="Historique Configurateur"/>
-      <sheetName val="General"/>
-      <sheetName val="Input"/>
-      <sheetName val="Cost Note"/>
-      <sheetName val="Inputs"/>
-      <sheetName val="Configurator"/>
-      <sheetName val="Costs"/>
-      <sheetName val="ums32-price list Ed6i"/>
-      <sheetName val="regular"/>
-      <sheetName val="price regular&amp;HA"/>
-      <sheetName val="IPIS direct costing"/>
-      <sheetName val="Global Pricing"/>
-      <sheetName val="Detailed Pricing"/>
-      <sheetName val="Principes"/>
-      <sheetName val="operations costs"/>
-      <sheetName val="BoQTest"/>
-      <sheetName val="Calculs initiaux"/>
-      <sheetName val="AFFAIRE"/>
-      <sheetName val="Garantie"/>
-      <sheetName val="Maintenance"/>
-      <sheetName val="Mode d'emploi"/>
-      <sheetName val="Environment"/>
-      <sheetName val="TabList"/>
-      <sheetName val="PPTables"/>
-      <sheetName val="cfoa51"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="BOE Labor"/>
-      <sheetName val="Financials by Month"/>
-      <sheetName val="5 Yr Financials"/>
-      <sheetName val="5 Yr Financials - Calendar"/>
-      <sheetName val="Web Hosting"/>
-      <sheetName val="SWG Skills"/>
-      <sheetName val="INSTRUCTIONS! READ THIS FIRST!!"/>
-      <sheetName val="WBS"/>
-      <sheetName val="Bridge Summary"/>
-      <sheetName val="Travel Inputs"/>
-      <sheetName val="ODC Inputs"/>
-      <sheetName val="Estimator Notes"/>
-      <sheetName val="Notes"/>
-      <sheetName val="Rates"/>
-      <sheetName val="Name Ranges (DO NOT CHANGE)"/>
-      <sheetName val="Import Template"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4938,7 +4453,442 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="CFO931"/>
+      <sheetName val="PFO"/>
+      <sheetName val="Hypothèses"/>
+      <sheetName val="UnitPrices"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="margin"/>
+      <sheetName val="CTRL"/>
+      <sheetName val="OGCAT-01"/>
+      <sheetName val="OGCAT-02"/>
+      <sheetName val="OGCAT-03"/>
+      <sheetName val="Spare-Price"/>
+      <sheetName val="OGCAT-04"/>
+      <sheetName val="Nokia FlexiHopper PDH"/>
+      <sheetName val="Catalogue A5070 SSG"/>
+      <sheetName val="Planner"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Historique"/>
+      <sheetName val="GFA-pricelist"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Breakdown"/>
+      <sheetName val="Synth"/>
+      <sheetName val="Dim"/>
+      <sheetName val="Global"/>
+      <sheetName val="Reference"/>
+      <sheetName val="Phase 1"/>
+      <sheetName val="Incoterm"/>
+      <sheetName val="Rates"/>
+      <sheetName val="DirectMarg"/>
+      <sheetName val="OP"/>
+      <sheetName val="IPIS"/>
+      <sheetName val="Phase 2"/>
+      <sheetName val="Phase 3"/>
+      <sheetName val="Phase 4"/>
+      <sheetName val="Phase 5"/>
+      <sheetName val="Phase 6"/>
+      <sheetName val="Phase 7"/>
+      <sheetName val="Phase Total"/>
+      <sheetName val="Erlang"/>
+      <sheetName val="Country Geozone Table"/>
+      <sheetName val="Evolutions"/>
+      <sheetName val="Hypothèses"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="FrontPage"/>
+      <sheetName val="aggregation"/>
+      <sheetName val="company"/>
+      <sheetName val="datastream"/>
+      <sheetName val="charts"/>
+      <sheetName val="analysts"/>
+      <sheetName val="definitions"/>
+      <sheetName val="graphs"/>
+      <sheetName val="overview"/>
+      <sheetName val="data"/>
+      <sheetName val="Reference"/>
+      <sheetName val="Sheet2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="INSTRUCTIONS! READ THIS FIRST!!"/>
+      <sheetName val="WBS"/>
+      <sheetName val="BOE Labor"/>
+      <sheetName val="Travel Inputs"/>
+      <sheetName val="ODC Inputs"/>
+      <sheetName val="Estimator Notes"/>
+      <sheetName val="Notes"/>
+      <sheetName val="Name Ranges (DO NOT CHANGE)"/>
+      <sheetName val="Import Template"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Breakdown"/>
+      <sheetName val="Synth"/>
+      <sheetName val="Global"/>
+      <sheetName val="CPABSS"/>
+      <sheetName val="MAIPLH"/>
+      <sheetName val="FCOC"/>
+      <sheetName val="DIM"/>
+      <sheetName val="RTU"/>
+      <sheetName val="OMC-R"/>
+      <sheetName val="Power"/>
+      <sheetName val="Customer"/>
+      <sheetName val="Reference"/>
+      <sheetName val="Erlang"/>
+      <sheetName val="CPFO"/>
+      <sheetName val="Training"/>
+      <sheetName val="Rfrce"/>
+      <sheetName val="Global_foreign"/>
+      <sheetName val="Global_local"/>
+      <sheetName val="Other"/>
+      <sheetName val="Sub"/>
+      <sheetName val="IPIS_TOTAL"/>
+      <sheetName val="DMarg_total"/>
+      <sheetName val="DMarg_foreign"/>
+      <sheetName val="DMarg_local"/>
+      <sheetName val="OP_foreign"/>
+      <sheetName val="OP_local"/>
+      <sheetName val="Synth_foreign"/>
+      <sheetName val="Synth_local"/>
+      <sheetName val="IPISN"/>
+      <sheetName val="IPISN+1"/>
+      <sheetName val="IPISN+2"/>
+      <sheetName val="IPISN+3"/>
+      <sheetName val="IPISN+4"/>
+      <sheetName val="IPISN+5"/>
+      <sheetName val="IPISN+6"/>
+      <sheetName val="Rates"/>
+      <sheetName val="BER CAL"/>
+      <sheetName val="data"/>
+      <sheetName val="overview"/>
+      <sheetName val="datastream"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="28" refreshError="1"/>
+      <sheetData sheetId="29" refreshError="1"/>
+      <sheetData sheetId="30" refreshError="1"/>
+      <sheetData sheetId="31" refreshError="1"/>
+      <sheetData sheetId="32" refreshError="1"/>
+      <sheetData sheetId="33" refreshError="1"/>
+      <sheetData sheetId="34" refreshError="1"/>
+      <sheetData sheetId="35" refreshError="1"/>
+      <sheetData sheetId="36" refreshError="1"/>
+      <sheetData sheetId="37" refreshError="1"/>
+      <sheetData sheetId="38" refreshError="1"/>
+      <sheetData sheetId="39" refreshError="1"/>
+      <sheetData sheetId="40" refreshError="1"/>
+      <sheetData sheetId="41" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="NOMENCLATURE NMS"/>
+      <sheetName val="Grouping MGT"/>
+      <sheetName val="Grouping Audit"/>
+      <sheetName val="Parts Form"/>
+      <sheetName val="Cabinets"/>
+      <sheetName val="ONUs"/>
+      <sheetName val="Input Data"/>
+      <sheetName val="Sort"/>
+      <sheetName val="MAIPLH"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Commercial"/>
+      <sheetName val="Tools"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="Quotation"/>
+      <sheetName val="Margin"/>
+      <sheetName val="Maintenance"/>
+      <sheetName val="Data"/>
+      <sheetName val="cfoa51"/>
+      <sheetName val="Bordereau"/>
+      <sheetName val="NOMENCLATURE NMS"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="version"/>
+      <sheetName val="Historique Configurateur"/>
+      <sheetName val="General"/>
+      <sheetName val="Input"/>
+      <sheetName val="Cost Note"/>
+      <sheetName val="Inputs"/>
+      <sheetName val="Configurator"/>
+      <sheetName val="Costs"/>
+      <sheetName val="ums32-price list Ed6i"/>
+      <sheetName val="regular"/>
+      <sheetName val="price regular&amp;HA"/>
+      <sheetName val="IPIS direct costing"/>
+      <sheetName val="Global Pricing"/>
+      <sheetName val="Detailed Pricing"/>
+      <sheetName val="Principes"/>
+      <sheetName val="operations costs"/>
+      <sheetName val="BoQTest"/>
+      <sheetName val="Calculs initiaux"/>
+      <sheetName val="AFFAIRE"/>
+      <sheetName val="Garantie"/>
+      <sheetName val="Maintenance"/>
+      <sheetName val="Mode d'emploi"/>
+      <sheetName val="Environment"/>
+      <sheetName val="TabList"/>
+      <sheetName val="PPTables"/>
+      <sheetName val="cfoa51"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="BOE Labor"/>
+      <sheetName val="Financials by Month"/>
+      <sheetName val="5 Yr Financials"/>
+      <sheetName val="5 Yr Financials - Calendar"/>
+      <sheetName val="Web Hosting"/>
+      <sheetName val="SWG Skills"/>
+      <sheetName val="INSTRUCTIONS! READ THIS FIRST!!"/>
+      <sheetName val="WBS"/>
+      <sheetName val="Bridge Summary"/>
+      <sheetName val="Travel Inputs"/>
+      <sheetName val="ODC Inputs"/>
+      <sheetName val="Estimator Notes"/>
+      <sheetName val="Notes"/>
+      <sheetName val="Rates"/>
+      <sheetName val="Name Ranges (DO NOT CHANGE)"/>
+      <sheetName val="Import Template"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4999,7 +4949,20 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Optimised"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5050,7 +5013,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5081,7 +5044,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5236,7 +5199,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5283,9 +5246,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Parameters"/>
       <sheetName val="Cover"/>
@@ -5304,7 +5270,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5339,7 +5305,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink46.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5384,9 +5350,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="DISCOUNT"/>
       <sheetName val="cover"/>
@@ -5413,9 +5382,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Summary"/>
       <sheetName val="Service(I&amp;C)"/>
@@ -5474,20 +5446,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Optimised"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink49.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5576,7 +5535,38 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="FrontPage"/>
+      <sheetName val="aggregation"/>
+      <sheetName val="company"/>
+      <sheetName val="datastream"/>
+      <sheetName val="charts"/>
+      <sheetName val="analysts"/>
+      <sheetName val="definitions"/>
+      <sheetName val="graphs"/>
+      <sheetName val="overview"/>
+      <sheetName val="data"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink50.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5617,7 +5607,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink51.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5638,7 +5628,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink52.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5681,7 +5671,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink53.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5700,7 +5690,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink54.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5725,7 +5715,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink55.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5770,9 +5760,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Navigation"/>
       <sheetName val="BasicInfo"/>
@@ -5869,7 +5862,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink57.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5886,7 +5879,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink58.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5905,40 +5898,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="FrontPage"/>
-      <sheetName val="aggregation"/>
-      <sheetName val="company"/>
-      <sheetName val="datastream"/>
-      <sheetName val="charts"/>
-      <sheetName val="analysts"/>
-      <sheetName val="definitions"/>
-      <sheetName val="graphs"/>
-      <sheetName val="overview"/>
-      <sheetName val="data"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="ProjectInfo"/>
       <sheetName val="Resource Plan"/>
@@ -5959,7 +5924,61 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="0-Total Summary"/>
+      <sheetName val="1-Total Summary"/>
+      <sheetName val="2-BTS Site Models"/>
+      <sheetName val="3-BTS swap Model"/>
+      <sheetName val="4-BSC Models"/>
+      <sheetName val="5-BTS Unit Prices"/>
+      <sheetName val="6-Other BSS &amp; GPRS Equip"/>
+      <sheetName val="7-Aerials Unit Price"/>
+      <sheetName val="8-MW&amp;SDH&amp;HDSL"/>
+      <sheetName val="9-Spares"/>
+      <sheetName val="10-SW Options"/>
+      <sheetName val="11-Additional_Services "/>
+      <sheetName val="12-Op. Additional Items"/>
+      <sheetName val="     "/>
+      <sheetName val="BOQ"/>
+      <sheetName val="3-BTS Site Models Swap"/>
+      <sheetName val="Sites Models Unit P"/>
+      <sheetName val="Inputs"/>
+      <sheetName val="Comparison"/>
+      <sheetName val="M 1.1 (2)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink60.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5978,7 +5997,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink61.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5999,9 +6018,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="L2 Site Model"/>
       <sheetName val="Mapping for L3 New&amp;Swap"/>
@@ -6056,9 +6078,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="INSTRUCTIONS! READ THIS FIRST!!"/>
       <sheetName val="WBS"/>
@@ -6089,7 +6114,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink64.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -6116,7 +6141,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink65.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -6163,9 +6188,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="BOE Labor"/>
       <sheetName val="Financials by Month"/>
@@ -6208,7 +6236,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink67.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -6243,7 +6271,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink68.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -6268,58 +6296,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="0-Total Summary"/>
-      <sheetName val="1-Total Summary"/>
-      <sheetName val="2-BTS Site Models"/>
-      <sheetName val="3-BTS swap Model"/>
-      <sheetName val="4-BSC Models"/>
-      <sheetName val="5-BTS Unit Prices"/>
-      <sheetName val="6-Other BSS &amp; GPRS Equip"/>
-      <sheetName val="7-Aerials Unit Price"/>
-      <sheetName val="8-MW&amp;SDH&amp;HDSL"/>
-      <sheetName val="9-Spares"/>
-      <sheetName val="10-SW Options"/>
-      <sheetName val="11-Additional_Services "/>
-      <sheetName val="12-Op. Additional Items"/>
-      <sheetName val="     "/>
-      <sheetName val="BOQ"/>
-      <sheetName val="3-BTS Site Models Swap"/>
-      <sheetName val="Sites Models Unit P"/>
-      <sheetName val="Inputs"/>
-      <sheetName val="Comparison"/>
-      <sheetName val="M 1.1 (2)"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink69.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -6378,7 +6355,36 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Infos"/>
+      <sheetName val="discontinuations"/>
+      <sheetName val="HW pricelist ICN VD"/>
+      <sheetName val="HW pricelist DACH"/>
+      <sheetName val="wiring pricelist"/>
+      <sheetName val="Spectrum pricelist"/>
+      <sheetName val="currency"/>
+      <sheetName val="SAP-Referenz"/>
+      <sheetName val="Price book "/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink70.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -6407,9 +6413,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="框架招标预测Frame Bidding Forecast"/>
       <sheetName val="Config"/>
@@ -6422,7 +6431,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink72.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -6463,7 +6472,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink73.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -6542,7 +6551,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink74.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -6595,9 +6604,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="PopCache"/>
       <sheetName val="BneWorkBookProperties"/>
@@ -6614,9 +6626,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="P&amp;L"/>
       <sheetName val="Summary by Labor category"/>
@@ -6641,9 +6656,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Executive summary "/>
       <sheetName val="Executive summary by zone"/>
@@ -6854,9 +6872,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="SW in keyfile"/>
       <sheetName val="PRC EPL"/>
@@ -6883,38 +6904,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Infos"/>
-      <sheetName val="discontinuations"/>
-      <sheetName val="HW pricelist ICN VD"/>
-      <sheetName val="HW pricelist DACH"/>
-      <sheetName val="wiring pricelist"/>
-      <sheetName val="Spectrum pricelist"/>
-      <sheetName val="currency"/>
-      <sheetName val="SAP-Referenz"/>
-      <sheetName val="Price book "/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Parameters"/>
       <sheetName val="Cover"/>
@@ -6933,9 +6928,67 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Output--&gt;"/>
+      <sheetName val="Summary"/>
+      <sheetName val="Subs chart"/>
+      <sheetName val="Scenarios_Subs"/>
+      <sheetName val="ARPU chart"/>
+      <sheetName val="Scenarios_Revenue"/>
+      <sheetName val="Inputs--&gt;"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Assumptions"/>
+      <sheetName val="Alg Hist subs"/>
+      <sheetName val="Algeria Subs Projections EMC"/>
+      <sheetName val="Covered Wilayas"/>
+      <sheetName val="Pops per Wilaya"/>
+      <sheetName val="Data"/>
+      <sheetName val="Market calculations--&gt;"/>
+      <sheetName val="MCO"/>
+      <sheetName val="Country potential"/>
+      <sheetName val="Subscribers &amp; Revenue"/>
+      <sheetName val="Backup--&gt;"/>
+      <sheetName val="MCO Back-Up"/>
+      <sheetName val="Elasticity- currently unused"/>
+      <sheetName val="SAP-Referenz"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Discount"/>
       <sheetName val="Parameters"/>
@@ -6982,9 +7035,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Parameters"/>
       <sheetName val="Cover"/>
@@ -7013,7 +7069,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink82.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7058,7 +7114,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink83.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7085,7 +7141,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink84.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7102,9 +7158,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink86.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="template"/>
       <sheetName val="version_information"/>
@@ -7131,7 +7190,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink87.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink86.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7156,7 +7215,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink88.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink87.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7203,7 +7262,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink89.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink88.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7294,64 +7353,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink89.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Output--&gt;"/>
-      <sheetName val="Summary"/>
-      <sheetName val="Subs chart"/>
-      <sheetName val="Scenarios_Subs"/>
-      <sheetName val="ARPU chart"/>
-      <sheetName val="Scenarios_Revenue"/>
-      <sheetName val="Inputs--&gt;"/>
-      <sheetName val="Scenarios"/>
-      <sheetName val="Assumptions"/>
-      <sheetName val="Alg Hist subs"/>
-      <sheetName val="Algeria Subs Projections EMC"/>
-      <sheetName val="Covered Wilayas"/>
-      <sheetName val="Pops per Wilaya"/>
-      <sheetName val="Data"/>
-      <sheetName val="Market calculations--&gt;"/>
-      <sheetName val="MCO"/>
-      <sheetName val="Country potential"/>
-      <sheetName val="Subscribers &amp; Revenue"/>
-      <sheetName val="Backup--&gt;"/>
-      <sheetName val="MCO Back-Up"/>
-      <sheetName val="Elasticity- currently unused"/>
-      <sheetName val="SAP-Referenz"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink90.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="template"/>
       <sheetName val="Project Data"/>
@@ -7368,7 +7375,40 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink91.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="M_Cfg"/>
+      <sheetName val="IsoCode"/>
+      <sheetName val="Input"/>
+      <sheetName val="PD_Data"/>
+      <sheetName val="PD"/>
+      <sheetName val="S_PD"/>
+      <sheetName val="FO"/>
+      <sheetName val="FO_Data"/>
+      <sheetName val="FU"/>
+      <sheetName val="FU_SST"/>
+      <sheetName val="Assumptions"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink90.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7387,9 +7427,12 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink92.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink91.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="规范1"/>
       <sheetName val="规范2"/>
@@ -7404,7 +7447,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink93.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink92.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -7844,7 +7887,7 @@
     <tabColor theme="5" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:H400"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
     <col min="2" max="2" width="7.33203125" customWidth="1"/>
@@ -7856,7 +7899,7 @@
     <col min="8" max="8" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7864,11 +7907,11 @@
       <c r="E1" s="3"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="G2" s="6"/>
     </row>
-    <row r="5" spans="1:8" ht="35.4" customHeight="1"/>
-    <row r="6" spans="1:8">
+    <row r="5" spans="1:8" ht="35.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>0</v>
       </c>
@@ -7879,7 +7922,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>1</v>
       </c>
@@ -7905,7 +7948,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>9</v>
       </c>
@@ -7927,7 +7970,7 @@
       <c r="G8" s="14"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>13</v>
       </c>
@@ -7949,7 +7992,7 @@
       <c r="G9" s="14"/>
       <c r="H9" s="15"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
@@ -7971,7 +8014,7 @@
       <c r="G10" s="14"/>
       <c r="H10" s="15"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>15</v>
       </c>
@@ -7993,7 +8036,7 @@
       <c r="G11" s="14"/>
       <c r="H11" s="15"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>16</v>
       </c>
@@ -8015,7 +8058,7 @@
       <c r="G12" s="14"/>
       <c r="H12" s="15"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
@@ -8037,7 +8080,7 @@
       <c r="G13" s="14"/>
       <c r="H13" s="15"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
@@ -8059,7 +8102,7 @@
       <c r="G14" s="14"/>
       <c r="H14" s="15"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>21</v>
       </c>
@@ -8081,7 +8124,7 @@
       <c r="G15" s="14"/>
       <c r="H15" s="15"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>21</v>
       </c>
@@ -8103,7 +8146,7 @@
       <c r="G16" s="14"/>
       <c r="H16" s="15"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>21</v>
       </c>
@@ -8125,7 +8168,7 @@
       <c r="G17" s="14"/>
       <c r="H17" s="15"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -8147,7 +8190,7 @@
       <c r="G18" s="14"/>
       <c r="H18" s="15"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>25</v>
       </c>
@@ -8169,7 +8212,7 @@
       <c r="G19" s="14"/>
       <c r="H19" s="15"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>25</v>
       </c>
@@ -8191,7 +8234,7 @@
       <c r="G20" s="14"/>
       <c r="H20" s="15"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>25</v>
       </c>
@@ -8217,7 +8260,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -8243,7 +8286,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>25</v>
       </c>
@@ -8267,7 +8310,7 @@
       </c>
       <c r="H23" s="15"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>25</v>
       </c>
@@ -8291,7 +8334,7 @@
       </c>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>25</v>
       </c>
@@ -8313,7 +8356,7 @@
       <c r="G25" s="14"/>
       <c r="H25" s="15"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>25</v>
       </c>
@@ -8335,7 +8378,7 @@
       <c r="G26" s="14"/>
       <c r="H26" s="15"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>32</v>
       </c>
@@ -8357,7 +8400,7 @@
       <c r="G27" s="14"/>
       <c r="H27" s="15"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>32</v>
       </c>
@@ -8379,7 +8422,7 @@
       <c r="G28" s="14"/>
       <c r="H28" s="15"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>32</v>
       </c>
@@ -8401,7 +8444,7 @@
       <c r="G29" s="14"/>
       <c r="H29" s="15"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>32</v>
       </c>
@@ -8423,7 +8466,7 @@
       <c r="G30" s="14"/>
       <c r="H30" s="15"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>33</v>
       </c>
@@ -8445,7 +8488,7 @@
       <c r="G31" s="14"/>
       <c r="H31" s="15"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>33</v>
       </c>
@@ -8467,7 +8510,7 @@
       <c r="G32" s="14"/>
       <c r="H32" s="15"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>33</v>
       </c>
@@ -8489,7 +8532,7 @@
       <c r="G33" s="14"/>
       <c r="H33" s="15"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>33</v>
       </c>
@@ -8511,7 +8554,7 @@
       <c r="G34" s="14"/>
       <c r="H34" s="15"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>34</v>
       </c>
@@ -8533,7 +8576,7 @@
       <c r="G35" s="14"/>
       <c r="H35" s="15"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>34</v>
       </c>
@@ -8555,7 +8598,7 @@
       <c r="G36" s="14"/>
       <c r="H36" s="15"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>37</v>
       </c>
@@ -8566,7 +8609,7 @@
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>38</v>
       </c>
@@ -8589,7 +8632,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
         <v>9</v>
       </c>
@@ -8610,7 +8653,7 @@
       </c>
       <c r="G40" s="21"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
         <v>9</v>
       </c>
@@ -8631,7 +8674,7 @@
       </c>
       <c r="G41" s="21"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>13</v>
       </c>
@@ -8652,7 +8695,7 @@
       </c>
       <c r="G42" s="21"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>13</v>
       </c>
@@ -8673,7 +8716,7 @@
       </c>
       <c r="G43" s="21"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>14</v>
       </c>
@@ -8694,7 +8737,7 @@
       </c>
       <c r="G44" s="21"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>14</v>
       </c>
@@ -8717,7 +8760,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>14</v>
       </c>
@@ -8740,7 +8783,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
         <v>14</v>
       </c>
@@ -8761,7 +8804,7 @@
       </c>
       <c r="G47" s="21"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>15</v>
       </c>
@@ -8782,7 +8825,7 @@
       </c>
       <c r="G48" s="21"/>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
         <v>15</v>
       </c>
@@ -8805,7 +8848,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>15</v>
       </c>
@@ -8828,7 +8871,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="9" t="s">
         <v>15</v>
       </c>
@@ -8849,7 +8892,7 @@
       </c>
       <c r="G51" s="21"/>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>16</v>
       </c>
@@ -8870,7 +8913,7 @@
       </c>
       <c r="G52" s="21"/>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="9" t="s">
         <v>16</v>
       </c>
@@ -8893,7 +8936,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>16</v>
       </c>
@@ -8916,7 +8959,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="9" t="s">
         <v>16</v>
       </c>
@@ -8937,7 +8980,7 @@
       </c>
       <c r="G55" s="21"/>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="9" t="s">
         <v>33</v>
       </c>
@@ -8958,7 +9001,7 @@
       </c>
       <c r="G56" s="14"/>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
         <v>33</v>
       </c>
@@ -8979,7 +9022,7 @@
       </c>
       <c r="G57" s="14"/>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
         <v>33</v>
       </c>
@@ -9000,7 +9043,7 @@
       </c>
       <c r="G58" s="14"/>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
         <v>33</v>
       </c>
@@ -9021,7 +9064,7 @@
       </c>
       <c r="G59" s="14"/>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
         <v>33</v>
       </c>
@@ -9042,7 +9085,7 @@
       </c>
       <c r="G60" s="14"/>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
         <v>33</v>
       </c>
@@ -9063,7 +9106,7 @@
       </c>
       <c r="G61" s="14"/>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
         <v>33</v>
       </c>
@@ -9084,7 +9127,7 @@
       </c>
       <c r="G62" s="14"/>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
         <v>33</v>
       </c>
@@ -9105,7 +9148,7 @@
       </c>
       <c r="G63" s="14"/>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
         <v>33</v>
       </c>
@@ -9126,7 +9169,7 @@
       </c>
       <c r="G64" s="14"/>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
         <v>33</v>
       </c>
@@ -9147,7 +9190,7 @@
       </c>
       <c r="G65" s="14"/>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="9" t="s">
         <v>33</v>
       </c>
@@ -9168,7 +9211,7 @@
       </c>
       <c r="G66" s="14"/>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
         <v>33</v>
       </c>
@@ -9189,7 +9232,7 @@
       </c>
       <c r="G67" s="14"/>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
         <v>33</v>
       </c>
@@ -9210,7 +9253,7 @@
       </c>
       <c r="G68" s="14"/>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
         <v>33</v>
       </c>
@@ -9231,7 +9274,7 @@
       </c>
       <c r="G69" s="14"/>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
         <v>33</v>
       </c>
@@ -9252,7 +9295,7 @@
       </c>
       <c r="G70" s="14"/>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
         <v>33</v>
       </c>
@@ -9273,7 +9316,7 @@
       </c>
       <c r="G71" s="14"/>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
         <v>33</v>
       </c>
@@ -9294,7 +9337,7 @@
       </c>
       <c r="G72" s="14"/>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
         <v>33</v>
       </c>
@@ -9315,7 +9358,7 @@
       </c>
       <c r="G73" s="14"/>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="s">
         <v>33</v>
       </c>
@@ -9336,7 +9379,7 @@
       </c>
       <c r="G74" s="14"/>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
         <v>33</v>
       </c>
@@ -9357,7 +9400,7 @@
       </c>
       <c r="G75" s="14"/>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="9" t="s">
         <v>33</v>
       </c>
@@ -9378,7 +9421,7 @@
       </c>
       <c r="G76" s="14"/>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="9" t="s">
         <v>33</v>
       </c>
@@ -9399,7 +9442,7 @@
       </c>
       <c r="G77" s="14"/>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
         <v>33</v>
       </c>
@@ -9420,7 +9463,7 @@
       </c>
       <c r="G78" s="14"/>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="9" t="s">
         <v>33</v>
       </c>
@@ -9441,7 +9484,7 @@
       </c>
       <c r="G79" s="14"/>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="9" t="s">
         <v>33</v>
       </c>
@@ -9462,7 +9505,7 @@
       </c>
       <c r="G80" s="14"/>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="9" t="s">
         <v>33</v>
       </c>
@@ -9483,7 +9526,7 @@
       </c>
       <c r="G81" s="14"/>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
         <v>33</v>
       </c>
@@ -9504,7 +9547,7 @@
       </c>
       <c r="G82" s="14"/>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
         <v>33</v>
       </c>
@@ -9525,7 +9568,7 @@
       </c>
       <c r="G83" s="14"/>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
         <v>33</v>
       </c>
@@ -9546,7 +9589,7 @@
       </c>
       <c r="G84" s="14"/>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
         <v>33</v>
       </c>
@@ -9567,7 +9610,7 @@
       </c>
       <c r="G85" s="21"/>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="9" t="s">
         <v>33</v>
       </c>
@@ -9588,7 +9631,7 @@
       </c>
       <c r="G86" s="21"/>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="9" t="s">
         <v>33</v>
       </c>
@@ -9611,7 +9654,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="9" t="s">
         <v>33</v>
       </c>
@@ -9634,7 +9677,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="9" t="s">
         <v>33</v>
       </c>
@@ -9657,7 +9700,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="9" t="s">
         <v>33</v>
       </c>
@@ -9680,7 +9723,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="9" t="s">
         <v>33</v>
       </c>
@@ -9703,7 +9746,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="9" t="s">
         <v>33</v>
       </c>
@@ -9726,7 +9769,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="9" t="s">
         <v>33</v>
       </c>
@@ -9749,7 +9792,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="9" t="s">
         <v>33</v>
       </c>
@@ -9772,7 +9815,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="9" t="s">
         <v>33</v>
       </c>
@@ -9795,7 +9838,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="9" t="s">
         <v>33</v>
       </c>
@@ -9818,7 +9861,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="9" t="s">
         <v>33</v>
       </c>
@@ -9841,7 +9884,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="9" t="s">
         <v>33</v>
       </c>
@@ -9864,7 +9907,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="9" t="s">
         <v>33</v>
       </c>
@@ -9887,7 +9930,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
         <v>33</v>
       </c>
@@ -9910,7 +9953,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
         <v>33</v>
       </c>
@@ -9933,7 +9976,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
         <v>33</v>
       </c>
@@ -9956,7 +9999,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="9" t="s">
         <v>33</v>
       </c>
@@ -9979,7 +10022,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="9" t="s">
         <v>33</v>
       </c>
@@ -10002,7 +10045,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="9" t="s">
         <v>33</v>
       </c>
@@ -10025,7 +10068,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="9" t="s">
         <v>33</v>
       </c>
@@ -10048,7 +10091,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="9" t="s">
         <v>33</v>
       </c>
@@ -10071,7 +10114,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="9" t="s">
         <v>33</v>
       </c>
@@ -10094,7 +10137,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="9" t="s">
         <v>33</v>
       </c>
@@ -10117,7 +10160,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="9" t="s">
         <v>33</v>
       </c>
@@ -10140,7 +10183,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="9" t="s">
         <v>33</v>
       </c>
@@ -10163,7 +10206,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="9" t="s">
         <v>33</v>
       </c>
@@ -10186,7 +10229,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="9" t="s">
         <v>33</v>
       </c>
@@ -10209,7 +10252,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="9" t="s">
         <v>33</v>
       </c>
@@ -10232,7 +10275,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="9" t="s">
         <v>33</v>
       </c>
@@ -10255,7 +10298,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="9" t="s">
         <v>33</v>
       </c>
@@ -10278,7 +10321,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="9" t="s">
         <v>33</v>
       </c>
@@ -10299,7 +10342,7 @@
       </c>
       <c r="G117" s="21"/>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="9" t="s">
         <v>17</v>
       </c>
@@ -10320,7 +10363,7 @@
       </c>
       <c r="G118" s="21"/>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="9" t="s">
         <v>17</v>
       </c>
@@ -10341,7 +10384,7 @@
       </c>
       <c r="G119" s="21"/>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="9" t="s">
         <v>17</v>
       </c>
@@ -10362,7 +10405,7 @@
       </c>
       <c r="G120" s="21"/>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="9" t="s">
         <v>17</v>
       </c>
@@ -10383,7 +10426,7 @@
       </c>
       <c r="G121" s="21"/>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="9" t="s">
         <v>17</v>
       </c>
@@ -10404,7 +10447,7 @@
       </c>
       <c r="G122" s="21"/>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="9" t="s">
         <v>17</v>
       </c>
@@ -10425,7 +10468,7 @@
       </c>
       <c r="G123" s="21"/>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="9" t="s">
         <v>17</v>
       </c>
@@ -10446,7 +10489,7 @@
       </c>
       <c r="G124" s="21"/>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="9" t="s">
         <v>17</v>
       </c>
@@ -10467,7 +10510,7 @@
       </c>
       <c r="G125" s="21"/>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="9" t="s">
         <v>17</v>
       </c>
@@ -10488,7 +10531,7 @@
       </c>
       <c r="G126" s="21"/>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="9" t="s">
         <v>17</v>
       </c>
@@ -10509,7 +10552,7 @@
       </c>
       <c r="G127" s="21"/>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="9" t="s">
         <v>17</v>
       </c>
@@ -10530,7 +10573,7 @@
       </c>
       <c r="G128" s="21"/>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="9" t="s">
         <v>17</v>
       </c>
@@ -10551,7 +10594,7 @@
       </c>
       <c r="G129" s="21"/>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="9" t="s">
         <v>17</v>
       </c>
@@ -10572,7 +10615,7 @@
       </c>
       <c r="G130" s="21"/>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="9" t="s">
         <v>17</v>
       </c>
@@ -10593,7 +10636,7 @@
       </c>
       <c r="G131" s="21"/>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="9" t="s">
         <v>17</v>
       </c>
@@ -10614,7 +10657,7 @@
       </c>
       <c r="G132" s="21"/>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="9" t="s">
         <v>17</v>
       </c>
@@ -10635,7 +10678,7 @@
       </c>
       <c r="G133" s="21"/>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="9" t="s">
         <v>17</v>
       </c>
@@ -10656,7 +10699,7 @@
       </c>
       <c r="G134" s="21"/>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="9" t="s">
         <v>17</v>
       </c>
@@ -10677,7 +10720,7 @@
       </c>
       <c r="G135" s="21"/>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="9" t="s">
         <v>17</v>
       </c>
@@ -10698,7 +10741,7 @@
       </c>
       <c r="G136" s="21"/>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="9" t="s">
         <v>17</v>
       </c>
@@ -10719,7 +10762,7 @@
       </c>
       <c r="G137" s="21"/>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="9" t="s">
         <v>17</v>
       </c>
@@ -10740,7 +10783,7 @@
       </c>
       <c r="G138" s="21"/>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="9" t="s">
         <v>168</v>
       </c>
@@ -10761,7 +10804,7 @@
       </c>
       <c r="G139" s="21"/>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="9" t="s">
         <v>168</v>
       </c>
@@ -10782,7 +10825,7 @@
       </c>
       <c r="G140" s="21"/>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="9" t="s">
         <v>168</v>
       </c>
@@ -10803,7 +10846,7 @@
       </c>
       <c r="G141" s="21"/>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="9" t="s">
         <v>168</v>
       </c>
@@ -10824,7 +10867,7 @@
       </c>
       <c r="G142" s="21"/>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="9" t="s">
         <v>168</v>
       </c>
@@ -10845,7 +10888,7 @@
       </c>
       <c r="G143" s="21"/>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="9" t="s">
         <v>168</v>
       </c>
@@ -10866,7 +10909,7 @@
       </c>
       <c r="G144" s="21"/>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="9" t="s">
         <v>168</v>
       </c>
@@ -10887,7 +10930,7 @@
       </c>
       <c r="G145" s="21"/>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="9" t="s">
         <v>168</v>
       </c>
@@ -10908,7 +10951,7 @@
       </c>
       <c r="G146" s="21"/>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="9" t="s">
         <v>168</v>
       </c>
@@ -10929,7 +10972,7 @@
       </c>
       <c r="G147" s="21"/>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="9" t="s">
         <v>168</v>
       </c>
@@ -10950,7 +10993,7 @@
       </c>
       <c r="G148" s="21"/>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="9" t="s">
         <v>168</v>
       </c>
@@ -10971,7 +11014,7 @@
       </c>
       <c r="G149" s="21"/>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="9" t="s">
         <v>168</v>
       </c>
@@ -10992,7 +11035,7 @@
       </c>
       <c r="G150" s="21"/>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="9" t="s">
         <v>168</v>
       </c>
@@ -11013,7 +11056,7 @@
       </c>
       <c r="G151" s="21"/>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="9" t="s">
         <v>168</v>
       </c>
@@ -11034,7 +11077,7 @@
       </c>
       <c r="G152" s="21"/>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="9" t="s">
         <v>168</v>
       </c>
@@ -11055,7 +11098,7 @@
       </c>
       <c r="G153" s="21"/>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="9" t="s">
         <v>168</v>
       </c>
@@ -11076,7 +11119,7 @@
       </c>
       <c r="G154" s="21"/>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="9" t="s">
         <v>168</v>
       </c>
@@ -11097,7 +11140,7 @@
       </c>
       <c r="G155" s="21"/>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="9" t="s">
         <v>168</v>
       </c>
@@ -11118,7 +11161,7 @@
       </c>
       <c r="G156" s="21"/>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="9" t="s">
         <v>168</v>
       </c>
@@ -11139,7 +11182,7 @@
       </c>
       <c r="G157" s="21"/>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="9" t="s">
         <v>168</v>
       </c>
@@ -11160,7 +11203,7 @@
       </c>
       <c r="G158" s="21"/>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="9" t="s">
         <v>21</v>
       </c>
@@ -11181,7 +11224,7 @@
       </c>
       <c r="G159" s="14"/>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="9" t="s">
         <v>21</v>
       </c>
@@ -11202,7 +11245,7 @@
       </c>
       <c r="G160" s="14"/>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="9" t="s">
         <v>21</v>
       </c>
@@ -11223,7 +11266,7 @@
       </c>
       <c r="G161" s="14"/>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="s">
         <v>21</v>
       </c>
@@ -11244,7 +11287,7 @@
       </c>
       <c r="G162" s="14"/>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="9" t="s">
         <v>21</v>
       </c>
@@ -11265,7 +11308,7 @@
       </c>
       <c r="G163" s="14"/>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="9" t="s">
         <v>21</v>
       </c>
@@ -11286,7 +11329,7 @@
       </c>
       <c r="G164" s="14"/>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="9" t="s">
         <v>21</v>
       </c>
@@ -11307,7 +11350,7 @@
       </c>
       <c r="G165" s="14"/>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="9" t="s">
         <v>21</v>
       </c>
@@ -11328,7 +11371,7 @@
       </c>
       <c r="G166" s="14"/>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="9" t="s">
         <v>21</v>
       </c>
@@ -11349,7 +11392,7 @@
       </c>
       <c r="G167" s="14"/>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="9" t="s">
         <v>21</v>
       </c>
@@ -11370,7 +11413,7 @@
       </c>
       <c r="G168" s="14"/>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="9" t="s">
         <v>21</v>
       </c>
@@ -11391,7 +11434,7 @@
       </c>
       <c r="G169" s="14"/>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="9" t="s">
         <v>21</v>
       </c>
@@ -11412,7 +11455,7 @@
       </c>
       <c r="G170" s="14"/>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="9" t="s">
         <v>21</v>
       </c>
@@ -11433,7 +11476,7 @@
       </c>
       <c r="G171" s="14"/>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="9" t="s">
         <v>21</v>
       </c>
@@ -11454,7 +11497,7 @@
       </c>
       <c r="G172" s="14"/>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="9" t="s">
         <v>21</v>
       </c>
@@ -11475,7 +11518,7 @@
       </c>
       <c r="G173" s="14"/>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="9" t="s">
         <v>21</v>
       </c>
@@ -11496,7 +11539,7 @@
       </c>
       <c r="G174" s="14"/>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="9" t="s">
         <v>21</v>
       </c>
@@ -11517,7 +11560,7 @@
       </c>
       <c r="G175" s="14"/>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="9" t="s">
         <v>21</v>
       </c>
@@ -11538,7 +11581,7 @@
       </c>
       <c r="G176" s="14"/>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="9" t="s">
         <v>21</v>
       </c>
@@ -11559,7 +11602,7 @@
       </c>
       <c r="G177" s="14"/>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="9" t="s">
         <v>21</v>
       </c>
@@ -11580,7 +11623,7 @@
       </c>
       <c r="G178" s="14"/>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="9" t="s">
         <v>21</v>
       </c>
@@ -11601,7 +11644,7 @@
       </c>
       <c r="G179" s="14"/>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="9" t="s">
         <v>21</v>
       </c>
@@ -11622,7 +11665,7 @@
       </c>
       <c r="G180" s="14"/>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="9" t="s">
         <v>21</v>
       </c>
@@ -11643,7 +11686,7 @@
       </c>
       <c r="G181" s="14"/>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="9" t="s">
         <v>21</v>
       </c>
@@ -11664,7 +11707,7 @@
       </c>
       <c r="G182" s="14"/>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="9" t="s">
         <v>21</v>
       </c>
@@ -11685,7 +11728,7 @@
       </c>
       <c r="G183" s="14"/>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="9" t="s">
         <v>21</v>
       </c>
@@ -11706,7 +11749,7 @@
       </c>
       <c r="G184" s="14"/>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="9" t="s">
         <v>21</v>
       </c>
@@ -11727,7 +11770,7 @@
       </c>
       <c r="G185" s="14"/>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="9" t="s">
         <v>21</v>
       </c>
@@ -11748,7 +11791,7 @@
       </c>
       <c r="G186" s="14"/>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="9" t="s">
         <v>21</v>
       </c>
@@ -11769,7 +11812,7 @@
       </c>
       <c r="G187" s="14"/>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="9" t="s">
         <v>21</v>
       </c>
@@ -11790,7 +11833,7 @@
       </c>
       <c r="G188" s="21"/>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="9" t="s">
         <v>21</v>
       </c>
@@ -11811,7 +11854,7 @@
       </c>
       <c r="G189" s="21"/>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="9" t="s">
         <v>21</v>
       </c>
@@ -11832,7 +11875,7 @@
       </c>
       <c r="G190" s="21"/>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="9" t="s">
         <v>21</v>
       </c>
@@ -11853,7 +11896,7 @@
       </c>
       <c r="G191" s="21"/>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="9" t="s">
         <v>21</v>
       </c>
@@ -11876,7 +11919,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="9" t="s">
         <v>21</v>
       </c>
@@ -11899,7 +11942,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="9" t="s">
         <v>21</v>
       </c>
@@ -11922,7 +11965,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="9" t="s">
         <v>21</v>
       </c>
@@ -11945,7 +11988,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="9" t="s">
         <v>21</v>
       </c>
@@ -11968,7 +12011,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="9" t="s">
         <v>21</v>
       </c>
@@ -11991,7 +12034,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="9" t="s">
         <v>21</v>
       </c>
@@ -12014,7 +12057,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="9" t="s">
         <v>21</v>
       </c>
@@ -12037,7 +12080,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="9" t="s">
         <v>21</v>
       </c>
@@ -12060,7 +12103,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="9" t="s">
         <v>21</v>
       </c>
@@ -12083,7 +12126,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="9" t="s">
         <v>21</v>
       </c>
@@ -12106,7 +12149,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="9" t="s">
         <v>21</v>
       </c>
@@ -12129,7 +12172,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="204" spans="1:7">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="9" t="s">
         <v>21</v>
       </c>
@@ -12152,7 +12195,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="9" t="s">
         <v>21</v>
       </c>
@@ -12175,7 +12218,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="9" t="s">
         <v>21</v>
       </c>
@@ -12198,7 +12241,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="207" spans="1:7">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="9" t="s">
         <v>21</v>
       </c>
@@ -12221,7 +12264,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="208" spans="1:7">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="9" t="s">
         <v>21</v>
       </c>
@@ -12244,7 +12287,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="9" t="s">
         <v>21</v>
       </c>
@@ -12267,7 +12310,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="9" t="s">
         <v>21</v>
       </c>
@@ -12290,7 +12333,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="9" t="s">
         <v>21</v>
       </c>
@@ -12313,7 +12356,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="9" t="s">
         <v>21</v>
       </c>
@@ -12336,7 +12379,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="9" t="s">
         <v>21</v>
       </c>
@@ -12359,7 +12402,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="9" t="s">
         <v>21</v>
       </c>
@@ -12382,7 +12425,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="9" t="s">
         <v>21</v>
       </c>
@@ -12405,7 +12448,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" s="9" t="s">
         <v>21</v>
       </c>
@@ -12428,7 +12471,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" s="9" t="s">
         <v>21</v>
       </c>
@@ -12451,7 +12494,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="9" t="s">
         <v>21</v>
       </c>
@@ -12474,7 +12517,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="9" t="s">
         <v>21</v>
       </c>
@@ -12497,7 +12540,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="9" t="s">
         <v>21</v>
       </c>
@@ -12520,7 +12563,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="9" t="s">
         <v>21</v>
       </c>
@@ -12543,7 +12586,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="9" t="s">
         <v>21</v>
       </c>
@@ -12564,7 +12607,7 @@
       </c>
       <c r="G222" s="21"/>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" s="9" t="s">
         <v>25</v>
       </c>
@@ -12585,7 +12628,7 @@
       </c>
       <c r="G223" s="14"/>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="9" t="s">
         <v>25</v>
       </c>
@@ -12606,7 +12649,7 @@
       </c>
       <c r="G224" s="14"/>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" s="9" t="s">
         <v>25</v>
       </c>
@@ -12627,7 +12670,7 @@
       </c>
       <c r="G225" s="14"/>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="9" t="s">
         <v>25</v>
       </c>
@@ -12648,7 +12691,7 @@
       </c>
       <c r="G226" s="14"/>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" s="9" t="s">
         <v>25</v>
       </c>
@@ -12669,7 +12712,7 @@
       </c>
       <c r="G227" s="14"/>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="9" t="s">
         <v>25</v>
       </c>
@@ -12690,7 +12733,7 @@
       </c>
       <c r="G228" s="14"/>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" s="9" t="s">
         <v>25</v>
       </c>
@@ -12711,7 +12754,7 @@
       </c>
       <c r="G229" s="14"/>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" s="9" t="s">
         <v>25</v>
       </c>
@@ -12732,7 +12775,7 @@
       </c>
       <c r="G230" s="14"/>
     </row>
-    <row r="231" spans="1:7">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" s="9" t="s">
         <v>25</v>
       </c>
@@ -12753,7 +12796,7 @@
       </c>
       <c r="G231" s="14"/>
     </row>
-    <row r="232" spans="1:7">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" s="9" t="s">
         <v>25</v>
       </c>
@@ -12774,7 +12817,7 @@
       </c>
       <c r="G232" s="14"/>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" s="9" t="s">
         <v>25</v>
       </c>
@@ -12795,7 +12838,7 @@
       </c>
       <c r="G233" s="14"/>
     </row>
-    <row r="234" spans="1:7">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" s="9" t="s">
         <v>25</v>
       </c>
@@ -12816,7 +12859,7 @@
       </c>
       <c r="G234" s="14"/>
     </row>
-    <row r="235" spans="1:7">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" s="9" t="s">
         <v>25</v>
       </c>
@@ -12837,7 +12880,7 @@
       </c>
       <c r="G235" s="14"/>
     </row>
-    <row r="236" spans="1:7">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="9" t="s">
         <v>25</v>
       </c>
@@ -12858,7 +12901,7 @@
       </c>
       <c r="G236" s="14"/>
     </row>
-    <row r="237" spans="1:7">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" s="9" t="s">
         <v>25</v>
       </c>
@@ -12879,7 +12922,7 @@
       </c>
       <c r="G237" s="14"/>
     </row>
-    <row r="238" spans="1:7">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" s="9" t="s">
         <v>25</v>
       </c>
@@ -12900,7 +12943,7 @@
       </c>
       <c r="G238" s="14"/>
     </row>
-    <row r="239" spans="1:7">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="9" t="s">
         <v>25</v>
       </c>
@@ -12921,7 +12964,7 @@
       </c>
       <c r="G239" s="14"/>
     </row>
-    <row r="240" spans="1:7">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" s="9" t="s">
         <v>25</v>
       </c>
@@ -12942,7 +12985,7 @@
       </c>
       <c r="G240" s="14"/>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" s="9" t="s">
         <v>25</v>
       </c>
@@ -12963,7 +13006,7 @@
       </c>
       <c r="G241" s="14"/>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" s="9" t="s">
         <v>25</v>
       </c>
@@ -12984,7 +13027,7 @@
       </c>
       <c r="G242" s="14"/>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" s="9" t="s">
         <v>25</v>
       </c>
@@ -13005,7 +13048,7 @@
       </c>
       <c r="G243" s="14"/>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" s="9" t="s">
         <v>25</v>
       </c>
@@ -13026,7 +13069,7 @@
       </c>
       <c r="G244" s="14"/>
     </row>
-    <row r="245" spans="1:7">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" s="9" t="s">
         <v>25</v>
       </c>
@@ -13047,7 +13090,7 @@
       </c>
       <c r="G245" s="14"/>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" s="9" t="s">
         <v>25</v>
       </c>
@@ -13068,7 +13111,7 @@
       </c>
       <c r="G246" s="14"/>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" s="9" t="s">
         <v>25</v>
       </c>
@@ -13089,7 +13132,7 @@
       </c>
       <c r="G247" s="14"/>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" s="9" t="s">
         <v>25</v>
       </c>
@@ -13110,7 +13153,7 @@
       </c>
       <c r="G248" s="14"/>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" s="9" t="s">
         <v>25</v>
       </c>
@@ -13131,7 +13174,7 @@
       </c>
       <c r="G249" s="14"/>
     </row>
-    <row r="250" spans="1:7">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" s="9" t="s">
         <v>25</v>
       </c>
@@ -13152,7 +13195,7 @@
       </c>
       <c r="G250" s="14"/>
     </row>
-    <row r="251" spans="1:7">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" s="9" t="s">
         <v>25</v>
       </c>
@@ -13173,7 +13216,7 @@
       </c>
       <c r="G251" s="21"/>
     </row>
-    <row r="252" spans="1:7">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" s="9" t="s">
         <v>25</v>
       </c>
@@ -13194,7 +13237,7 @@
       </c>
       <c r="G252" s="21"/>
     </row>
-    <row r="253" spans="1:7">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" s="9" t="s">
         <v>25</v>
       </c>
@@ -13215,7 +13258,7 @@
       </c>
       <c r="G253" s="21"/>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" s="9" t="s">
         <v>25</v>
       </c>
@@ -13236,7 +13279,7 @@
       </c>
       <c r="G254" s="21"/>
     </row>
-    <row r="255" spans="1:7">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" s="9" t="s">
         <v>25</v>
       </c>
@@ -13257,7 +13300,7 @@
       </c>
       <c r="G255" s="21"/>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" s="9" t="s">
         <v>25</v>
       </c>
@@ -13280,7 +13323,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" s="9" t="s">
         <v>25</v>
       </c>
@@ -13303,7 +13346,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" s="9" t="s">
         <v>25</v>
       </c>
@@ -13326,7 +13369,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="259" spans="1:7">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" s="9" t="s">
         <v>25</v>
       </c>
@@ -13349,7 +13392,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" s="9" t="s">
         <v>25</v>
       </c>
@@ -13372,7 +13415,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" s="9" t="s">
         <v>25</v>
       </c>
@@ -13395,7 +13438,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" s="9" t="s">
         <v>25</v>
       </c>
@@ -13418,7 +13461,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" s="9" t="s">
         <v>25</v>
       </c>
@@ -13441,7 +13484,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" s="9" t="s">
         <v>25</v>
       </c>
@@ -13464,7 +13507,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265" s="9" t="s">
         <v>25</v>
       </c>
@@ -13487,7 +13530,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" s="9" t="s">
         <v>25</v>
       </c>
@@ -13510,7 +13553,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" s="9" t="s">
         <v>25</v>
       </c>
@@ -13533,7 +13576,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268" s="9" t="s">
         <v>25</v>
       </c>
@@ -13556,7 +13599,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A269" s="9" t="s">
         <v>25</v>
       </c>
@@ -13579,7 +13622,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A270" s="9" t="s">
         <v>25</v>
       </c>
@@ -13602,7 +13645,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A271" s="9" t="s">
         <v>25</v>
       </c>
@@ -13625,7 +13668,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A272" s="9" t="s">
         <v>25</v>
       </c>
@@ -13648,7 +13691,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" s="9" t="s">
         <v>25</v>
       </c>
@@ -13671,7 +13714,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" s="9" t="s">
         <v>25</v>
       </c>
@@ -13694,7 +13737,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" s="9" t="s">
         <v>25</v>
       </c>
@@ -13717,7 +13760,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" s="9" t="s">
         <v>25</v>
       </c>
@@ -13740,7 +13783,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" s="9" t="s">
         <v>25</v>
       </c>
@@ -13763,7 +13806,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" s="9" t="s">
         <v>25</v>
       </c>
@@ -13786,7 +13829,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" s="9" t="s">
         <v>25</v>
       </c>
@@ -13809,7 +13852,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" s="9" t="s">
         <v>25</v>
       </c>
@@ -13832,7 +13875,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="281" spans="1:7">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" s="9" t="s">
         <v>25</v>
       </c>
@@ -13855,7 +13898,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" s="9" t="s">
         <v>25</v>
       </c>
@@ -13878,7 +13921,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283" s="9" t="s">
         <v>25</v>
       </c>
@@ -13901,7 +13944,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="284" spans="1:7">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" s="9" t="s">
         <v>25</v>
       </c>
@@ -13924,7 +13967,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="285" spans="1:7">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285" s="9" t="s">
         <v>25</v>
       </c>
@@ -13947,7 +13990,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="286" spans="1:7">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" s="9" t="s">
         <v>25</v>
       </c>
@@ -13970,7 +14013,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287" s="9" t="s">
         <v>25</v>
       </c>
@@ -13993,7 +14036,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" s="9" t="s">
         <v>25</v>
       </c>
@@ -14016,7 +14059,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="289" spans="1:7">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" s="9" t="s">
         <v>25</v>
       </c>
@@ -14039,7 +14082,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="290" spans="1:7">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" s="9" t="s">
         <v>25</v>
       </c>
@@ -14062,7 +14105,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="291" spans="1:7">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291" s="9" t="s">
         <v>25</v>
       </c>
@@ -14085,7 +14128,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="292" spans="1:7">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" s="9" t="s">
         <v>25</v>
       </c>
@@ -14108,7 +14151,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="293" spans="1:7">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" s="9" t="s">
         <v>25</v>
       </c>
@@ -14131,7 +14174,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="294" spans="1:7">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" s="9" t="s">
         <v>25</v>
       </c>
@@ -14154,7 +14197,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="295" spans="1:7">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" s="9" t="s">
         <v>25</v>
       </c>
@@ -14175,7 +14218,7 @@
       </c>
       <c r="G295" s="21"/>
     </row>
-    <row r="296" spans="1:7">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" s="9" t="s">
         <v>32</v>
       </c>
@@ -14196,7 +14239,7 @@
       </c>
       <c r="G296" s="14"/>
     </row>
-    <row r="297" spans="1:7">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" s="9" t="s">
         <v>32</v>
       </c>
@@ -14217,7 +14260,7 @@
       </c>
       <c r="G297" s="14"/>
     </row>
-    <row r="298" spans="1:7">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A298" s="9" t="s">
         <v>32</v>
       </c>
@@ -14238,7 +14281,7 @@
       </c>
       <c r="G298" s="14"/>
     </row>
-    <row r="299" spans="1:7">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A299" s="9" t="s">
         <v>32</v>
       </c>
@@ -14259,7 +14302,7 @@
       </c>
       <c r="G299" s="14"/>
     </row>
-    <row r="300" spans="1:7">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A300" s="9" t="s">
         <v>32</v>
       </c>
@@ -14280,7 +14323,7 @@
       </c>
       <c r="G300" s="14"/>
     </row>
-    <row r="301" spans="1:7">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A301" s="9" t="s">
         <v>32</v>
       </c>
@@ -14301,7 +14344,7 @@
       </c>
       <c r="G301" s="14"/>
     </row>
-    <row r="302" spans="1:7">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A302" s="9" t="s">
         <v>32</v>
       </c>
@@ -14322,7 +14365,7 @@
       </c>
       <c r="G302" s="14"/>
     </row>
-    <row r="303" spans="1:7">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A303" s="9" t="s">
         <v>32</v>
       </c>
@@ -14343,7 +14386,7 @@
       </c>
       <c r="G303" s="14"/>
     </row>
-    <row r="304" spans="1:7">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A304" s="9" t="s">
         <v>32</v>
       </c>
@@ -14364,7 +14407,7 @@
       </c>
       <c r="G304" s="14"/>
     </row>
-    <row r="305" spans="1:7">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A305" s="9" t="s">
         <v>32</v>
       </c>
@@ -14385,7 +14428,7 @@
       </c>
       <c r="G305" s="14"/>
     </row>
-    <row r="306" spans="1:7">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A306" s="9" t="s">
         <v>32</v>
       </c>
@@ -14406,7 +14449,7 @@
       </c>
       <c r="G306" s="14"/>
     </row>
-    <row r="307" spans="1:7">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A307" s="9" t="s">
         <v>32</v>
       </c>
@@ -14427,7 +14470,7 @@
       </c>
       <c r="G307" s="14"/>
     </row>
-    <row r="308" spans="1:7">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A308" s="9" t="s">
         <v>32</v>
       </c>
@@ -14448,7 +14491,7 @@
       </c>
       <c r="G308" s="14"/>
     </row>
-    <row r="309" spans="1:7">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A309" s="9" t="s">
         <v>32</v>
       </c>
@@ -14469,7 +14512,7 @@
       </c>
       <c r="G309" s="14"/>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A310" s="9" t="s">
         <v>32</v>
       </c>
@@ -14490,7 +14533,7 @@
       </c>
       <c r="G310" s="14"/>
     </row>
-    <row r="311" spans="1:7">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A311" s="9" t="s">
         <v>32</v>
       </c>
@@ -14511,7 +14554,7 @@
       </c>
       <c r="G311" s="14"/>
     </row>
-    <row r="312" spans="1:7">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A312" s="9" t="s">
         <v>32</v>
       </c>
@@ -14532,7 +14575,7 @@
       </c>
       <c r="G312" s="14"/>
     </row>
-    <row r="313" spans="1:7">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A313" s="9" t="s">
         <v>32</v>
       </c>
@@ -14553,7 +14596,7 @@
       </c>
       <c r="G313" s="14"/>
     </row>
-    <row r="314" spans="1:7">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A314" s="9" t="s">
         <v>32</v>
       </c>
@@ -14574,7 +14617,7 @@
       </c>
       <c r="G314" s="14"/>
     </row>
-    <row r="315" spans="1:7">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A315" s="9" t="s">
         <v>32</v>
       </c>
@@ -14595,7 +14638,7 @@
       </c>
       <c r="G315" s="14"/>
     </row>
-    <row r="316" spans="1:7">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A316" s="9" t="s">
         <v>32</v>
       </c>
@@ -14616,7 +14659,7 @@
       </c>
       <c r="G316" s="14"/>
     </row>
-    <row r="317" spans="1:7">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A317" s="9" t="s">
         <v>32</v>
       </c>
@@ -14637,7 +14680,7 @@
       </c>
       <c r="G317" s="14"/>
     </row>
-    <row r="318" spans="1:7">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A318" s="9" t="s">
         <v>32</v>
       </c>
@@ -14658,7 +14701,7 @@
       </c>
       <c r="G318" s="14"/>
     </row>
-    <row r="319" spans="1:7">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A319" s="9" t="s">
         <v>32</v>
       </c>
@@ -14679,7 +14722,7 @@
       </c>
       <c r="G319" s="14"/>
     </row>
-    <row r="320" spans="1:7">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A320" s="9" t="s">
         <v>32</v>
       </c>
@@ -14700,7 +14743,7 @@
       </c>
       <c r="G320" s="14"/>
     </row>
-    <row r="321" spans="1:7">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A321" s="9" t="s">
         <v>32</v>
       </c>
@@ -14721,7 +14764,7 @@
       </c>
       <c r="G321" s="14"/>
     </row>
-    <row r="322" spans="1:7">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A322" s="9" t="s">
         <v>32</v>
       </c>
@@ -14742,7 +14785,7 @@
       </c>
       <c r="G322" s="14"/>
     </row>
-    <row r="323" spans="1:7">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A323" s="9" t="s">
         <v>32</v>
       </c>
@@ -14763,7 +14806,7 @@
       </c>
       <c r="G323" s="14"/>
     </row>
-    <row r="324" spans="1:7">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A324" s="9" t="s">
         <v>32</v>
       </c>
@@ -14784,7 +14827,7 @@
       </c>
       <c r="G324" s="14"/>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A325" s="9" t="s">
         <v>32</v>
       </c>
@@ -14805,7 +14848,7 @@
       </c>
       <c r="G325" s="14"/>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A326" s="9" t="s">
         <v>32</v>
       </c>
@@ -14826,7 +14869,7 @@
       </c>
       <c r="G326" s="14"/>
     </row>
-    <row r="327" spans="1:7">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A327" s="9" t="s">
         <v>32</v>
       </c>
@@ -14847,7 +14890,7 @@
       </c>
       <c r="G327" s="14"/>
     </row>
-    <row r="328" spans="1:7">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A328" s="9" t="s">
         <v>32</v>
       </c>
@@ -14868,7 +14911,7 @@
       </c>
       <c r="G328" s="14"/>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A329" s="9" t="s">
         <v>32</v>
       </c>
@@ -14889,7 +14932,7 @@
       </c>
       <c r="G329" s="21"/>
     </row>
-    <row r="330" spans="1:7">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A330" s="9" t="s">
         <v>32</v>
       </c>
@@ -14910,7 +14953,7 @@
       </c>
       <c r="G330" s="21"/>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A331" s="9" t="s">
         <v>32</v>
       </c>
@@ -14931,7 +14974,7 @@
       </c>
       <c r="G331" s="21"/>
     </row>
-    <row r="332" spans="1:7">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A332" s="9" t="s">
         <v>32</v>
       </c>
@@ -14952,7 +14995,7 @@
       </c>
       <c r="G332" s="21"/>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A333" s="9" t="s">
         <v>32</v>
       </c>
@@ -14973,7 +15016,7 @@
       </c>
       <c r="G333" s="21"/>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A334" s="9" t="s">
         <v>32</v>
       </c>
@@ -14994,7 +15037,7 @@
       </c>
       <c r="G334" s="21"/>
     </row>
-    <row r="335" spans="1:7">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A335" s="9" t="s">
         <v>32</v>
       </c>
@@ -15015,7 +15058,7 @@
       </c>
       <c r="G335" s="21"/>
     </row>
-    <row r="336" spans="1:7">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A336" s="9" t="s">
         <v>32</v>
       </c>
@@ -15036,7 +15079,7 @@
       </c>
       <c r="G336" s="21"/>
     </row>
-    <row r="337" spans="1:7">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A337" s="9" t="s">
         <v>32</v>
       </c>
@@ -15057,7 +15100,7 @@
       </c>
       <c r="G337" s="21"/>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A338" s="9" t="s">
         <v>32</v>
       </c>
@@ -15078,7 +15121,7 @@
       </c>
       <c r="G338" s="21"/>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A339" s="9" t="s">
         <v>32</v>
       </c>
@@ -15099,7 +15142,7 @@
       </c>
       <c r="G339" s="21"/>
     </row>
-    <row r="340" spans="1:7">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A340" s="9" t="s">
         <v>32</v>
       </c>
@@ -15120,7 +15163,7 @@
       </c>
       <c r="G340" s="21"/>
     </row>
-    <row r="341" spans="1:7">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A341" s="9" t="s">
         <v>32</v>
       </c>
@@ -15141,7 +15184,7 @@
       </c>
       <c r="G341" s="21"/>
     </row>
-    <row r="342" spans="1:7">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A342" s="9" t="s">
         <v>32</v>
       </c>
@@ -15162,7 +15205,7 @@
       </c>
       <c r="G342" s="21"/>
     </row>
-    <row r="343" spans="1:7">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A343" s="9" t="s">
         <v>32</v>
       </c>
@@ -15183,7 +15226,7 @@
       </c>
       <c r="G343" s="21"/>
     </row>
-    <row r="344" spans="1:7">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A344" s="9" t="s">
         <v>32</v>
       </c>
@@ -15204,7 +15247,7 @@
       </c>
       <c r="G344" s="21"/>
     </row>
-    <row r="345" spans="1:7">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A345" s="9" t="s">
         <v>32</v>
       </c>
@@ -15225,7 +15268,7 @@
       </c>
       <c r="G345" s="21"/>
     </row>
-    <row r="346" spans="1:7">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A346" s="9" t="s">
         <v>32</v>
       </c>
@@ -15246,7 +15289,7 @@
       </c>
       <c r="G346" s="21"/>
     </row>
-    <row r="347" spans="1:7">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A347" s="9" t="s">
         <v>32</v>
       </c>
@@ -15267,7 +15310,7 @@
       </c>
       <c r="G347" s="21"/>
     </row>
-    <row r="348" spans="1:7">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A348" s="9" t="s">
         <v>32</v>
       </c>
@@ -15288,7 +15331,7 @@
       </c>
       <c r="G348" s="21"/>
     </row>
-    <row r="349" spans="1:7">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A349" s="9" t="s">
         <v>32</v>
       </c>
@@ -15309,7 +15352,7 @@
       </c>
       <c r="G349" s="21"/>
     </row>
-    <row r="350" spans="1:7">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A350" s="9" t="s">
         <v>32</v>
       </c>
@@ -15330,7 +15373,7 @@
       </c>
       <c r="G350" s="21"/>
     </row>
-    <row r="351" spans="1:7">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A351" s="9" t="s">
         <v>32</v>
       </c>
@@ -15351,7 +15394,7 @@
       </c>
       <c r="G351" s="21"/>
     </row>
-    <row r="352" spans="1:7">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A352" s="9" t="s">
         <v>32</v>
       </c>
@@ -15372,7 +15415,7 @@
       </c>
       <c r="G352" s="21"/>
     </row>
-    <row r="353" spans="1:7">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A353" s="9" t="s">
         <v>32</v>
       </c>
@@ -15393,7 +15436,7 @@
       </c>
       <c r="G353" s="21"/>
     </row>
-    <row r="354" spans="1:7">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A354" s="9" t="s">
         <v>32</v>
       </c>
@@ -15414,7 +15457,7 @@
       </c>
       <c r="G354" s="21"/>
     </row>
-    <row r="355" spans="1:7">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A355" s="9" t="s">
         <v>32</v>
       </c>
@@ -15435,7 +15478,7 @@
       </c>
       <c r="G355" s="21"/>
     </row>
-    <row r="356" spans="1:7">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A356" s="9" t="s">
         <v>32</v>
       </c>
@@ -15456,7 +15499,7 @@
       </c>
       <c r="G356" s="21"/>
     </row>
-    <row r="357" spans="1:7">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A357" s="9" t="s">
         <v>32</v>
       </c>
@@ -15477,7 +15520,7 @@
       </c>
       <c r="G357" s="21"/>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A358" s="9" t="s">
         <v>32</v>
       </c>
@@ -15498,7 +15541,7 @@
       </c>
       <c r="G358" s="21"/>
     </row>
-    <row r="359" spans="1:7">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A359" s="9" t="s">
         <v>34</v>
       </c>
@@ -15519,7 +15562,7 @@
       </c>
       <c r="G359" s="21"/>
     </row>
-    <row r="360" spans="1:7">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A360" s="9" t="s">
         <v>34</v>
       </c>
@@ -15540,7 +15583,7 @@
       </c>
       <c r="G360" s="21"/>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A361" s="9" t="s">
         <v>34</v>
       </c>
@@ -15561,7 +15604,7 @@
       </c>
       <c r="G361" s="21"/>
     </row>
-    <row r="362" spans="1:7">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A362" s="9" t="s">
         <v>34</v>
       </c>
@@ -15582,7 +15625,7 @@
       </c>
       <c r="G362" s="21"/>
     </row>
-    <row r="363" spans="1:7">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A363" s="9" t="s">
         <v>34</v>
       </c>
@@ -15603,7 +15646,7 @@
       </c>
       <c r="G363" s="21"/>
     </row>
-    <row r="364" spans="1:7">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A364" s="9" t="s">
         <v>34</v>
       </c>
@@ -15624,7 +15667,7 @@
       </c>
       <c r="G364" s="21"/>
     </row>
-    <row r="365" spans="1:7">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A365" s="9" t="s">
         <v>34</v>
       </c>
@@ -15645,7 +15688,7 @@
       </c>
       <c r="G365" s="21"/>
     </row>
-    <row r="366" spans="1:7">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A366" s="9" t="s">
         <v>34</v>
       </c>
@@ -15666,7 +15709,7 @@
       </c>
       <c r="G366" s="21"/>
     </row>
-    <row r="367" spans="1:7">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A367" s="9" t="s">
         <v>34</v>
       </c>
@@ -15687,7 +15730,7 @@
       </c>
       <c r="G367" s="21"/>
     </row>
-    <row r="368" spans="1:7">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A368" s="9" t="s">
         <v>34</v>
       </c>
@@ -15708,7 +15751,7 @@
       </c>
       <c r="G368" s="21"/>
     </row>
-    <row r="369" spans="1:7">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A369" s="9" t="s">
         <v>34</v>
       </c>
@@ -15729,7 +15772,7 @@
       </c>
       <c r="G369" s="21"/>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A370" s="9" t="s">
         <v>34</v>
       </c>
@@ -15750,7 +15793,7 @@
       </c>
       <c r="G370" s="21"/>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A371" s="9" t="s">
         <v>34</v>
       </c>
@@ -15771,7 +15814,7 @@
       </c>
       <c r="G371" s="21"/>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A372" s="9" t="s">
         <v>34</v>
       </c>
@@ -15792,7 +15835,7 @@
       </c>
       <c r="G372" s="21"/>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A373" s="9" t="s">
         <v>34</v>
       </c>
@@ -15813,7 +15856,7 @@
       </c>
       <c r="G373" s="21"/>
     </row>
-    <row r="374" spans="1:7">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A374" s="9" t="s">
         <v>34</v>
       </c>
@@ -15834,7 +15877,7 @@
       </c>
       <c r="G374" s="21"/>
     </row>
-    <row r="375" spans="1:7">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A375" s="9" t="s">
         <v>34</v>
       </c>
@@ -15855,7 +15898,7 @@
       </c>
       <c r="G375" s="21"/>
     </row>
-    <row r="376" spans="1:7">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A376" s="9" t="s">
         <v>34</v>
       </c>
@@ -15876,7 +15919,7 @@
       </c>
       <c r="G376" s="21"/>
     </row>
-    <row r="377" spans="1:7">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A377" s="9" t="s">
         <v>34</v>
       </c>
@@ -15897,7 +15940,7 @@
       </c>
       <c r="G377" s="21"/>
     </row>
-    <row r="378" spans="1:7">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A378" s="9" t="s">
         <v>34</v>
       </c>
@@ -15918,7 +15961,7 @@
       </c>
       <c r="G378" s="21"/>
     </row>
-    <row r="379" spans="1:7">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A379" s="9" t="s">
         <v>34</v>
       </c>
@@ -15939,7 +15982,7 @@
       </c>
       <c r="G379" s="21"/>
     </row>
-    <row r="380" spans="1:7">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A380" s="9" t="s">
         <v>34</v>
       </c>
@@ -15960,7 +16003,7 @@
       </c>
       <c r="G380" s="21"/>
     </row>
-    <row r="381" spans="1:7">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A381" s="9" t="s">
         <v>34</v>
       </c>
@@ -15981,7 +16024,7 @@
       </c>
       <c r="G381" s="21"/>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A382" s="9" t="s">
         <v>34</v>
       </c>
@@ -16002,7 +16045,7 @@
       </c>
       <c r="G382" s="21"/>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A383" s="9" t="s">
         <v>34</v>
       </c>
@@ -16023,7 +16066,7 @@
       </c>
       <c r="G383" s="21"/>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A384" s="9" t="s">
         <v>34</v>
       </c>
@@ -16044,7 +16087,7 @@
       </c>
       <c r="G384" s="21"/>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A385" s="9" t="s">
         <v>34</v>
       </c>
@@ -16065,7 +16108,7 @@
       </c>
       <c r="G385" s="21"/>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A386" s="9" t="s">
         <v>34</v>
       </c>
@@ -16086,7 +16129,7 @@
       </c>
       <c r="G386" s="21"/>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A387" s="9" t="s">
         <v>34</v>
       </c>
@@ -16107,7 +16150,7 @@
       </c>
       <c r="G387" s="21"/>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A388" s="9" t="s">
         <v>34</v>
       </c>
@@ -16128,7 +16171,7 @@
       </c>
       <c r="G388" s="21"/>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A389" s="9" t="s">
         <v>34</v>
       </c>
@@ -16149,7 +16192,7 @@
       </c>
       <c r="G389" s="21"/>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A390" s="9" t="s">
         <v>34</v>
       </c>
@@ -16170,7 +16213,7 @@
       </c>
       <c r="G390" s="21"/>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A391" s="9" t="s">
         <v>34</v>
       </c>
@@ -16191,12 +16234,12 @@
       </c>
       <c r="G391" s="21"/>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A393" s="7" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="394" spans="1:7">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A394" s="43" t="s">
         <v>158</v>
       </c>
@@ -16219,7 +16262,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="395" spans="1:7">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A395" s="46" t="s">
         <v>159</v>
       </c>
@@ -16242,7 +16285,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A396" s="46" t="s">
         <v>159</v>
       </c>
@@ -16265,7 +16308,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="397" spans="1:7">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A397" s="46" t="s">
         <v>159</v>
       </c>
@@ -16288,7 +16331,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="398" spans="1:7">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A398" s="46" t="s">
         <v>165</v>
       </c>
@@ -16309,7 +16352,7 @@
       </c>
       <c r="G398" s="50"/>
     </row>
-    <row r="399" spans="1:7">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A399" s="46" t="s">
         <v>165</v>
       </c>
@@ -16330,7 +16373,7 @@
       </c>
       <c r="G399" s="50"/>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A400" s="52"/>
       <c r="B400" s="16"/>
       <c r="C400" s="9"/>

--- a/Info/input/pr_model.xlsx
+++ b/Info/input/pr_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\10265696\Documents\AI Transformation\Skill\create-pr-cd\Info\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AI\Downloads\pr_model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF570C1-379E-4329-8CA7-F92FFFA580D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CA657B-26C0-44D5-BCF0-0A33FD4A272F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="2592" windowWidth="23256" windowHeight="13896" xr2:uid="{089DC7BF-D48F-4FC9-B123-3E33291912E1}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{089DC7BF-D48F-4FC9-B123-3E33291912E1}"/>
   </bookViews>
   <sheets>
     <sheet name="TX Line Item (After 21-Apr 26)" sheetId="1" r:id="rId1"/>
@@ -1755,7 +1755,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2038" uniqueCount="185">
   <si>
     <t>TX Site Survey</t>
   </si>
@@ -2262,6 +2262,55 @@
   </si>
   <si>
     <t>Decom - Relo</t>
+  </si>
+  <si>
+    <t>Jendela TX Migration</t>
+  </si>
+  <si>
+    <t>Jendela Model</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Starlink Dismantle (Return/MRCF included) &amp; Migration</t>
+  </si>
+  <si>
+    <t>Starlink Dismantling with 1 antenna（Cage Top）</t>
+  </si>
+  <si>
+    <t>Packing and return included, Included EHS/CCTV</t>
+  </si>
+  <si>
+    <t>Starlink cut over to Existing MW/IP transmission</t>
+  </si>
+  <si>
+    <t>As-built Document and ATP already included</t>
+  </si>
+  <si>
+    <t>MW Dismantle &amp; MRCF</t>
+  </si>
+  <si>
+    <t>MW Installation</t>
+  </si>
+  <si>
+    <t>Migration from Starlink to MW. All xD sites MW installation by ZTE.
+All Q0xxxx or S0xxxx under xC Jendela project, MW to be installed by Huawei.</t>
+  </si>
+  <si>
+    <t>New Installation</t>
+  </si>
+  <si>
+    <t>Fiber Installation</t>
+  </si>
+  <si>
+    <t>Patching work with seperate mobilization</t>
+  </si>
+  <si>
+    <t>Trip</t>
+  </si>
+  <si>
+    <t>Applicable only for Fiber OB unless TX SOW is BBU Patching</t>
   </si>
 </sst>
 </file>
@@ -2271,7 +2320,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d/mmm/yy;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2572,7 +2621,13 @@
     <cellStyle name="Normal 4 2 2" xfId="4" xr:uid="{AA962A7B-5706-4E11-9052-78D6BBABB481}"/>
     <cellStyle name="常规 116" xfId="3" xr:uid="{D47286A5-C404-4C5F-8EF4-22DB28E47183}"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="29">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3283,9 +3338,6 @@
 <file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="首页说明"/>
       <sheetName val="国家维表"/>
@@ -3989,9 +4041,6 @@
 <file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="RFQ"/>
       <sheetName val="SOW &amp; BOQ"/>
@@ -4138,9 +4187,6 @@
 <file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="BudgetGuide"/>
       <sheetName val="ARCGuide"/>
@@ -4212,9 +4258,6 @@
 <file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="BudgetGuide"/>
       <sheetName val="ARCGuide"/>
@@ -4268,9 +4311,6 @@
 <file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="template"/>
       <sheetName val="version_information"/>
@@ -4595,9 +4635,6 @@
 <file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="INSTRUCTIONS! READ THIS FIRST!!"/>
       <sheetName val="WBS"/>
@@ -4845,9 +4882,6 @@
 <file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="BOE Labor"/>
       <sheetName val="Financials by Month"/>
@@ -5249,9 +5283,6 @@
 <file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Parameters"/>
       <sheetName val="Cover"/>
@@ -5353,9 +5384,6 @@
 <file path=xl/externalLinks/externalLink47.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="DISCOUNT"/>
       <sheetName val="cover"/>
@@ -5385,9 +5413,6 @@
 <file path=xl/externalLinks/externalLink48.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Summary"/>
       <sheetName val="Service(I&amp;C)"/>
@@ -5763,9 +5788,6 @@
 <file path=xl/externalLinks/externalLink56.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Navigation"/>
       <sheetName val="BasicInfo"/>
@@ -5901,9 +5923,6 @@
 <file path=xl/externalLinks/externalLink59.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="ProjectInfo"/>
       <sheetName val="Resource Plan"/>
@@ -5927,9 +5946,6 @@
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="0-Total Summary"/>
       <sheetName val="1-Total Summary"/>
@@ -6021,9 +6037,6 @@
 <file path=xl/externalLinks/externalLink62.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="L2 Site Model"/>
       <sheetName val="Mapping for L3 New&amp;Swap"/>
@@ -6081,9 +6094,6 @@
 <file path=xl/externalLinks/externalLink63.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="INSTRUCTIONS! READ THIS FIRST!!"/>
       <sheetName val="WBS"/>
@@ -6191,9 +6201,6 @@
 <file path=xl/externalLinks/externalLink66.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="BOE Labor"/>
       <sheetName val="Financials by Month"/>
@@ -6416,9 +6423,6 @@
 <file path=xl/externalLinks/externalLink71.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="框架招标预测Frame Bidding Forecast"/>
       <sheetName val="Config"/>
@@ -6607,9 +6611,6 @@
 <file path=xl/externalLinks/externalLink75.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="PopCache"/>
       <sheetName val="BneWorkBookProperties"/>
@@ -6629,9 +6630,6 @@
 <file path=xl/externalLinks/externalLink76.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="P&amp;L"/>
       <sheetName val="Summary by Labor category"/>
@@ -6659,9 +6657,6 @@
 <file path=xl/externalLinks/externalLink77.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Executive summary "/>
       <sheetName val="Executive summary by zone"/>
@@ -6875,9 +6870,6 @@
 <file path=xl/externalLinks/externalLink78.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="SW in keyfile"/>
       <sheetName val="PRC EPL"/>
@@ -6907,9 +6899,6 @@
 <file path=xl/externalLinks/externalLink79.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Parameters"/>
       <sheetName val="Cover"/>
@@ -6986,9 +6975,6 @@
 <file path=xl/externalLinks/externalLink80.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Discount"/>
       <sheetName val="Parameters"/>
@@ -7038,9 +7024,6 @@
 <file path=xl/externalLinks/externalLink81.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Parameters"/>
       <sheetName val="Cover"/>
@@ -7161,9 +7144,6 @@
 <file path=xl/externalLinks/externalLink85.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="template"/>
       <sheetName val="version_information"/>
@@ -7356,9 +7336,6 @@
 <file path=xl/externalLinks/externalLink89.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="template"/>
       <sheetName val="Project Data"/>
@@ -7430,9 +7407,6 @@
 <file path=xl/externalLinks/externalLink91.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="规范1"/>
       <sheetName val="规范2"/>
@@ -7577,49 +7551,66 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{63BE9434-AFC4-4CB4-9E45-994979C6D48E}" name="Table1169" displayName="Table1169" ref="A7:H36" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{63BE9434-AFC4-4CB4-9E45-994979C6D48E}" name="Table1169" displayName="Table1169" ref="A7:H36" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
   <autoFilter ref="A7:H36" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{EC9F81E5-C261-4F84-913A-A8762B1312C9}" name="TSS Model" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{3082E680-9603-4B33-86DF-E70FD7ED2C99}" name="Code" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{A37CA3C1-D74F-485F-BCB7-8DC91B63E87A}" name="Description" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{730F4A6B-FF0F-484F-B58A-7BBE10ACEEFB}" name="Unit" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{8636914A-C6C2-42D8-8FFE-709BAC9BE095}" name="Quantity" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{B76A66B7-2F75-4DA1-87D2-4C4B0C210C18}" name="Rules" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{76A1B753-6759-40D3-985F-AF1ACE921915}" name="Remarks" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{22926371-3F86-47A5-AAC0-948E5FF8B53A}" name="Remarks2" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{EC9F81E5-C261-4F84-913A-A8762B1312C9}" name="TSS Model" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{3082E680-9603-4B33-86DF-E70FD7ED2C99}" name="Code" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{A37CA3C1-D74F-485F-BCB7-8DC91B63E87A}" name="Description" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{730F4A6B-FF0F-484F-B58A-7BBE10ACEEFB}" name="Unit" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{8636914A-C6C2-42D8-8FFE-709BAC9BE095}" name="Quantity" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{B76A66B7-2F75-4DA1-87D2-4C4B0C210C18}" name="Rules" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{76A1B753-6759-40D3-985F-AF1ACE921915}" name="Remarks" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{22926371-3F86-47A5-AAC0-948E5FF8B53A}" name="Remarks2" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E134095E-3A51-4411-AA4E-A7309047E07A}" name="Table12714" displayName="Table12714" ref="A39:G391" totalsRowShown="0" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E134095E-3A51-4411-AA4E-A7309047E07A}" name="Table12714" displayName="Table12714" ref="A39:G391" totalsRowShown="0" dataDxfId="18">
   <autoFilter ref="A39:G391" xr:uid="{00000000-0009-0000-0100-00000C000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{291468C8-FDC2-4D9B-A444-194B3C6EFF3C}" name="TI Model" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{28F275E1-BFCC-4FF5-9C11-521DB87DE68F}" name="Code" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{6B7D0885-7542-4368-A983-8D5BA7CDD68B}" name="Description" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{6BA7A254-0F46-4E60-9904-80E088865BAC}" name="Unit" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{52575437-1240-4117-849D-D4A2CDB3A6B3}" name="Quantity" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{DD56CF5C-CA1B-42E1-8AD5-8AC6C2E320C1}" name="Rules" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{F0C4064A-B968-42EE-B9E0-EF2B0CBF1C01}" name="Remarks" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{291468C8-FDC2-4D9B-A444-194B3C6EFF3C}" name="TI Model" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{28F275E1-BFCC-4FF5-9C11-521DB87DE68F}" name="Code" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{6B7D0885-7542-4368-A983-8D5BA7CDD68B}" name="Description" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{6BA7A254-0F46-4E60-9904-80E088865BAC}" name="Unit" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{52575437-1240-4117-849D-D4A2CDB3A6B3}" name="Quantity" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{DD56CF5C-CA1B-42E1-8AD5-8AC6C2E320C1}" name="Rules" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{F0C4064A-B968-42EE-B9E0-EF2B0CBF1C01}" name="Remarks" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4CD2CA86-7CEE-4CD0-B47C-C641CA0F181E}" name="Table3" displayName="Table3" ref="A394:G399" totalsRowShown="0" headerRowDxfId="8" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4CD2CA86-7CEE-4CD0-B47C-C641CA0F181E}" name="Table3" displayName="Table3" ref="A394:G399" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
   <autoFilter ref="A394:G399" xr:uid="{C921409B-4D8C-4615-9077-350B6EB96C40}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{31A7B6B0-1197-4056-BDD3-94A5636411E4}" name="Add PR Line Item Model" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{CE2CF9A6-DD5F-4820-AEFE-953E73E863E2}" name="Code" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{2040AADD-8DE9-4F3D-A4BA-363DE5796B06}" name="Description" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{EA415442-6911-4DFE-9C10-B3D349AE27D4}" name="Unit" dataDxfId="3" dataCellStyle="常规 116"/>
-    <tableColumn id="5" xr3:uid="{B4571B37-35C9-408F-A519-45BF32359BAE}" name="Quantity" dataDxfId="2" dataCellStyle="常规 116"/>
-    <tableColumn id="6" xr3:uid="{1B1CCC05-126A-4CDF-A4EE-EFE8F7F19828}" name="Rules" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{CF984CE1-29CF-459A-85E5-C220F87AC4EE}" name="Remarks" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{31A7B6B0-1197-4056-BDD3-94A5636411E4}" name="Add PR Line Item Model" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{CE2CF9A6-DD5F-4820-AEFE-953E73E863E2}" name="Code" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{2040AADD-8DE9-4F3D-A4BA-363DE5796B06}" name="Description" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{EA415442-6911-4DFE-9C10-B3D349AE27D4}" name="Unit" dataDxfId="5" dataCellStyle="常规 116"/>
+    <tableColumn id="5" xr3:uid="{B4571B37-35C9-408F-A519-45BF32359BAE}" name="Quantity" dataDxfId="4" dataCellStyle="常规 116"/>
+    <tableColumn id="6" xr3:uid="{1B1CCC05-126A-4CDF-A4EE-EFE8F7F19828}" name="Rules" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{CF984CE1-29CF-459A-85E5-C220F87AC4EE}" name="Remarks" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6FE8D8A9-2777-48E3-9B64-F9F2BBA4F91A}" name="Table4" displayName="Table4" ref="A402:H471" totalsRowShown="0">
+  <autoFilter ref="A402:H471" xr:uid="{6FE8D8A9-2777-48E3-9B64-F9F2BBA4F91A}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{3330CE23-3AFE-41D7-B8D6-611EFE913851}" name="Jendela Model"/>
+    <tableColumn id="2" xr3:uid="{3E3B97D8-46C1-4372-A40D-B5F8DBB7A154}" name="Code"/>
+    <tableColumn id="3" xr3:uid="{53E90165-AA05-4EC1-AD62-48E6797BC1F5}" name="Description"/>
+    <tableColumn id="4" xr3:uid="{6F1F1C8E-2E6C-4102-84C3-4B051DC14973}" name="Unit" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{F49F2E89-596F-47D2-985D-392C5220F6CC}" name="Quantity" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{3A7340F3-DE23-4E2D-9566-CE8D16E69ABF}" name="Rules"/>
+    <tableColumn id="7" xr3:uid="{8C07F447-36CD-4AA5-9E86-A150307F366C}" name="Remarks"/>
+    <tableColumn id="8" xr3:uid="{91AC0ADD-EC3E-4BC9-A6A1-4483B2B59D37}" name="Phase"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7886,20 +7877,20 @@
   <sheetPr>
     <tabColor theme="5" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:H400"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H471"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.44140625" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="57.33203125" customWidth="1"/>
-    <col min="4" max="4" width="9" style="4"/>
-    <col min="5" max="5" width="7.44140625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="4.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7907,11 +7898,11 @@
       <c r="E1" s="3"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="G2" s="6"/>
     </row>
-    <row r="5" spans="1:8" ht="35.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="35.450000000000003" customHeight="1"/>
+    <row r="6" spans="1:8">
       <c r="A6" s="7" t="s">
         <v>0</v>
       </c>
@@ -7922,7 +7913,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7" s="8" t="s">
         <v>1</v>
       </c>
@@ -7948,7 +7939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8" s="9" t="s">
         <v>9</v>
       </c>
@@ -7970,7 +7961,7 @@
       <c r="G8" s="14"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="A9" s="9" t="s">
         <v>13</v>
       </c>
@@ -7992,7 +7983,7 @@
       <c r="G9" s="14"/>
       <c r="H9" s="15"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10" s="9" t="s">
         <v>14</v>
       </c>
@@ -8014,7 +8005,7 @@
       <c r="G10" s="14"/>
       <c r="H10" s="15"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11" s="9" t="s">
         <v>15</v>
       </c>
@@ -8036,7 +8027,7 @@
       <c r="G11" s="14"/>
       <c r="H11" s="15"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12" s="9" t="s">
         <v>16</v>
       </c>
@@ -8058,7 +8049,7 @@
       <c r="G12" s="14"/>
       <c r="H12" s="15"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
@@ -8080,7 +8071,7 @@
       <c r="G13" s="14"/>
       <c r="H13" s="15"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
@@ -8102,7 +8093,7 @@
       <c r="G14" s="14"/>
       <c r="H14" s="15"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15" s="9" t="s">
         <v>21</v>
       </c>
@@ -8124,7 +8115,7 @@
       <c r="G15" s="14"/>
       <c r="H15" s="15"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="A16" s="9" t="s">
         <v>21</v>
       </c>
@@ -8146,7 +8137,7 @@
       <c r="G16" s="14"/>
       <c r="H16" s="15"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8">
       <c r="A17" s="9" t="s">
         <v>21</v>
       </c>
@@ -8168,7 +8159,7 @@
       <c r="G17" s="14"/>
       <c r="H17" s="15"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -8190,7 +8181,7 @@
       <c r="G18" s="14"/>
       <c r="H18" s="15"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8">
       <c r="A19" s="9" t="s">
         <v>25</v>
       </c>
@@ -8212,7 +8203,7 @@
       <c r="G19" s="14"/>
       <c r="H19" s="15"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8">
       <c r="A20" s="9" t="s">
         <v>25</v>
       </c>
@@ -8234,7 +8225,7 @@
       <c r="G20" s="14"/>
       <c r="H20" s="15"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8">
       <c r="A21" s="9" t="s">
         <v>25</v>
       </c>
@@ -8260,7 +8251,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -8286,7 +8277,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8">
       <c r="A23" s="9" t="s">
         <v>25</v>
       </c>
@@ -8310,7 +8301,7 @@
       </c>
       <c r="H23" s="15"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8">
       <c r="A24" s="9" t="s">
         <v>25</v>
       </c>
@@ -8334,7 +8325,7 @@
       </c>
       <c r="H24" s="15"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8">
       <c r="A25" s="9" t="s">
         <v>25</v>
       </c>
@@ -8356,7 +8347,7 @@
       <c r="G25" s="14"/>
       <c r="H25" s="15"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8">
       <c r="A26" s="9" t="s">
         <v>25</v>
       </c>
@@ -8378,7 +8369,7 @@
       <c r="G26" s="14"/>
       <c r="H26" s="15"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8">
       <c r="A27" s="9" t="s">
         <v>32</v>
       </c>
@@ -8400,7 +8391,7 @@
       <c r="G27" s="14"/>
       <c r="H27" s="15"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8">
       <c r="A28" s="9" t="s">
         <v>32</v>
       </c>
@@ -8422,7 +8413,7 @@
       <c r="G28" s="14"/>
       <c r="H28" s="15"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8">
       <c r="A29" s="9" t="s">
         <v>32</v>
       </c>
@@ -8444,7 +8435,7 @@
       <c r="G29" s="14"/>
       <c r="H29" s="15"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8">
       <c r="A30" s="9" t="s">
         <v>32</v>
       </c>
@@ -8466,7 +8457,7 @@
       <c r="G30" s="14"/>
       <c r="H30" s="15"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8">
       <c r="A31" s="9" t="s">
         <v>33</v>
       </c>
@@ -8488,7 +8479,7 @@
       <c r="G31" s="14"/>
       <c r="H31" s="15"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8">
       <c r="A32" s="9" t="s">
         <v>33</v>
       </c>
@@ -8510,7 +8501,7 @@
       <c r="G32" s="14"/>
       <c r="H32" s="15"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8">
       <c r="A33" s="9" t="s">
         <v>33</v>
       </c>
@@ -8532,7 +8523,7 @@
       <c r="G33" s="14"/>
       <c r="H33" s="15"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8">
       <c r="A34" s="9" t="s">
         <v>33</v>
       </c>
@@ -8554,7 +8545,7 @@
       <c r="G34" s="14"/>
       <c r="H34" s="15"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8">
       <c r="A35" s="9" t="s">
         <v>34</v>
       </c>
@@ -8576,7 +8567,7 @@
       <c r="G35" s="14"/>
       <c r="H35" s="15"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8">
       <c r="A36" s="9" t="s">
         <v>34</v>
       </c>
@@ -8598,7 +8589,7 @@
       <c r="G36" s="14"/>
       <c r="H36" s="15"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8">
       <c r="A38" s="7" t="s">
         <v>37</v>
       </c>
@@ -8609,7 +8600,7 @@
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8">
       <c r="A39" s="3" t="s">
         <v>38</v>
       </c>
@@ -8632,7 +8623,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8">
       <c r="A40" s="9" t="s">
         <v>9</v>
       </c>
@@ -8653,7 +8644,7 @@
       </c>
       <c r="G40" s="21"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8">
       <c r="A41" s="9" t="s">
         <v>9</v>
       </c>
@@ -8674,7 +8665,7 @@
       </c>
       <c r="G41" s="21"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8">
       <c r="A42" s="9" t="s">
         <v>13</v>
       </c>
@@ -8695,7 +8686,7 @@
       </c>
       <c r="G42" s="21"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8">
       <c r="A43" s="9" t="s">
         <v>13</v>
       </c>
@@ -8716,7 +8707,7 @@
       </c>
       <c r="G43" s="21"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8">
       <c r="A44" s="9" t="s">
         <v>14</v>
       </c>
@@ -8737,7 +8728,7 @@
       </c>
       <c r="G44" s="21"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8">
       <c r="A45" s="9" t="s">
         <v>14</v>
       </c>
@@ -8760,7 +8751,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8">
       <c r="A46" s="9" t="s">
         <v>14</v>
       </c>
@@ -8783,7 +8774,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8">
       <c r="A47" s="9" t="s">
         <v>14</v>
       </c>
@@ -8804,7 +8795,7 @@
       </c>
       <c r="G47" s="21"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8">
       <c r="A48" s="9" t="s">
         <v>15</v>
       </c>
@@ -8825,7 +8816,7 @@
       </c>
       <c r="G48" s="21"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49" s="9" t="s">
         <v>15</v>
       </c>
@@ -8848,7 +8839,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7">
       <c r="A50" s="9" t="s">
         <v>15</v>
       </c>
@@ -8871,7 +8862,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7">
       <c r="A51" s="9" t="s">
         <v>15</v>
       </c>
@@ -8892,7 +8883,7 @@
       </c>
       <c r="G51" s="21"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7">
       <c r="A52" s="9" t="s">
         <v>16</v>
       </c>
@@ -8913,7 +8904,7 @@
       </c>
       <c r="G52" s="21"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="A53" s="9" t="s">
         <v>16</v>
       </c>
@@ -8936,7 +8927,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7">
       <c r="A54" s="9" t="s">
         <v>16</v>
       </c>
@@ -8959,7 +8950,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7">
       <c r="A55" s="9" t="s">
         <v>16</v>
       </c>
@@ -8980,7 +8971,7 @@
       </c>
       <c r="G55" s="21"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7">
       <c r="A56" s="9" t="s">
         <v>33</v>
       </c>
@@ -9001,7 +8992,7 @@
       </c>
       <c r="G56" s="14"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="A57" s="9" t="s">
         <v>33</v>
       </c>
@@ -9022,7 +9013,7 @@
       </c>
       <c r="G57" s="14"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7">
       <c r="A58" s="9" t="s">
         <v>33</v>
       </c>
@@ -9043,7 +9034,7 @@
       </c>
       <c r="G58" s="14"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7">
       <c r="A59" s="9" t="s">
         <v>33</v>
       </c>
@@ -9064,7 +9055,7 @@
       </c>
       <c r="G59" s="14"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7">
       <c r="A60" s="9" t="s">
         <v>33</v>
       </c>
@@ -9085,7 +9076,7 @@
       </c>
       <c r="G60" s="14"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7">
       <c r="A61" s="9" t="s">
         <v>33</v>
       </c>
@@ -9106,7 +9097,7 @@
       </c>
       <c r="G61" s="14"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7">
       <c r="A62" s="9" t="s">
         <v>33</v>
       </c>
@@ -9127,7 +9118,7 @@
       </c>
       <c r="G62" s="14"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7">
       <c r="A63" s="9" t="s">
         <v>33</v>
       </c>
@@ -9148,7 +9139,7 @@
       </c>
       <c r="G63" s="14"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7">
       <c r="A64" s="9" t="s">
         <v>33</v>
       </c>
@@ -9169,7 +9160,7 @@
       </c>
       <c r="G64" s="14"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7">
       <c r="A65" s="9" t="s">
         <v>33</v>
       </c>
@@ -9190,7 +9181,7 @@
       </c>
       <c r="G65" s="14"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7">
       <c r="A66" s="9" t="s">
         <v>33</v>
       </c>
@@ -9211,7 +9202,7 @@
       </c>
       <c r="G66" s="14"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7">
       <c r="A67" s="9" t="s">
         <v>33</v>
       </c>
@@ -9232,7 +9223,7 @@
       </c>
       <c r="G67" s="14"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7">
       <c r="A68" s="9" t="s">
         <v>33</v>
       </c>
@@ -9253,7 +9244,7 @@
       </c>
       <c r="G68" s="14"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7">
       <c r="A69" s="9" t="s">
         <v>33</v>
       </c>
@@ -9274,7 +9265,7 @@
       </c>
       <c r="G69" s="14"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7">
       <c r="A70" s="9" t="s">
         <v>33</v>
       </c>
@@ -9295,7 +9286,7 @@
       </c>
       <c r="G70" s="14"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7">
       <c r="A71" s="9" t="s">
         <v>33</v>
       </c>
@@ -9316,7 +9307,7 @@
       </c>
       <c r="G71" s="14"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7">
       <c r="A72" s="9" t="s">
         <v>33</v>
       </c>
@@ -9337,7 +9328,7 @@
       </c>
       <c r="G72" s="14"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7">
       <c r="A73" s="9" t="s">
         <v>33</v>
       </c>
@@ -9358,7 +9349,7 @@
       </c>
       <c r="G73" s="14"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7">
       <c r="A74" s="9" t="s">
         <v>33</v>
       </c>
@@ -9379,7 +9370,7 @@
       </c>
       <c r="G74" s="14"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7">
       <c r="A75" s="9" t="s">
         <v>33</v>
       </c>
@@ -9400,7 +9391,7 @@
       </c>
       <c r="G75" s="14"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7">
       <c r="A76" s="9" t="s">
         <v>33</v>
       </c>
@@ -9421,7 +9412,7 @@
       </c>
       <c r="G76" s="14"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7">
       <c r="A77" s="9" t="s">
         <v>33</v>
       </c>
@@ -9442,7 +9433,7 @@
       </c>
       <c r="G77" s="14"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7">
       <c r="A78" s="9" t="s">
         <v>33</v>
       </c>
@@ -9463,7 +9454,7 @@
       </c>
       <c r="G78" s="14"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7">
       <c r="A79" s="9" t="s">
         <v>33</v>
       </c>
@@ -9484,7 +9475,7 @@
       </c>
       <c r="G79" s="14"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7">
       <c r="A80" s="9" t="s">
         <v>33</v>
       </c>
@@ -9505,7 +9496,7 @@
       </c>
       <c r="G80" s="14"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7">
       <c r="A81" s="9" t="s">
         <v>33</v>
       </c>
@@ -9526,7 +9517,7 @@
       </c>
       <c r="G81" s="14"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7">
       <c r="A82" s="9" t="s">
         <v>33</v>
       </c>
@@ -9547,7 +9538,7 @@
       </c>
       <c r="G82" s="14"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7">
       <c r="A83" s="9" t="s">
         <v>33</v>
       </c>
@@ -9568,7 +9559,7 @@
       </c>
       <c r="G83" s="14"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7">
       <c r="A84" s="9" t="s">
         <v>33</v>
       </c>
@@ -9589,7 +9580,7 @@
       </c>
       <c r="G84" s="14"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7">
       <c r="A85" s="9" t="s">
         <v>33</v>
       </c>
@@ -9610,7 +9601,7 @@
       </c>
       <c r="G85" s="21"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7">
       <c r="A86" s="9" t="s">
         <v>33</v>
       </c>
@@ -9631,7 +9622,7 @@
       </c>
       <c r="G86" s="21"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7">
       <c r="A87" s="9" t="s">
         <v>33</v>
       </c>
@@ -9654,7 +9645,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7">
       <c r="A88" s="9" t="s">
         <v>33</v>
       </c>
@@ -9677,7 +9668,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7">
       <c r="A89" s="9" t="s">
         <v>33</v>
       </c>
@@ -9700,7 +9691,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7">
       <c r="A90" s="9" t="s">
         <v>33</v>
       </c>
@@ -9723,7 +9714,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7">
       <c r="A91" s="9" t="s">
         <v>33</v>
       </c>
@@ -9746,7 +9737,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7">
       <c r="A92" s="9" t="s">
         <v>33</v>
       </c>
@@ -9769,7 +9760,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7">
       <c r="A93" s="9" t="s">
         <v>33</v>
       </c>
@@ -9792,7 +9783,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7">
       <c r="A94" s="9" t="s">
         <v>33</v>
       </c>
@@ -9815,7 +9806,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7">
       <c r="A95" s="9" t="s">
         <v>33</v>
       </c>
@@ -9838,7 +9829,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7">
       <c r="A96" s="9" t="s">
         <v>33</v>
       </c>
@@ -9861,7 +9852,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7">
       <c r="A97" s="9" t="s">
         <v>33</v>
       </c>
@@ -9884,7 +9875,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7">
       <c r="A98" s="9" t="s">
         <v>33</v>
       </c>
@@ -9907,7 +9898,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7">
       <c r="A99" s="9" t="s">
         <v>33</v>
       </c>
@@ -9930,7 +9921,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7">
       <c r="A100" s="9" t="s">
         <v>33</v>
       </c>
@@ -9953,7 +9944,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7">
       <c r="A101" s="9" t="s">
         <v>33</v>
       </c>
@@ -9976,7 +9967,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7">
       <c r="A102" s="9" t="s">
         <v>33</v>
       </c>
@@ -9999,7 +9990,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7">
       <c r="A103" s="9" t="s">
         <v>33</v>
       </c>
@@ -10022,7 +10013,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7">
       <c r="A104" s="9" t="s">
         <v>33</v>
       </c>
@@ -10045,7 +10036,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7">
       <c r="A105" s="9" t="s">
         <v>33</v>
       </c>
@@ -10068,7 +10059,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7">
       <c r="A106" s="9" t="s">
         <v>33</v>
       </c>
@@ -10091,7 +10082,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7">
       <c r="A107" s="9" t="s">
         <v>33</v>
       </c>
@@ -10114,7 +10105,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7">
       <c r="A108" s="9" t="s">
         <v>33</v>
       </c>
@@ -10137,7 +10128,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7">
       <c r="A109" s="9" t="s">
         <v>33</v>
       </c>
@@ -10160,7 +10151,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7">
       <c r="A110" s="9" t="s">
         <v>33</v>
       </c>
@@ -10183,7 +10174,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7">
       <c r="A111" s="9" t="s">
         <v>33</v>
       </c>
@@ -10206,7 +10197,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7">
       <c r="A112" s="9" t="s">
         <v>33</v>
       </c>
@@ -10229,7 +10220,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7">
       <c r="A113" s="9" t="s">
         <v>33</v>
       </c>
@@ -10252,7 +10243,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7">
       <c r="A114" s="9" t="s">
         <v>33</v>
       </c>
@@ -10275,7 +10266,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7">
       <c r="A115" s="9" t="s">
         <v>33</v>
       </c>
@@ -10298,7 +10289,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7">
       <c r="A116" s="9" t="s">
         <v>33</v>
       </c>
@@ -10321,7 +10312,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7">
       <c r="A117" s="9" t="s">
         <v>33</v>
       </c>
@@ -10342,7 +10333,7 @@
       </c>
       <c r="G117" s="21"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7">
       <c r="A118" s="9" t="s">
         <v>17</v>
       </c>
@@ -10363,7 +10354,7 @@
       </c>
       <c r="G118" s="21"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7">
       <c r="A119" s="9" t="s">
         <v>17</v>
       </c>
@@ -10384,7 +10375,7 @@
       </c>
       <c r="G119" s="21"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7">
       <c r="A120" s="9" t="s">
         <v>17</v>
       </c>
@@ -10405,7 +10396,7 @@
       </c>
       <c r="G120" s="21"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7">
       <c r="A121" s="9" t="s">
         <v>17</v>
       </c>
@@ -10426,7 +10417,7 @@
       </c>
       <c r="G121" s="21"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7">
       <c r="A122" s="9" t="s">
         <v>17</v>
       </c>
@@ -10447,7 +10438,7 @@
       </c>
       <c r="G122" s="21"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7">
       <c r="A123" s="9" t="s">
         <v>17</v>
       </c>
@@ -10468,7 +10459,7 @@
       </c>
       <c r="G123" s="21"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7">
       <c r="A124" s="9" t="s">
         <v>17</v>
       </c>
@@ -10489,7 +10480,7 @@
       </c>
       <c r="G124" s="21"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7">
       <c r="A125" s="9" t="s">
         <v>17</v>
       </c>
@@ -10510,7 +10501,7 @@
       </c>
       <c r="G125" s="21"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7">
       <c r="A126" s="9" t="s">
         <v>17</v>
       </c>
@@ -10531,7 +10522,7 @@
       </c>
       <c r="G126" s="21"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7">
       <c r="A127" s="9" t="s">
         <v>17</v>
       </c>
@@ -10552,7 +10543,7 @@
       </c>
       <c r="G127" s="21"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7">
       <c r="A128" s="9" t="s">
         <v>17</v>
       </c>
@@ -10573,7 +10564,7 @@
       </c>
       <c r="G128" s="21"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7">
       <c r="A129" s="9" t="s">
         <v>17</v>
       </c>
@@ -10594,7 +10585,7 @@
       </c>
       <c r="G129" s="21"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7">
       <c r="A130" s="9" t="s">
         <v>17</v>
       </c>
@@ -10615,7 +10606,7 @@
       </c>
       <c r="G130" s="21"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7">
       <c r="A131" s="9" t="s">
         <v>17</v>
       </c>
@@ -10636,7 +10627,7 @@
       </c>
       <c r="G131" s="21"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7">
       <c r="A132" s="9" t="s">
         <v>17</v>
       </c>
@@ -10657,7 +10648,7 @@
       </c>
       <c r="G132" s="21"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7">
       <c r="A133" s="9" t="s">
         <v>17</v>
       </c>
@@ -10678,7 +10669,7 @@
       </c>
       <c r="G133" s="21"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7">
       <c r="A134" s="9" t="s">
         <v>17</v>
       </c>
@@ -10699,7 +10690,7 @@
       </c>
       <c r="G134" s="21"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7">
       <c r="A135" s="9" t="s">
         <v>17</v>
       </c>
@@ -10720,7 +10711,7 @@
       </c>
       <c r="G135" s="21"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7">
       <c r="A136" s="9" t="s">
         <v>17</v>
       </c>
@@ -10741,7 +10732,7 @@
       </c>
       <c r="G136" s="21"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7">
       <c r="A137" s="9" t="s">
         <v>17</v>
       </c>
@@ -10762,7 +10753,7 @@
       </c>
       <c r="G137" s="21"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7">
       <c r="A138" s="9" t="s">
         <v>17</v>
       </c>
@@ -10783,7 +10774,7 @@
       </c>
       <c r="G138" s="21"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7">
       <c r="A139" s="9" t="s">
         <v>168</v>
       </c>
@@ -10804,7 +10795,7 @@
       </c>
       <c r="G139" s="21"/>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7">
       <c r="A140" s="9" t="s">
         <v>168</v>
       </c>
@@ -10825,7 +10816,7 @@
       </c>
       <c r="G140" s="21"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7">
       <c r="A141" s="9" t="s">
         <v>168</v>
       </c>
@@ -10846,7 +10837,7 @@
       </c>
       <c r="G141" s="21"/>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7">
       <c r="A142" s="9" t="s">
         <v>168</v>
       </c>
@@ -10867,7 +10858,7 @@
       </c>
       <c r="G142" s="21"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7">
       <c r="A143" s="9" t="s">
         <v>168</v>
       </c>
@@ -10888,7 +10879,7 @@
       </c>
       <c r="G143" s="21"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7">
       <c r="A144" s="9" t="s">
         <v>168</v>
       </c>
@@ -10909,7 +10900,7 @@
       </c>
       <c r="G144" s="21"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7">
       <c r="A145" s="9" t="s">
         <v>168</v>
       </c>
@@ -10930,7 +10921,7 @@
       </c>
       <c r="G145" s="21"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7">
       <c r="A146" s="9" t="s">
         <v>168</v>
       </c>
@@ -10951,7 +10942,7 @@
       </c>
       <c r="G146" s="21"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7">
       <c r="A147" s="9" t="s">
         <v>168</v>
       </c>
@@ -10972,7 +10963,7 @@
       </c>
       <c r="G147" s="21"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7">
       <c r="A148" s="9" t="s">
         <v>168</v>
       </c>
@@ -10993,7 +10984,7 @@
       </c>
       <c r="G148" s="21"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7">
       <c r="A149" s="9" t="s">
         <v>168</v>
       </c>
@@ -11014,7 +11005,7 @@
       </c>
       <c r="G149" s="21"/>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7">
       <c r="A150" s="9" t="s">
         <v>168</v>
       </c>
@@ -11035,7 +11026,7 @@
       </c>
       <c r="G150" s="21"/>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7">
       <c r="A151" s="9" t="s">
         <v>168</v>
       </c>
@@ -11056,7 +11047,7 @@
       </c>
       <c r="G151" s="21"/>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7">
       <c r="A152" s="9" t="s">
         <v>168</v>
       </c>
@@ -11077,7 +11068,7 @@
       </c>
       <c r="G152" s="21"/>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7">
       <c r="A153" s="9" t="s">
         <v>168</v>
       </c>
@@ -11098,7 +11089,7 @@
       </c>
       <c r="G153" s="21"/>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7">
       <c r="A154" s="9" t="s">
         <v>168</v>
       </c>
@@ -11119,7 +11110,7 @@
       </c>
       <c r="G154" s="21"/>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7">
       <c r="A155" s="9" t="s">
         <v>168</v>
       </c>
@@ -11140,7 +11131,7 @@
       </c>
       <c r="G155" s="21"/>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7">
       <c r="A156" s="9" t="s">
         <v>168</v>
       </c>
@@ -11161,7 +11152,7 @@
       </c>
       <c r="G156" s="21"/>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7">
       <c r="A157" s="9" t="s">
         <v>168</v>
       </c>
@@ -11182,7 +11173,7 @@
       </c>
       <c r="G157" s="21"/>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7">
       <c r="A158" s="9" t="s">
         <v>168</v>
       </c>
@@ -11203,7 +11194,7 @@
       </c>
       <c r="G158" s="21"/>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7">
       <c r="A159" s="9" t="s">
         <v>21</v>
       </c>
@@ -11224,7 +11215,7 @@
       </c>
       <c r="G159" s="14"/>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7">
       <c r="A160" s="9" t="s">
         <v>21</v>
       </c>
@@ -11245,7 +11236,7 @@
       </c>
       <c r="G160" s="14"/>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7">
       <c r="A161" s="9" t="s">
         <v>21</v>
       </c>
@@ -11266,7 +11257,7 @@
       </c>
       <c r="G161" s="14"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7">
       <c r="A162" s="9" t="s">
         <v>21</v>
       </c>
@@ -11287,7 +11278,7 @@
       </c>
       <c r="G162" s="14"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7">
       <c r="A163" s="9" t="s">
         <v>21</v>
       </c>
@@ -11308,7 +11299,7 @@
       </c>
       <c r="G163" s="14"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7">
       <c r="A164" s="9" t="s">
         <v>21</v>
       </c>
@@ -11329,7 +11320,7 @@
       </c>
       <c r="G164" s="14"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7">
       <c r="A165" s="9" t="s">
         <v>21</v>
       </c>
@@ -11350,7 +11341,7 @@
       </c>
       <c r="G165" s="14"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7">
       <c r="A166" s="9" t="s">
         <v>21</v>
       </c>
@@ -11371,7 +11362,7 @@
       </c>
       <c r="G166" s="14"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7">
       <c r="A167" s="9" t="s">
         <v>21</v>
       </c>
@@ -11392,7 +11383,7 @@
       </c>
       <c r="G167" s="14"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7">
       <c r="A168" s="9" t="s">
         <v>21</v>
       </c>
@@ -11413,7 +11404,7 @@
       </c>
       <c r="G168" s="14"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7">
       <c r="A169" s="9" t="s">
         <v>21</v>
       </c>
@@ -11434,7 +11425,7 @@
       </c>
       <c r="G169" s="14"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7">
       <c r="A170" s="9" t="s">
         <v>21</v>
       </c>
@@ -11455,7 +11446,7 @@
       </c>
       <c r="G170" s="14"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7">
       <c r="A171" s="9" t="s">
         <v>21</v>
       </c>
@@ -11476,7 +11467,7 @@
       </c>
       <c r="G171" s="14"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7">
       <c r="A172" s="9" t="s">
         <v>21</v>
       </c>
@@ -11497,7 +11488,7 @@
       </c>
       <c r="G172" s="14"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7">
       <c r="A173" s="9" t="s">
         <v>21</v>
       </c>
@@ -11518,7 +11509,7 @@
       </c>
       <c r="G173" s="14"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7">
       <c r="A174" s="9" t="s">
         <v>21</v>
       </c>
@@ -11539,7 +11530,7 @@
       </c>
       <c r="G174" s="14"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7">
       <c r="A175" s="9" t="s">
         <v>21</v>
       </c>
@@ -11560,7 +11551,7 @@
       </c>
       <c r="G175" s="14"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7">
       <c r="A176" s="9" t="s">
         <v>21</v>
       </c>
@@ -11581,7 +11572,7 @@
       </c>
       <c r="G176" s="14"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7">
       <c r="A177" s="9" t="s">
         <v>21</v>
       </c>
@@ -11602,7 +11593,7 @@
       </c>
       <c r="G177" s="14"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7">
       <c r="A178" s="9" t="s">
         <v>21</v>
       </c>
@@ -11623,7 +11614,7 @@
       </c>
       <c r="G178" s="14"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7">
       <c r="A179" s="9" t="s">
         <v>21</v>
       </c>
@@ -11644,7 +11635,7 @@
       </c>
       <c r="G179" s="14"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7">
       <c r="A180" s="9" t="s">
         <v>21</v>
       </c>
@@ -11665,7 +11656,7 @@
       </c>
       <c r="G180" s="14"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7">
       <c r="A181" s="9" t="s">
         <v>21</v>
       </c>
@@ -11686,7 +11677,7 @@
       </c>
       <c r="G181" s="14"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7">
       <c r="A182" s="9" t="s">
         <v>21</v>
       </c>
@@ -11707,7 +11698,7 @@
       </c>
       <c r="G182" s="14"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7">
       <c r="A183" s="9" t="s">
         <v>21</v>
       </c>
@@ -11728,7 +11719,7 @@
       </c>
       <c r="G183" s="14"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7">
       <c r="A184" s="9" t="s">
         <v>21</v>
       </c>
@@ -11749,7 +11740,7 @@
       </c>
       <c r="G184" s="14"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7">
       <c r="A185" s="9" t="s">
         <v>21</v>
       </c>
@@ -11770,7 +11761,7 @@
       </c>
       <c r="G185" s="14"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7">
       <c r="A186" s="9" t="s">
         <v>21</v>
       </c>
@@ -11791,7 +11782,7 @@
       </c>
       <c r="G186" s="14"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7">
       <c r="A187" s="9" t="s">
         <v>21</v>
       </c>
@@ -11812,7 +11803,7 @@
       </c>
       <c r="G187" s="14"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7">
       <c r="A188" s="9" t="s">
         <v>21</v>
       </c>
@@ -11833,7 +11824,7 @@
       </c>
       <c r="G188" s="21"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7">
       <c r="A189" s="9" t="s">
         <v>21</v>
       </c>
@@ -11854,7 +11845,7 @@
       </c>
       <c r="G189" s="21"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7">
       <c r="A190" s="9" t="s">
         <v>21</v>
       </c>
@@ -11875,7 +11866,7 @@
       </c>
       <c r="G190" s="21"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7">
       <c r="A191" s="9" t="s">
         <v>21</v>
       </c>
@@ -11896,7 +11887,7 @@
       </c>
       <c r="G191" s="21"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7">
       <c r="A192" s="9" t="s">
         <v>21</v>
       </c>
@@ -11919,7 +11910,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7">
       <c r="A193" s="9" t="s">
         <v>21</v>
       </c>
@@ -11942,7 +11933,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7">
       <c r="A194" s="9" t="s">
         <v>21</v>
       </c>
@@ -11965,7 +11956,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7">
       <c r="A195" s="9" t="s">
         <v>21</v>
       </c>
@@ -11988,7 +11979,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7">
       <c r="A196" s="9" t="s">
         <v>21</v>
       </c>
@@ -12011,7 +12002,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7">
       <c r="A197" s="9" t="s">
         <v>21</v>
       </c>
@@ -12034,7 +12025,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7">
       <c r="A198" s="9" t="s">
         <v>21</v>
       </c>
@@ -12057,7 +12048,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7">
       <c r="A199" s="9" t="s">
         <v>21</v>
       </c>
@@ -12080,7 +12071,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7">
       <c r="A200" s="9" t="s">
         <v>21</v>
       </c>
@@ -12103,7 +12094,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7">
       <c r="A201" s="9" t="s">
         <v>21</v>
       </c>
@@ -12126,7 +12117,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7">
       <c r="A202" s="9" t="s">
         <v>21</v>
       </c>
@@ -12149,7 +12140,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7">
       <c r="A203" s="9" t="s">
         <v>21</v>
       </c>
@@ -12172,7 +12163,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7">
       <c r="A204" s="9" t="s">
         <v>21</v>
       </c>
@@ -12195,7 +12186,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7">
       <c r="A205" s="9" t="s">
         <v>21</v>
       </c>
@@ -12218,7 +12209,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7">
       <c r="A206" s="9" t="s">
         <v>21</v>
       </c>
@@ -12241,7 +12232,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7">
       <c r="A207" s="9" t="s">
         <v>21</v>
       </c>
@@ -12264,7 +12255,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7">
       <c r="A208" s="9" t="s">
         <v>21</v>
       </c>
@@ -12287,7 +12278,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7">
       <c r="A209" s="9" t="s">
         <v>21</v>
       </c>
@@ -12310,7 +12301,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7">
       <c r="A210" s="9" t="s">
         <v>21</v>
       </c>
@@ -12333,7 +12324,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7">
       <c r="A211" s="9" t="s">
         <v>21</v>
       </c>
@@ -12356,7 +12347,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7">
       <c r="A212" s="9" t="s">
         <v>21</v>
       </c>
@@ -12379,7 +12370,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7">
       <c r="A213" s="9" t="s">
         <v>21</v>
       </c>
@@ -12402,7 +12393,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7">
       <c r="A214" s="9" t="s">
         <v>21</v>
       </c>
@@ -12425,7 +12416,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7">
       <c r="A215" s="9" t="s">
         <v>21</v>
       </c>
@@ -12448,7 +12439,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7">
       <c r="A216" s="9" t="s">
         <v>21</v>
       </c>
@@ -12471,7 +12462,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7">
       <c r="A217" s="9" t="s">
         <v>21</v>
       </c>
@@ -12494,7 +12485,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7">
       <c r="A218" s="9" t="s">
         <v>21</v>
       </c>
@@ -12517,7 +12508,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7">
       <c r="A219" s="9" t="s">
         <v>21</v>
       </c>
@@ -12540,7 +12531,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7">
       <c r="A220" s="9" t="s">
         <v>21</v>
       </c>
@@ -12563,7 +12554,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7">
       <c r="A221" s="9" t="s">
         <v>21</v>
       </c>
@@ -12586,7 +12577,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7">
       <c r="A222" s="9" t="s">
         <v>21</v>
       </c>
@@ -12607,7 +12598,7 @@
       </c>
       <c r="G222" s="21"/>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7">
       <c r="A223" s="9" t="s">
         <v>25</v>
       </c>
@@ -12628,7 +12619,7 @@
       </c>
       <c r="G223" s="14"/>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7">
       <c r="A224" s="9" t="s">
         <v>25</v>
       </c>
@@ -12649,7 +12640,7 @@
       </c>
       <c r="G224" s="14"/>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7">
       <c r="A225" s="9" t="s">
         <v>25</v>
       </c>
@@ -12670,7 +12661,7 @@
       </c>
       <c r="G225" s="14"/>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7">
       <c r="A226" s="9" t="s">
         <v>25</v>
       </c>
@@ -12691,7 +12682,7 @@
       </c>
       <c r="G226" s="14"/>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7">
       <c r="A227" s="9" t="s">
         <v>25</v>
       </c>
@@ -12712,7 +12703,7 @@
       </c>
       <c r="G227" s="14"/>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7">
       <c r="A228" s="9" t="s">
         <v>25</v>
       </c>
@@ -12733,7 +12724,7 @@
       </c>
       <c r="G228" s="14"/>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7">
       <c r="A229" s="9" t="s">
         <v>25</v>
       </c>
@@ -12754,7 +12745,7 @@
       </c>
       <c r="G229" s="14"/>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7">
       <c r="A230" s="9" t="s">
         <v>25</v>
       </c>
@@ -12775,7 +12766,7 @@
       </c>
       <c r="G230" s="14"/>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7">
       <c r="A231" s="9" t="s">
         <v>25</v>
       </c>
@@ -12796,7 +12787,7 @@
       </c>
       <c r="G231" s="14"/>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7">
       <c r="A232" s="9" t="s">
         <v>25</v>
       </c>
@@ -12817,7 +12808,7 @@
       </c>
       <c r="G232" s="14"/>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7">
       <c r="A233" s="9" t="s">
         <v>25</v>
       </c>
@@ -12838,7 +12829,7 @@
       </c>
       <c r="G233" s="14"/>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7">
       <c r="A234" s="9" t="s">
         <v>25</v>
       </c>
@@ -12859,7 +12850,7 @@
       </c>
       <c r="G234" s="14"/>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7">
       <c r="A235" s="9" t="s">
         <v>25</v>
       </c>
@@ -12880,7 +12871,7 @@
       </c>
       <c r="G235" s="14"/>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7">
       <c r="A236" s="9" t="s">
         <v>25</v>
       </c>
@@ -12901,7 +12892,7 @@
       </c>
       <c r="G236" s="14"/>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7">
       <c r="A237" s="9" t="s">
         <v>25</v>
       </c>
@@ -12922,7 +12913,7 @@
       </c>
       <c r="G237" s="14"/>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7">
       <c r="A238" s="9" t="s">
         <v>25</v>
       </c>
@@ -12943,7 +12934,7 @@
       </c>
       <c r="G238" s="14"/>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7">
       <c r="A239" s="9" t="s">
         <v>25</v>
       </c>
@@ -12964,7 +12955,7 @@
       </c>
       <c r="G239" s="14"/>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7">
       <c r="A240" s="9" t="s">
         <v>25</v>
       </c>
@@ -12985,7 +12976,7 @@
       </c>
       <c r="G240" s="14"/>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7">
       <c r="A241" s="9" t="s">
         <v>25</v>
       </c>
@@ -13006,7 +12997,7 @@
       </c>
       <c r="G241" s="14"/>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7">
       <c r="A242" s="9" t="s">
         <v>25</v>
       </c>
@@ -13027,7 +13018,7 @@
       </c>
       <c r="G242" s="14"/>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7">
       <c r="A243" s="9" t="s">
         <v>25</v>
       </c>
@@ -13048,7 +13039,7 @@
       </c>
       <c r="G243" s="14"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7">
       <c r="A244" s="9" t="s">
         <v>25</v>
       </c>
@@ -13069,7 +13060,7 @@
       </c>
       <c r="G244" s="14"/>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7">
       <c r="A245" s="9" t="s">
         <v>25</v>
       </c>
@@ -13090,7 +13081,7 @@
       </c>
       <c r="G245" s="14"/>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7">
       <c r="A246" s="9" t="s">
         <v>25</v>
       </c>
@@ -13111,7 +13102,7 @@
       </c>
       <c r="G246" s="14"/>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7">
       <c r="A247" s="9" t="s">
         <v>25</v>
       </c>
@@ -13132,7 +13123,7 @@
       </c>
       <c r="G247" s="14"/>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7">
       <c r="A248" s="9" t="s">
         <v>25</v>
       </c>
@@ -13153,7 +13144,7 @@
       </c>
       <c r="G248" s="14"/>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7">
       <c r="A249" s="9" t="s">
         <v>25</v>
       </c>
@@ -13174,7 +13165,7 @@
       </c>
       <c r="G249" s="14"/>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7">
       <c r="A250" s="9" t="s">
         <v>25</v>
       </c>
@@ -13195,7 +13186,7 @@
       </c>
       <c r="G250" s="14"/>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7">
       <c r="A251" s="9" t="s">
         <v>25</v>
       </c>
@@ -13216,7 +13207,7 @@
       </c>
       <c r="G251" s="21"/>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7">
       <c r="A252" s="9" t="s">
         <v>25</v>
       </c>
@@ -13237,7 +13228,7 @@
       </c>
       <c r="G252" s="21"/>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7">
       <c r="A253" s="9" t="s">
         <v>25</v>
       </c>
@@ -13258,7 +13249,7 @@
       </c>
       <c r="G253" s="21"/>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7">
       <c r="A254" s="9" t="s">
         <v>25</v>
       </c>
@@ -13279,7 +13270,7 @@
       </c>
       <c r="G254" s="21"/>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7">
       <c r="A255" s="9" t="s">
         <v>25</v>
       </c>
@@ -13300,7 +13291,7 @@
       </c>
       <c r="G255" s="21"/>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7">
       <c r="A256" s="9" t="s">
         <v>25</v>
       </c>
@@ -13323,7 +13314,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7">
       <c r="A257" s="9" t="s">
         <v>25</v>
       </c>
@@ -13346,7 +13337,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7">
       <c r="A258" s="9" t="s">
         <v>25</v>
       </c>
@@ -13369,7 +13360,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7">
       <c r="A259" s="9" t="s">
         <v>25</v>
       </c>
@@ -13392,7 +13383,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7">
       <c r="A260" s="9" t="s">
         <v>25</v>
       </c>
@@ -13415,7 +13406,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7">
       <c r="A261" s="9" t="s">
         <v>25</v>
       </c>
@@ -13438,7 +13429,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7">
       <c r="A262" s="9" t="s">
         <v>25</v>
       </c>
@@ -13461,7 +13452,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7">
       <c r="A263" s="9" t="s">
         <v>25</v>
       </c>
@@ -13484,7 +13475,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7">
       <c r="A264" s="9" t="s">
         <v>25</v>
       </c>
@@ -13507,7 +13498,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7">
       <c r="A265" s="9" t="s">
         <v>25</v>
       </c>
@@ -13530,7 +13521,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7">
       <c r="A266" s="9" t="s">
         <v>25</v>
       </c>
@@ -13553,7 +13544,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7">
       <c r="A267" s="9" t="s">
         <v>25</v>
       </c>
@@ -13576,7 +13567,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:7">
       <c r="A268" s="9" t="s">
         <v>25</v>
       </c>
@@ -13599,7 +13590,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:7">
       <c r="A269" s="9" t="s">
         <v>25</v>
       </c>
@@ -13622,7 +13613,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:7">
       <c r="A270" s="9" t="s">
         <v>25</v>
       </c>
@@ -13645,7 +13636,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:7">
       <c r="A271" s="9" t="s">
         <v>25</v>
       </c>
@@ -13668,7 +13659,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:7">
       <c r="A272" s="9" t="s">
         <v>25</v>
       </c>
@@ -13691,7 +13682,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7">
       <c r="A273" s="9" t="s">
         <v>25</v>
       </c>
@@ -13714,7 +13705,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7">
       <c r="A274" s="9" t="s">
         <v>25</v>
       </c>
@@ -13737,7 +13728,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7">
       <c r="A275" s="9" t="s">
         <v>25</v>
       </c>
@@ -13760,7 +13751,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7">
       <c r="A276" s="9" t="s">
         <v>25</v>
       </c>
@@ -13783,7 +13774,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7">
       <c r="A277" s="9" t="s">
         <v>25</v>
       </c>
@@ -13806,7 +13797,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7">
       <c r="A278" s="9" t="s">
         <v>25</v>
       </c>
@@ -13829,7 +13820,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7">
       <c r="A279" s="9" t="s">
         <v>25</v>
       </c>
@@ -13852,7 +13843,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7">
       <c r="A280" s="9" t="s">
         <v>25</v>
       </c>
@@ -13875,7 +13866,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7">
       <c r="A281" s="9" t="s">
         <v>25</v>
       </c>
@@ -13898,7 +13889,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7">
       <c r="A282" s="9" t="s">
         <v>25</v>
       </c>
@@ -13921,7 +13912,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7">
       <c r="A283" s="9" t="s">
         <v>25</v>
       </c>
@@ -13944,7 +13935,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7">
       <c r="A284" s="9" t="s">
         <v>25</v>
       </c>
@@ -13967,7 +13958,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7">
       <c r="A285" s="9" t="s">
         <v>25</v>
       </c>
@@ -13990,7 +13981,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7">
       <c r="A286" s="9" t="s">
         <v>25</v>
       </c>
@@ -14013,7 +14004,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7">
       <c r="A287" s="9" t="s">
         <v>25</v>
       </c>
@@ -14036,7 +14027,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7">
       <c r="A288" s="9" t="s">
         <v>25</v>
       </c>
@@ -14059,7 +14050,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:7">
       <c r="A289" s="9" t="s">
         <v>25</v>
       </c>
@@ -14082,7 +14073,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:7">
       <c r="A290" s="9" t="s">
         <v>25</v>
       </c>
@@ -14105,7 +14096,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:7">
       <c r="A291" s="9" t="s">
         <v>25</v>
       </c>
@@ -14128,7 +14119,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:7">
       <c r="A292" s="9" t="s">
         <v>25</v>
       </c>
@@ -14151,7 +14142,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:7">
       <c r="A293" s="9" t="s">
         <v>25</v>
       </c>
@@ -14174,7 +14165,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:7">
       <c r="A294" s="9" t="s">
         <v>25</v>
       </c>
@@ -14197,7 +14188,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:7">
       <c r="A295" s="9" t="s">
         <v>25</v>
       </c>
@@ -14218,7 +14209,7 @@
       </c>
       <c r="G295" s="21"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:7">
       <c r="A296" s="9" t="s">
         <v>32</v>
       </c>
@@ -14239,7 +14230,7 @@
       </c>
       <c r="G296" s="14"/>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:7">
       <c r="A297" s="9" t="s">
         <v>32</v>
       </c>
@@ -14260,7 +14251,7 @@
       </c>
       <c r="G297" s="14"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:7">
       <c r="A298" s="9" t="s">
         <v>32</v>
       </c>
@@ -14281,7 +14272,7 @@
       </c>
       <c r="G298" s="14"/>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:7">
       <c r="A299" s="9" t="s">
         <v>32</v>
       </c>
@@ -14302,7 +14293,7 @@
       </c>
       <c r="G299" s="14"/>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:7">
       <c r="A300" s="9" t="s">
         <v>32</v>
       </c>
@@ -14323,7 +14314,7 @@
       </c>
       <c r="G300" s="14"/>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:7">
       <c r="A301" s="9" t="s">
         <v>32</v>
       </c>
@@ -14344,7 +14335,7 @@
       </c>
       <c r="G301" s="14"/>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:7">
       <c r="A302" s="9" t="s">
         <v>32</v>
       </c>
@@ -14365,7 +14356,7 @@
       </c>
       <c r="G302" s="14"/>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:7">
       <c r="A303" s="9" t="s">
         <v>32</v>
       </c>
@@ -14386,7 +14377,7 @@
       </c>
       <c r="G303" s="14"/>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:7">
       <c r="A304" s="9" t="s">
         <v>32</v>
       </c>
@@ -14407,7 +14398,7 @@
       </c>
       <c r="G304" s="14"/>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:7">
       <c r="A305" s="9" t="s">
         <v>32</v>
       </c>
@@ -14428,7 +14419,7 @@
       </c>
       <c r="G305" s="14"/>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:7">
       <c r="A306" s="9" t="s">
         <v>32</v>
       </c>
@@ -14449,7 +14440,7 @@
       </c>
       <c r="G306" s="14"/>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:7">
       <c r="A307" s="9" t="s">
         <v>32</v>
       </c>
@@ -14470,7 +14461,7 @@
       </c>
       <c r="G307" s="14"/>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:7">
       <c r="A308" s="9" t="s">
         <v>32</v>
       </c>
@@ -14491,7 +14482,7 @@
       </c>
       <c r="G308" s="14"/>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:7">
       <c r="A309" s="9" t="s">
         <v>32</v>
       </c>
@@ -14512,7 +14503,7 @@
       </c>
       <c r="G309" s="14"/>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:7">
       <c r="A310" s="9" t="s">
         <v>32</v>
       </c>
@@ -14533,7 +14524,7 @@
       </c>
       <c r="G310" s="14"/>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:7">
       <c r="A311" s="9" t="s">
         <v>32</v>
       </c>
@@ -14554,7 +14545,7 @@
       </c>
       <c r="G311" s="14"/>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:7">
       <c r="A312" s="9" t="s">
         <v>32</v>
       </c>
@@ -14575,7 +14566,7 @@
       </c>
       <c r="G312" s="14"/>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:7">
       <c r="A313" s="9" t="s">
         <v>32</v>
       </c>
@@ -14596,7 +14587,7 @@
       </c>
       <c r="G313" s="14"/>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:7">
       <c r="A314" s="9" t="s">
         <v>32</v>
       </c>
@@ -14617,7 +14608,7 @@
       </c>
       <c r="G314" s="14"/>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:7">
       <c r="A315" s="9" t="s">
         <v>32</v>
       </c>
@@ -14638,7 +14629,7 @@
       </c>
       <c r="G315" s="14"/>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:7">
       <c r="A316" s="9" t="s">
         <v>32</v>
       </c>
@@ -14659,7 +14650,7 @@
       </c>
       <c r="G316" s="14"/>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:7">
       <c r="A317" s="9" t="s">
         <v>32</v>
       </c>
@@ -14680,7 +14671,7 @@
       </c>
       <c r="G317" s="14"/>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:7">
       <c r="A318" s="9" t="s">
         <v>32</v>
       </c>
@@ -14701,7 +14692,7 @@
       </c>
       <c r="G318" s="14"/>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:7">
       <c r="A319" s="9" t="s">
         <v>32</v>
       </c>
@@ -14722,7 +14713,7 @@
       </c>
       <c r="G319" s="14"/>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:7">
       <c r="A320" s="9" t="s">
         <v>32</v>
       </c>
@@ -14743,7 +14734,7 @@
       </c>
       <c r="G320" s="14"/>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:7">
       <c r="A321" s="9" t="s">
         <v>32</v>
       </c>
@@ -14764,7 +14755,7 @@
       </c>
       <c r="G321" s="14"/>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:7">
       <c r="A322" s="9" t="s">
         <v>32</v>
       </c>
@@ -14785,7 +14776,7 @@
       </c>
       <c r="G322" s="14"/>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:7">
       <c r="A323" s="9" t="s">
         <v>32</v>
       </c>
@@ -14806,7 +14797,7 @@
       </c>
       <c r="G323" s="14"/>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:7">
       <c r="A324" s="9" t="s">
         <v>32</v>
       </c>
@@ -14827,7 +14818,7 @@
       </c>
       <c r="G324" s="14"/>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:7">
       <c r="A325" s="9" t="s">
         <v>32</v>
       </c>
@@ -14848,7 +14839,7 @@
       </c>
       <c r="G325" s="14"/>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:7">
       <c r="A326" s="9" t="s">
         <v>32</v>
       </c>
@@ -14869,7 +14860,7 @@
       </c>
       <c r="G326" s="14"/>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:7">
       <c r="A327" s="9" t="s">
         <v>32</v>
       </c>
@@ -14890,7 +14881,7 @@
       </c>
       <c r="G327" s="14"/>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7">
       <c r="A328" s="9" t="s">
         <v>32</v>
       </c>
@@ -14911,7 +14902,7 @@
       </c>
       <c r="G328" s="14"/>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7">
       <c r="A329" s="9" t="s">
         <v>32</v>
       </c>
@@ -14932,7 +14923,7 @@
       </c>
       <c r="G329" s="21"/>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7">
       <c r="A330" s="9" t="s">
         <v>32</v>
       </c>
@@ -14953,7 +14944,7 @@
       </c>
       <c r="G330" s="21"/>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7">
       <c r="A331" s="9" t="s">
         <v>32</v>
       </c>
@@ -14974,7 +14965,7 @@
       </c>
       <c r="G331" s="21"/>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7">
       <c r="A332" s="9" t="s">
         <v>32</v>
       </c>
@@ -14995,7 +14986,7 @@
       </c>
       <c r="G332" s="21"/>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7">
       <c r="A333" s="9" t="s">
         <v>32</v>
       </c>
@@ -15016,7 +15007,7 @@
       </c>
       <c r="G333" s="21"/>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7">
       <c r="A334" s="9" t="s">
         <v>32</v>
       </c>
@@ -15037,7 +15028,7 @@
       </c>
       <c r="G334" s="21"/>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7">
       <c r="A335" s="9" t="s">
         <v>32</v>
       </c>
@@ -15058,7 +15049,7 @@
       </c>
       <c r="G335" s="21"/>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7">
       <c r="A336" s="9" t="s">
         <v>32</v>
       </c>
@@ -15079,7 +15070,7 @@
       </c>
       <c r="G336" s="21"/>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7">
       <c r="A337" s="9" t="s">
         <v>32</v>
       </c>
@@ -15100,7 +15091,7 @@
       </c>
       <c r="G337" s="21"/>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7">
       <c r="A338" s="9" t="s">
         <v>32</v>
       </c>
@@ -15121,7 +15112,7 @@
       </c>
       <c r="G338" s="21"/>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7">
       <c r="A339" s="9" t="s">
         <v>32</v>
       </c>
@@ -15142,7 +15133,7 @@
       </c>
       <c r="G339" s="21"/>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7">
       <c r="A340" s="9" t="s">
         <v>32</v>
       </c>
@@ -15163,7 +15154,7 @@
       </c>
       <c r="G340" s="21"/>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7">
       <c r="A341" s="9" t="s">
         <v>32</v>
       </c>
@@ -15184,7 +15175,7 @@
       </c>
       <c r="G341" s="21"/>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7">
       <c r="A342" s="9" t="s">
         <v>32</v>
       </c>
@@ -15205,7 +15196,7 @@
       </c>
       <c r="G342" s="21"/>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7">
       <c r="A343" s="9" t="s">
         <v>32</v>
       </c>
@@ -15226,7 +15217,7 @@
       </c>
       <c r="G343" s="21"/>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7">
       <c r="A344" s="9" t="s">
         <v>32</v>
       </c>
@@ -15247,7 +15238,7 @@
       </c>
       <c r="G344" s="21"/>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7">
       <c r="A345" s="9" t="s">
         <v>32</v>
       </c>
@@ -15268,7 +15259,7 @@
       </c>
       <c r="G345" s="21"/>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7">
       <c r="A346" s="9" t="s">
         <v>32</v>
       </c>
@@ -15289,7 +15280,7 @@
       </c>
       <c r="G346" s="21"/>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7">
       <c r="A347" s="9" t="s">
         <v>32</v>
       </c>
@@ -15310,7 +15301,7 @@
       </c>
       <c r="G347" s="21"/>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7">
       <c r="A348" s="9" t="s">
         <v>32</v>
       </c>
@@ -15331,7 +15322,7 @@
       </c>
       <c r="G348" s="21"/>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7">
       <c r="A349" s="9" t="s">
         <v>32</v>
       </c>
@@ -15352,7 +15343,7 @@
       </c>
       <c r="G349" s="21"/>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7">
       <c r="A350" s="9" t="s">
         <v>32</v>
       </c>
@@ -15373,7 +15364,7 @@
       </c>
       <c r="G350" s="21"/>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7">
       <c r="A351" s="9" t="s">
         <v>32</v>
       </c>
@@ -15394,7 +15385,7 @@
       </c>
       <c r="G351" s="21"/>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7">
       <c r="A352" s="9" t="s">
         <v>32</v>
       </c>
@@ -15415,7 +15406,7 @@
       </c>
       <c r="G352" s="21"/>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:7">
       <c r="A353" s="9" t="s">
         <v>32</v>
       </c>
@@ -15436,7 +15427,7 @@
       </c>
       <c r="G353" s="21"/>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:7">
       <c r="A354" s="9" t="s">
         <v>32</v>
       </c>
@@ -15457,7 +15448,7 @@
       </c>
       <c r="G354" s="21"/>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:7">
       <c r="A355" s="9" t="s">
         <v>32</v>
       </c>
@@ -15478,7 +15469,7 @@
       </c>
       <c r="G355" s="21"/>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:7">
       <c r="A356" s="9" t="s">
         <v>32</v>
       </c>
@@ -15499,7 +15490,7 @@
       </c>
       <c r="G356" s="21"/>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:7">
       <c r="A357" s="9" t="s">
         <v>32</v>
       </c>
@@ -15520,7 +15511,7 @@
       </c>
       <c r="G357" s="21"/>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:7">
       <c r="A358" s="9" t="s">
         <v>32</v>
       </c>
@@ -15541,7 +15532,7 @@
       </c>
       <c r="G358" s="21"/>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:7">
       <c r="A359" s="9" t="s">
         <v>34</v>
       </c>
@@ -15562,7 +15553,7 @@
       </c>
       <c r="G359" s="21"/>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:7">
       <c r="A360" s="9" t="s">
         <v>34</v>
       </c>
@@ -15583,7 +15574,7 @@
       </c>
       <c r="G360" s="21"/>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:7">
       <c r="A361" s="9" t="s">
         <v>34</v>
       </c>
@@ -15604,7 +15595,7 @@
       </c>
       <c r="G361" s="21"/>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:7">
       <c r="A362" s="9" t="s">
         <v>34</v>
       </c>
@@ -15625,7 +15616,7 @@
       </c>
       <c r="G362" s="21"/>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:7">
       <c r="A363" s="9" t="s">
         <v>34</v>
       </c>
@@ -15646,7 +15637,7 @@
       </c>
       <c r="G363" s="21"/>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:7">
       <c r="A364" s="9" t="s">
         <v>34</v>
       </c>
@@ -15667,7 +15658,7 @@
       </c>
       <c r="G364" s="21"/>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:7">
       <c r="A365" s="9" t="s">
         <v>34</v>
       </c>
@@ -15688,7 +15679,7 @@
       </c>
       <c r="G365" s="21"/>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:7">
       <c r="A366" s="9" t="s">
         <v>34</v>
       </c>
@@ -15709,7 +15700,7 @@
       </c>
       <c r="G366" s="21"/>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:7">
       <c r="A367" s="9" t="s">
         <v>34</v>
       </c>
@@ -15730,7 +15721,7 @@
       </c>
       <c r="G367" s="21"/>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:7">
       <c r="A368" s="9" t="s">
         <v>34</v>
       </c>
@@ -15751,7 +15742,7 @@
       </c>
       <c r="G368" s="21"/>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:7">
       <c r="A369" s="9" t="s">
         <v>34</v>
       </c>
@@ -15772,7 +15763,7 @@
       </c>
       <c r="G369" s="21"/>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:7">
       <c r="A370" s="9" t="s">
         <v>34</v>
       </c>
@@ -15793,7 +15784,7 @@
       </c>
       <c r="G370" s="21"/>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:7">
       <c r="A371" s="9" t="s">
         <v>34</v>
       </c>
@@ -15814,7 +15805,7 @@
       </c>
       <c r="G371" s="21"/>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:7">
       <c r="A372" s="9" t="s">
         <v>34</v>
       </c>
@@ -15835,7 +15826,7 @@
       </c>
       <c r="G372" s="21"/>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:7">
       <c r="A373" s="9" t="s">
         <v>34</v>
       </c>
@@ -15856,7 +15847,7 @@
       </c>
       <c r="G373" s="21"/>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:7">
       <c r="A374" s="9" t="s">
         <v>34</v>
       </c>
@@ -15877,7 +15868,7 @@
       </c>
       <c r="G374" s="21"/>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:7">
       <c r="A375" s="9" t="s">
         <v>34</v>
       </c>
@@ -15898,7 +15889,7 @@
       </c>
       <c r="G375" s="21"/>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:7">
       <c r="A376" s="9" t="s">
         <v>34</v>
       </c>
@@ -15919,7 +15910,7 @@
       </c>
       <c r="G376" s="21"/>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:7">
       <c r="A377" s="9" t="s">
         <v>34</v>
       </c>
@@ -15940,7 +15931,7 @@
       </c>
       <c r="G377" s="21"/>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:7">
       <c r="A378" s="9" t="s">
         <v>34</v>
       </c>
@@ -15961,7 +15952,7 @@
       </c>
       <c r="G378" s="21"/>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:7">
       <c r="A379" s="9" t="s">
         <v>34</v>
       </c>
@@ -15982,7 +15973,7 @@
       </c>
       <c r="G379" s="21"/>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:7">
       <c r="A380" s="9" t="s">
         <v>34</v>
       </c>
@@ -16003,7 +15994,7 @@
       </c>
       <c r="G380" s="21"/>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:7">
       <c r="A381" s="9" t="s">
         <v>34</v>
       </c>
@@ -16024,7 +16015,7 @@
       </c>
       <c r="G381" s="21"/>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:7">
       <c r="A382" s="9" t="s">
         <v>34</v>
       </c>
@@ -16045,7 +16036,7 @@
       </c>
       <c r="G382" s="21"/>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:7">
       <c r="A383" s="9" t="s">
         <v>34</v>
       </c>
@@ -16066,7 +16057,7 @@
       </c>
       <c r="G383" s="21"/>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:7">
       <c r="A384" s="9" t="s">
         <v>34</v>
       </c>
@@ -16087,7 +16078,7 @@
       </c>
       <c r="G384" s="21"/>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:7">
       <c r="A385" s="9" t="s">
         <v>34</v>
       </c>
@@ -16108,7 +16099,7 @@
       </c>
       <c r="G385" s="21"/>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:7">
       <c r="A386" s="9" t="s">
         <v>34</v>
       </c>
@@ -16129,7 +16120,7 @@
       </c>
       <c r="G386" s="21"/>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:7">
       <c r="A387" s="9" t="s">
         <v>34</v>
       </c>
@@ -16150,7 +16141,7 @@
       </c>
       <c r="G387" s="21"/>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:7">
       <c r="A388" s="9" t="s">
         <v>34</v>
       </c>
@@ -16171,7 +16162,7 @@
       </c>
       <c r="G388" s="21"/>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:7">
       <c r="A389" s="9" t="s">
         <v>34</v>
       </c>
@@ -16192,7 +16183,7 @@
       </c>
       <c r="G389" s="21"/>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:7">
       <c r="A390" s="9" t="s">
         <v>34</v>
       </c>
@@ -16213,7 +16204,7 @@
       </c>
       <c r="G390" s="21"/>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:7">
       <c r="A391" s="9" t="s">
         <v>34</v>
       </c>
@@ -16234,12 +16225,12 @@
       </c>
       <c r="G391" s="21"/>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:7">
       <c r="A393" s="7" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:7">
       <c r="A394" s="43" t="s">
         <v>158</v>
       </c>
@@ -16262,7 +16253,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:7">
       <c r="A395" s="46" t="s">
         <v>159</v>
       </c>
@@ -16285,7 +16276,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:7">
       <c r="A396" s="46" t="s">
         <v>159</v>
       </c>
@@ -16308,7 +16299,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:7">
       <c r="A397" s="46" t="s">
         <v>159</v>
       </c>
@@ -16331,7 +16322,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:7">
       <c r="A398" s="46" t="s">
         <v>165</v>
       </c>
@@ -16352,7 +16343,7 @@
       </c>
       <c r="G398" s="50"/>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:7">
       <c r="A399" s="46" t="s">
         <v>165</v>
       </c>
@@ -16373,7 +16364,7 @@
       </c>
       <c r="G399" s="50"/>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:7">
       <c r="A400" s="52"/>
       <c r="B400" s="16"/>
       <c r="C400" s="9"/>
@@ -16382,19 +16373,1641 @@
       <c r="F400" s="14"/>
       <c r="G400" s="53"/>
     </row>
+    <row r="401" spans="1:8">
+      <c r="A401" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8">
+      <c r="A402" t="s">
+        <v>170</v>
+      </c>
+      <c r="B402" t="s">
+        <v>2</v>
+      </c>
+      <c r="C402" t="s">
+        <v>3</v>
+      </c>
+      <c r="D402" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E402" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F402" t="s">
+        <v>6</v>
+      </c>
+      <c r="G402" t="s">
+        <v>7</v>
+      </c>
+      <c r="H402" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8">
+      <c r="A403" t="s">
+        <v>172</v>
+      </c>
+      <c r="B403">
+        <v>350000597850</v>
+      </c>
+      <c r="C403" t="s">
+        <v>173</v>
+      </c>
+      <c r="D403" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E403" s="5">
+        <v>1</v>
+      </c>
+      <c r="F403" t="s">
+        <v>12</v>
+      </c>
+      <c r="G403" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8">
+      <c r="A404" t="s">
+        <v>172</v>
+      </c>
+      <c r="B404">
+        <v>350000597852</v>
+      </c>
+      <c r="C404" t="s">
+        <v>175</v>
+      </c>
+      <c r="D404" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E404" s="5">
+        <v>1</v>
+      </c>
+      <c r="F404" t="s">
+        <v>12</v>
+      </c>
+      <c r="G404" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8">
+      <c r="A405" t="s">
+        <v>177</v>
+      </c>
+      <c r="B405">
+        <v>350000589232</v>
+      </c>
+      <c r="C405" t="s">
+        <v>81</v>
+      </c>
+      <c r="D405" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E405" s="5">
+        <v>1</v>
+      </c>
+      <c r="F405" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8">
+      <c r="A406" t="s">
+        <v>177</v>
+      </c>
+      <c r="B406">
+        <v>350000589241</v>
+      </c>
+      <c r="C406" t="s">
+        <v>84</v>
+      </c>
+      <c r="D406" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E406" s="5">
+        <v>1</v>
+      </c>
+      <c r="F406" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8">
+      <c r="A407" t="s">
+        <v>177</v>
+      </c>
+      <c r="B407">
+        <v>350000589242</v>
+      </c>
+      <c r="C407" t="s">
+        <v>85</v>
+      </c>
+      <c r="D407" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E407" s="5">
+        <v>1</v>
+      </c>
+      <c r="F407" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8">
+      <c r="A408" t="s">
+        <v>177</v>
+      </c>
+      <c r="B408">
+        <v>350000589243</v>
+      </c>
+      <c r="C408" t="s">
+        <v>86</v>
+      </c>
+      <c r="D408" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E408" s="5">
+        <v>1</v>
+      </c>
+      <c r="F408" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8">
+      <c r="A409" t="s">
+        <v>177</v>
+      </c>
+      <c r="B409">
+        <v>350000589244</v>
+      </c>
+      <c r="C409" t="s">
+        <v>87</v>
+      </c>
+      <c r="D409" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E409" s="5">
+        <v>1</v>
+      </c>
+      <c r="F409" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8">
+      <c r="A410" t="s">
+        <v>177</v>
+      </c>
+      <c r="B410">
+        <v>350000589253</v>
+      </c>
+      <c r="C410" t="s">
+        <v>88</v>
+      </c>
+      <c r="D410" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E410" s="5">
+        <v>1</v>
+      </c>
+      <c r="F410" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8">
+      <c r="A411" t="s">
+        <v>177</v>
+      </c>
+      <c r="B411">
+        <v>350000589254</v>
+      </c>
+      <c r="C411" t="s">
+        <v>89</v>
+      </c>
+      <c r="D411" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E411" s="5">
+        <v>1</v>
+      </c>
+      <c r="F411" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8">
+      <c r="A412" t="s">
+        <v>177</v>
+      </c>
+      <c r="B412">
+        <v>350000589255</v>
+      </c>
+      <c r="C412" t="s">
+        <v>90</v>
+      </c>
+      <c r="D412" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E412" s="5">
+        <v>1</v>
+      </c>
+      <c r="F412" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8">
+      <c r="A413" t="s">
+        <v>177</v>
+      </c>
+      <c r="B413">
+        <v>350000589256</v>
+      </c>
+      <c r="C413" t="s">
+        <v>91</v>
+      </c>
+      <c r="D413" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E413" s="5">
+        <v>1</v>
+      </c>
+      <c r="F413" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8">
+      <c r="A414" t="s">
+        <v>177</v>
+      </c>
+      <c r="B414">
+        <v>350000589263</v>
+      </c>
+      <c r="C414" t="s">
+        <v>92</v>
+      </c>
+      <c r="D414" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E414" s="5">
+        <v>1</v>
+      </c>
+      <c r="F414" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8">
+      <c r="A415" t="s">
+        <v>177</v>
+      </c>
+      <c r="B415">
+        <v>350000589264</v>
+      </c>
+      <c r="C415" t="s">
+        <v>93</v>
+      </c>
+      <c r="D415" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E415" s="5">
+        <v>1</v>
+      </c>
+      <c r="F415" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8">
+      <c r="A416" t="s">
+        <v>177</v>
+      </c>
+      <c r="B416">
+        <v>350000589265</v>
+      </c>
+      <c r="C416" t="s">
+        <v>94</v>
+      </c>
+      <c r="D416" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E416" s="5">
+        <v>1</v>
+      </c>
+      <c r="F416" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6">
+      <c r="A417" t="s">
+        <v>177</v>
+      </c>
+      <c r="B417">
+        <v>350000589272</v>
+      </c>
+      <c r="C417" t="s">
+        <v>95</v>
+      </c>
+      <c r="D417" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E417" s="5">
+        <v>1</v>
+      </c>
+      <c r="F417" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6">
+      <c r="A418" t="s">
+        <v>177</v>
+      </c>
+      <c r="B418">
+        <v>350000589273</v>
+      </c>
+      <c r="C418" t="s">
+        <v>96</v>
+      </c>
+      <c r="D418" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E418" s="5">
+        <v>1</v>
+      </c>
+      <c r="F418" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6">
+      <c r="A419" t="s">
+        <v>177</v>
+      </c>
+      <c r="B419">
+        <v>350000589274</v>
+      </c>
+      <c r="C419" t="s">
+        <v>97</v>
+      </c>
+      <c r="D419" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E419" s="5">
+        <v>1</v>
+      </c>
+      <c r="F419" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6">
+      <c r="A420" t="s">
+        <v>177</v>
+      </c>
+      <c r="B420">
+        <v>350000589281</v>
+      </c>
+      <c r="C420" t="s">
+        <v>98</v>
+      </c>
+      <c r="D420" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E420" s="5">
+        <v>1</v>
+      </c>
+      <c r="F420" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6">
+      <c r="A421" t="s">
+        <v>177</v>
+      </c>
+      <c r="B421">
+        <v>350000589282</v>
+      </c>
+      <c r="C421" t="s">
+        <v>99</v>
+      </c>
+      <c r="D421" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E421" s="5">
+        <v>1</v>
+      </c>
+      <c r="F421" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6">
+      <c r="A422" t="s">
+        <v>177</v>
+      </c>
+      <c r="B422">
+        <v>350000589283</v>
+      </c>
+      <c r="C422" t="s">
+        <v>100</v>
+      </c>
+      <c r="D422" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E422" s="5">
+        <v>1</v>
+      </c>
+      <c r="F422" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6">
+      <c r="A423" t="s">
+        <v>177</v>
+      </c>
+      <c r="B423">
+        <v>350000589306</v>
+      </c>
+      <c r="C423" t="s">
+        <v>101</v>
+      </c>
+      <c r="D423" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E423" s="5">
+        <v>1</v>
+      </c>
+      <c r="F423" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6">
+      <c r="A424" t="s">
+        <v>177</v>
+      </c>
+      <c r="B424">
+        <v>350000589307</v>
+      </c>
+      <c r="C424" t="s">
+        <v>102</v>
+      </c>
+      <c r="D424" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E424" s="5">
+        <v>1</v>
+      </c>
+      <c r="F424" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6">
+      <c r="A425" t="s">
+        <v>177</v>
+      </c>
+      <c r="B425">
+        <v>350000589308</v>
+      </c>
+      <c r="C425" t="s">
+        <v>103</v>
+      </c>
+      <c r="D425" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E425" s="5">
+        <v>1</v>
+      </c>
+      <c r="F425" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6">
+      <c r="A426" t="s">
+        <v>177</v>
+      </c>
+      <c r="B426">
+        <v>350000589309</v>
+      </c>
+      <c r="C426" t="s">
+        <v>104</v>
+      </c>
+      <c r="D426" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E426" s="5">
+        <v>1</v>
+      </c>
+      <c r="F426" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6">
+      <c r="A427" t="s">
+        <v>177</v>
+      </c>
+      <c r="B427">
+        <v>350000589310</v>
+      </c>
+      <c r="C427" t="s">
+        <v>105</v>
+      </c>
+      <c r="D427" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E427" s="5">
+        <v>1</v>
+      </c>
+      <c r="F427" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6">
+      <c r="A428" t="s">
+        <v>177</v>
+      </c>
+      <c r="B428">
+        <v>350000589311</v>
+      </c>
+      <c r="C428" t="s">
+        <v>106</v>
+      </c>
+      <c r="D428" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E428" s="5">
+        <v>1</v>
+      </c>
+      <c r="F428" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6">
+      <c r="A429" t="s">
+        <v>177</v>
+      </c>
+      <c r="B429">
+        <v>350000589312</v>
+      </c>
+      <c r="C429" t="s">
+        <v>107</v>
+      </c>
+      <c r="D429" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E429" s="5">
+        <v>1</v>
+      </c>
+      <c r="F429" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6">
+      <c r="A430" t="s">
+        <v>177</v>
+      </c>
+      <c r="B430">
+        <v>350000589313</v>
+      </c>
+      <c r="C430" t="s">
+        <v>108</v>
+      </c>
+      <c r="D430" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E430" s="5">
+        <v>1</v>
+      </c>
+      <c r="F430" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6">
+      <c r="A431" t="s">
+        <v>177</v>
+      </c>
+      <c r="B431">
+        <v>350000589314</v>
+      </c>
+      <c r="C431" t="s">
+        <v>109</v>
+      </c>
+      <c r="D431" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E431" s="5">
+        <v>1</v>
+      </c>
+      <c r="F431" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="432" spans="1:6">
+      <c r="A432" t="s">
+        <v>177</v>
+      </c>
+      <c r="B432">
+        <v>350000589315</v>
+      </c>
+      <c r="C432" t="s">
+        <v>110</v>
+      </c>
+      <c r="D432" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E432" s="5">
+        <v>1</v>
+      </c>
+      <c r="F432" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8">
+      <c r="A433" t="s">
+        <v>177</v>
+      </c>
+      <c r="B433">
+        <v>350000589316</v>
+      </c>
+      <c r="C433" t="s">
+        <v>111</v>
+      </c>
+      <c r="D433" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E433" s="5">
+        <v>1</v>
+      </c>
+      <c r="F433" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8">
+      <c r="A434" t="s">
+        <v>177</v>
+      </c>
+      <c r="B434">
+        <v>350001095413</v>
+      </c>
+      <c r="C434" t="s">
+        <v>153</v>
+      </c>
+      <c r="D434" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E434" s="5">
+        <v>1</v>
+      </c>
+      <c r="F434" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8">
+      <c r="A435" t="s">
+        <v>177</v>
+      </c>
+      <c r="B435">
+        <v>350001095414</v>
+      </c>
+      <c r="C435" t="s">
+        <v>154</v>
+      </c>
+      <c r="D435" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E435" s="5">
+        <v>1</v>
+      </c>
+      <c r="F435" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8">
+      <c r="A436" t="s">
+        <v>177</v>
+      </c>
+      <c r="B436">
+        <v>350001095415</v>
+      </c>
+      <c r="C436" t="s">
+        <v>155</v>
+      </c>
+      <c r="D436" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E436" s="5">
+        <v>1</v>
+      </c>
+      <c r="F436" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8">
+      <c r="A437" t="s">
+        <v>177</v>
+      </c>
+      <c r="B437">
+        <v>350001095416</v>
+      </c>
+      <c r="C437" t="s">
+        <v>156</v>
+      </c>
+      <c r="D437" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E437" s="5">
+        <v>1</v>
+      </c>
+      <c r="F437" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8">
+      <c r="A438" t="s">
+        <v>178</v>
+      </c>
+      <c r="B438">
+        <v>350000214911</v>
+      </c>
+      <c r="C438" t="s">
+        <v>46</v>
+      </c>
+      <c r="D438" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E438" s="5">
+        <v>1</v>
+      </c>
+      <c r="F438" t="s">
+        <v>47</v>
+      </c>
+      <c r="G438" t="s">
+        <v>179</v>
+      </c>
+      <c r="H438" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8">
+      <c r="A439" t="s">
+        <v>178</v>
+      </c>
+      <c r="B439">
+        <v>350000214920</v>
+      </c>
+      <c r="C439" t="s">
+        <v>48</v>
+      </c>
+      <c r="D439" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E439" s="5">
+        <v>1</v>
+      </c>
+      <c r="F439" t="s">
+        <v>47</v>
+      </c>
+      <c r="G439" t="s">
+        <v>179</v>
+      </c>
+      <c r="H439" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8">
+      <c r="A440" t="s">
+        <v>178</v>
+      </c>
+      <c r="B440">
+        <v>350000214921</v>
+      </c>
+      <c r="C440" t="s">
+        <v>49</v>
+      </c>
+      <c r="D440" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E440" s="5">
+        <v>1</v>
+      </c>
+      <c r="F440" t="s">
+        <v>47</v>
+      </c>
+      <c r="G440" t="s">
+        <v>179</v>
+      </c>
+      <c r="H440" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8">
+      <c r="A441" t="s">
+        <v>178</v>
+      </c>
+      <c r="B441">
+        <v>350000214922</v>
+      </c>
+      <c r="C441" t="s">
+        <v>50</v>
+      </c>
+      <c r="D441" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E441" s="5">
+        <v>1</v>
+      </c>
+      <c r="F441" t="s">
+        <v>47</v>
+      </c>
+      <c r="G441" t="s">
+        <v>179</v>
+      </c>
+      <c r="H441" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8">
+      <c r="A442" t="s">
+        <v>178</v>
+      </c>
+      <c r="B442">
+        <v>350000214923</v>
+      </c>
+      <c r="C442" t="s">
+        <v>51</v>
+      </c>
+      <c r="D442" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E442" s="5">
+        <v>1</v>
+      </c>
+      <c r="F442" t="s">
+        <v>47</v>
+      </c>
+      <c r="G442" t="s">
+        <v>179</v>
+      </c>
+      <c r="H442" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8">
+      <c r="A443" t="s">
+        <v>178</v>
+      </c>
+      <c r="B443">
+        <v>350000475874</v>
+      </c>
+      <c r="C443" t="s">
+        <v>52</v>
+      </c>
+      <c r="D443" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E443" s="5">
+        <v>1</v>
+      </c>
+      <c r="F443" t="s">
+        <v>47</v>
+      </c>
+      <c r="G443" t="s">
+        <v>179</v>
+      </c>
+      <c r="H443" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8">
+      <c r="A444" t="s">
+        <v>178</v>
+      </c>
+      <c r="B444">
+        <v>350000475875</v>
+      </c>
+      <c r="C444" t="s">
+        <v>53</v>
+      </c>
+      <c r="D444" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E444" s="5">
+        <v>1</v>
+      </c>
+      <c r="F444" t="s">
+        <v>47</v>
+      </c>
+      <c r="G444" t="s">
+        <v>179</v>
+      </c>
+      <c r="H444" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8">
+      <c r="A445" t="s">
+        <v>178</v>
+      </c>
+      <c r="B445">
+        <v>350000475876</v>
+      </c>
+      <c r="C445" t="s">
+        <v>54</v>
+      </c>
+      <c r="D445" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E445" s="5">
+        <v>1</v>
+      </c>
+      <c r="F445" t="s">
+        <v>47</v>
+      </c>
+      <c r="G445" t="s">
+        <v>179</v>
+      </c>
+      <c r="H445" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8">
+      <c r="A446" t="s">
+        <v>178</v>
+      </c>
+      <c r="B446">
+        <v>350000475877</v>
+      </c>
+      <c r="C446" t="s">
+        <v>55</v>
+      </c>
+      <c r="D446" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E446" s="5">
+        <v>1</v>
+      </c>
+      <c r="F446" t="s">
+        <v>47</v>
+      </c>
+      <c r="G446" t="s">
+        <v>179</v>
+      </c>
+      <c r="H446" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8">
+      <c r="A447" t="s">
+        <v>178</v>
+      </c>
+      <c r="B447">
+        <v>350000214930</v>
+      </c>
+      <c r="C447" t="s">
+        <v>56</v>
+      </c>
+      <c r="D447" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E447" s="5">
+        <v>1</v>
+      </c>
+      <c r="F447" t="s">
+        <v>47</v>
+      </c>
+      <c r="G447" t="s">
+        <v>179</v>
+      </c>
+      <c r="H447" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8">
+      <c r="A448" t="s">
+        <v>178</v>
+      </c>
+      <c r="B448">
+        <v>350000214931</v>
+      </c>
+      <c r="C448" t="s">
+        <v>57</v>
+      </c>
+      <c r="D448" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E448" s="5">
+        <v>1</v>
+      </c>
+      <c r="F448" t="s">
+        <v>47</v>
+      </c>
+      <c r="G448" t="s">
+        <v>179</v>
+      </c>
+      <c r="H448" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8">
+      <c r="A449" t="s">
+        <v>178</v>
+      </c>
+      <c r="B449">
+        <v>350000214932</v>
+      </c>
+      <c r="C449" t="s">
+        <v>58</v>
+      </c>
+      <c r="D449" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E449" s="5">
+        <v>1</v>
+      </c>
+      <c r="F449" t="s">
+        <v>47</v>
+      </c>
+      <c r="G449" t="s">
+        <v>179</v>
+      </c>
+      <c r="H449" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8">
+      <c r="A450" t="s">
+        <v>178</v>
+      </c>
+      <c r="B450">
+        <v>350000214939</v>
+      </c>
+      <c r="C450" t="s">
+        <v>59</v>
+      </c>
+      <c r="D450" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E450" s="5">
+        <v>1</v>
+      </c>
+      <c r="F450" t="s">
+        <v>47</v>
+      </c>
+      <c r="G450" t="s">
+        <v>179</v>
+      </c>
+      <c r="H450" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8">
+      <c r="A451" t="s">
+        <v>178</v>
+      </c>
+      <c r="B451">
+        <v>350000214940</v>
+      </c>
+      <c r="C451" t="s">
+        <v>60</v>
+      </c>
+      <c r="D451" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E451" s="5">
+        <v>1</v>
+      </c>
+      <c r="F451" t="s">
+        <v>47</v>
+      </c>
+      <c r="G451" t="s">
+        <v>179</v>
+      </c>
+      <c r="H451" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8">
+      <c r="A452" t="s">
+        <v>178</v>
+      </c>
+      <c r="B452">
+        <v>350000214941</v>
+      </c>
+      <c r="C452" t="s">
+        <v>61</v>
+      </c>
+      <c r="D452" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E452" s="5">
+        <v>1</v>
+      </c>
+      <c r="F452" t="s">
+        <v>47</v>
+      </c>
+      <c r="G452" t="s">
+        <v>179</v>
+      </c>
+      <c r="H452" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8">
+      <c r="A453" t="s">
+        <v>178</v>
+      </c>
+      <c r="B453">
+        <v>350000298408</v>
+      </c>
+      <c r="C453" t="s">
+        <v>62</v>
+      </c>
+      <c r="D453" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E453" s="5">
+        <v>1</v>
+      </c>
+      <c r="F453" t="s">
+        <v>47</v>
+      </c>
+      <c r="G453" t="s">
+        <v>179</v>
+      </c>
+      <c r="H453" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8">
+      <c r="A454" t="s">
+        <v>178</v>
+      </c>
+      <c r="B454">
+        <v>350000298409</v>
+      </c>
+      <c r="C454" t="s">
+        <v>63</v>
+      </c>
+      <c r="D454" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E454" s="5">
+        <v>1</v>
+      </c>
+      <c r="F454" t="s">
+        <v>47</v>
+      </c>
+      <c r="G454" t="s">
+        <v>179</v>
+      </c>
+      <c r="H454" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8">
+      <c r="A455" t="s">
+        <v>178</v>
+      </c>
+      <c r="B455">
+        <v>350000298410</v>
+      </c>
+      <c r="C455" t="s">
+        <v>64</v>
+      </c>
+      <c r="D455" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E455" s="5">
+        <v>1</v>
+      </c>
+      <c r="F455" t="s">
+        <v>47</v>
+      </c>
+      <c r="G455" t="s">
+        <v>179</v>
+      </c>
+      <c r="H455" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8">
+      <c r="A456" t="s">
+        <v>178</v>
+      </c>
+      <c r="B456">
+        <v>350000212468</v>
+      </c>
+      <c r="C456" t="s">
+        <v>65</v>
+      </c>
+      <c r="D456" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E456" s="5">
+        <v>1</v>
+      </c>
+      <c r="F456" t="s">
+        <v>47</v>
+      </c>
+      <c r="G456" t="s">
+        <v>179</v>
+      </c>
+      <c r="H456" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8">
+      <c r="A457" t="s">
+        <v>178</v>
+      </c>
+      <c r="B457">
+        <v>350000212469</v>
+      </c>
+      <c r="C457" t="s">
+        <v>66</v>
+      </c>
+      <c r="D457" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E457" s="5">
+        <v>1</v>
+      </c>
+      <c r="F457" t="s">
+        <v>47</v>
+      </c>
+      <c r="G457" t="s">
+        <v>179</v>
+      </c>
+      <c r="H457" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8">
+      <c r="A458" t="s">
+        <v>178</v>
+      </c>
+      <c r="B458">
+        <v>350000212470</v>
+      </c>
+      <c r="C458" t="s">
+        <v>67</v>
+      </c>
+      <c r="D458" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E458" s="5">
+        <v>1</v>
+      </c>
+      <c r="F458" t="s">
+        <v>47</v>
+      </c>
+      <c r="G458" t="s">
+        <v>179</v>
+      </c>
+      <c r="H458" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8">
+      <c r="A459" t="s">
+        <v>178</v>
+      </c>
+      <c r="B459">
+        <v>350000212471</v>
+      </c>
+      <c r="C459" t="s">
+        <v>68</v>
+      </c>
+      <c r="D459" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E459" s="5">
+        <v>1</v>
+      </c>
+      <c r="F459" t="s">
+        <v>47</v>
+      </c>
+      <c r="G459" t="s">
+        <v>179</v>
+      </c>
+      <c r="H459" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8">
+      <c r="A460" t="s">
+        <v>178</v>
+      </c>
+      <c r="B460">
+        <v>350000212472</v>
+      </c>
+      <c r="C460" t="s">
+        <v>69</v>
+      </c>
+      <c r="D460" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E460" s="5">
+        <v>1</v>
+      </c>
+      <c r="F460" t="s">
+        <v>47</v>
+      </c>
+      <c r="G460" t="s">
+        <v>179</v>
+      </c>
+      <c r="H460" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8">
+      <c r="A461" t="s">
+        <v>178</v>
+      </c>
+      <c r="B461">
+        <v>350000212473</v>
+      </c>
+      <c r="C461" t="s">
+        <v>70</v>
+      </c>
+      <c r="D461" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E461" s="5">
+        <v>1</v>
+      </c>
+      <c r="F461" t="s">
+        <v>47</v>
+      </c>
+      <c r="G461" t="s">
+        <v>179</v>
+      </c>
+      <c r="H461" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8">
+      <c r="A462" t="s">
+        <v>178</v>
+      </c>
+      <c r="B462">
+        <v>350000358611</v>
+      </c>
+      <c r="C462" t="s">
+        <v>71</v>
+      </c>
+      <c r="D462" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E462" s="5">
+        <v>1</v>
+      </c>
+      <c r="F462" t="s">
+        <v>47</v>
+      </c>
+      <c r="G462" t="s">
+        <v>179</v>
+      </c>
+      <c r="H462" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8">
+      <c r="A463" t="s">
+        <v>178</v>
+      </c>
+      <c r="B463">
+        <v>350000212474</v>
+      </c>
+      <c r="C463" t="s">
+        <v>72</v>
+      </c>
+      <c r="D463" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E463" s="5">
+        <v>1</v>
+      </c>
+      <c r="F463" t="s">
+        <v>47</v>
+      </c>
+      <c r="G463" t="s">
+        <v>179</v>
+      </c>
+      <c r="H463" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8">
+      <c r="A464" t="s">
+        <v>178</v>
+      </c>
+      <c r="B464">
+        <v>350000212475</v>
+      </c>
+      <c r="C464" t="s">
+        <v>73</v>
+      </c>
+      <c r="D464" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E464" s="5">
+        <v>1</v>
+      </c>
+      <c r="F464" t="s">
+        <v>47</v>
+      </c>
+      <c r="G464" t="s">
+        <v>179</v>
+      </c>
+      <c r="H464" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8">
+      <c r="A465" t="s">
+        <v>178</v>
+      </c>
+      <c r="B465">
+        <v>350000212476</v>
+      </c>
+      <c r="C465" t="s">
+        <v>74</v>
+      </c>
+      <c r="D465" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E465" s="5">
+        <v>1</v>
+      </c>
+      <c r="F465" t="s">
+        <v>47</v>
+      </c>
+      <c r="G465" t="s">
+        <v>179</v>
+      </c>
+      <c r="H465" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8">
+      <c r="A466" t="s">
+        <v>178</v>
+      </c>
+      <c r="B466">
+        <v>350000589206</v>
+      </c>
+      <c r="C466" t="s">
+        <v>75</v>
+      </c>
+      <c r="D466" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E466" s="5">
+        <v>1</v>
+      </c>
+      <c r="F466" t="s">
+        <v>47</v>
+      </c>
+      <c r="G466" t="s">
+        <v>179</v>
+      </c>
+      <c r="H466" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8">
+      <c r="A467" t="s">
+        <v>178</v>
+      </c>
+      <c r="B467">
+        <v>350001095409</v>
+      </c>
+      <c r="C467" t="s">
+        <v>132</v>
+      </c>
+      <c r="D467" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E467" s="5">
+        <v>1</v>
+      </c>
+      <c r="F467" t="s">
+        <v>133</v>
+      </c>
+      <c r="G467" t="s">
+        <v>179</v>
+      </c>
+      <c r="H467" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8">
+      <c r="A468" t="s">
+        <v>178</v>
+      </c>
+      <c r="B468">
+        <v>350001095410</v>
+      </c>
+      <c r="C468" t="s">
+        <v>134</v>
+      </c>
+      <c r="D468" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E468" s="5">
+        <v>1</v>
+      </c>
+      <c r="F468" t="s">
+        <v>133</v>
+      </c>
+      <c r="G468" t="s">
+        <v>179</v>
+      </c>
+      <c r="H468" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8">
+      <c r="A469" t="s">
+        <v>178</v>
+      </c>
+      <c r="B469">
+        <v>350001095411</v>
+      </c>
+      <c r="C469" t="s">
+        <v>135</v>
+      </c>
+      <c r="D469" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E469" s="5">
+        <v>1</v>
+      </c>
+      <c r="F469" t="s">
+        <v>133</v>
+      </c>
+      <c r="G469" t="s">
+        <v>179</v>
+      </c>
+      <c r="H469" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8">
+      <c r="A470" t="s">
+        <v>178</v>
+      </c>
+      <c r="B470">
+        <v>350001095412</v>
+      </c>
+      <c r="C470" t="s">
+        <v>136</v>
+      </c>
+      <c r="D470" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E470" s="5">
+        <v>1</v>
+      </c>
+      <c r="F470" t="s">
+        <v>133</v>
+      </c>
+      <c r="G470" t="s">
+        <v>179</v>
+      </c>
+      <c r="H470" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8">
+      <c r="A471" t="s">
+        <v>181</v>
+      </c>
+      <c r="B471">
+        <v>350000499960</v>
+      </c>
+      <c r="C471" t="s">
+        <v>182</v>
+      </c>
+      <c r="D471" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E471" s="5">
+        <v>1</v>
+      </c>
+      <c r="F471" t="s">
+        <v>12</v>
+      </c>
+      <c r="G471" t="s">
+        <v>184</v>
+      </c>
+      <c r="H471" t="s">
+        <v>180</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="37" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
-  <tableParts count="3">
+  <tableParts count="4">
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{3A4CF648-6AED-40f4-86FF-DC5316D8AED3}">
       <x14:slicerList xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-        <x14:slicer r:id="rId6"/>
+        <x14:slicer r:id="rId7"/>
       </x14:slicerList>
     </ext>
   </extLst>

--- a/Info/input/pr_model.xlsx
+++ b/Info/input/pr_model.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AI\Downloads\pr_model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\create-pr-cd\Info\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CA657B-26C0-44D5-BCF0-0A33FD4A272F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95B9EB34-793F-414C-BD74-0772B11E9F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{089DC7BF-D48F-4FC9-B123-3E33291912E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{089DC7BF-D48F-4FC9-B123-3E33291912E1}"/>
   </bookViews>
   <sheets>
     <sheet name="TX Line Item (After 21-Apr 26)" sheetId="1" r:id="rId1"/>
@@ -1755,7 +1755,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2038" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="174">
   <si>
     <t>TX Site Survey</t>
   </si>
@@ -2264,18 +2264,6 @@
     <t>Decom - Relo</t>
   </si>
   <si>
-    <t>Jendela TX Migration</t>
-  </si>
-  <si>
-    <t>Jendela Model</t>
-  </si>
-  <si>
-    <t>Phase</t>
-  </si>
-  <si>
-    <t>Starlink Dismantle (Return/MRCF included) &amp; Migration</t>
-  </si>
-  <si>
     <t>Starlink Dismantling with 1 antenna（Cage Top）</t>
   </si>
   <si>
@@ -2288,29 +2276,7 @@
     <t>As-built Document and ATP already included</t>
   </si>
   <si>
-    <t>MW Dismantle &amp; MRCF</t>
-  </si>
-  <si>
-    <t>MW Installation</t>
-  </si>
-  <si>
-    <t>Migration from Starlink to MW. All xD sites MW installation by ZTE.
-All Q0xxxx or S0xxxx under xC Jendela project, MW to be installed by Huawei.</t>
-  </si>
-  <si>
-    <t>New Installation</t>
-  </si>
-  <si>
-    <t>Fiber Installation</t>
-  </si>
-  <si>
-    <t>Patching work with seperate mobilization</t>
-  </si>
-  <si>
-    <t>Trip</t>
-  </si>
-  <si>
-    <t>Applicable only for Fiber OB unless TX SOW is BBU Patching</t>
+    <t>Starlink Dismanle</t>
   </si>
 </sst>
 </file>
@@ -2456,7 +2422,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2613,6 +2579,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Accent2" xfId="1" builtinId="33"/>
@@ -2621,13 +2602,7 @@
     <cellStyle name="Normal 4 2 2" xfId="4" xr:uid="{AA962A7B-5706-4E11-9052-78D6BBABB481}"/>
     <cellStyle name="常规 116" xfId="3" xr:uid="{D47286A5-C404-4C5F-8EF4-22DB28E47183}"/>
   </cellStyles>
-  <dxfs count="29">
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="27">
     <dxf>
       <font>
         <b val="0"/>
@@ -7545,72 +7520,55 @@
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
   <slicer name="TSS Model 2" xr10:uid="{E33A02A9-D86D-43D1-9039-09161BF92214}" cache="Slicer_TSS_Model111" caption="TSS Model" columnCount="3" rowHeight="144000"/>
-  <slicer name="TI Model 4" xr10:uid="{B4327E0F-182D-45E7-B3D4-958A4D12DC15}" cache="Slicer_TI_Model111" caption="TI Model" columnCount="3" rowHeight="144000"/>
+  <slicer name="TI Model 4" xr10:uid="{B4327E0F-182D-45E7-B3D4-958A4D12DC15}" cache="Slicer_TI_Model111" caption="TI Model" startItem="3" columnCount="3" rowHeight="144000"/>
   <slicer name="Add PR Line Item Model" xr10:uid="{E8947F4E-693E-4B65-9D40-E966E635AD8E}" cache="Slicer_Add_PR_Line_Item_Model" caption="Add PR Line Item Model" rowHeight="234950"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{63BE9434-AFC4-4CB4-9E45-994979C6D48E}" name="Table1169" displayName="Table1169" ref="A7:H36" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{63BE9434-AFC4-4CB4-9E45-994979C6D48E}" name="Table1169" displayName="Table1169" ref="A7:H36" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="A7:H36" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{EC9F81E5-C261-4F84-913A-A8762B1312C9}" name="TSS Model" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{3082E680-9603-4B33-86DF-E70FD7ED2C99}" name="Code" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{A37CA3C1-D74F-485F-BCB7-8DC91B63E87A}" name="Description" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{730F4A6B-FF0F-484F-B58A-7BBE10ACEEFB}" name="Unit" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{8636914A-C6C2-42D8-8FFE-709BAC9BE095}" name="Quantity" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{B76A66B7-2F75-4DA1-87D2-4C4B0C210C18}" name="Rules" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{76A1B753-6759-40D3-985F-AF1ACE921915}" name="Remarks" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{22926371-3F86-47A5-AAC0-948E5FF8B53A}" name="Remarks2" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{EC9F81E5-C261-4F84-913A-A8762B1312C9}" name="TSS Model" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{3082E680-9603-4B33-86DF-E70FD7ED2C99}" name="Code" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{A37CA3C1-D74F-485F-BCB7-8DC91B63E87A}" name="Description" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{730F4A6B-FF0F-484F-B58A-7BBE10ACEEFB}" name="Unit" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{8636914A-C6C2-42D8-8FFE-709BAC9BE095}" name="Quantity" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{B76A66B7-2F75-4DA1-87D2-4C4B0C210C18}" name="Rules" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{76A1B753-6759-40D3-985F-AF1ACE921915}" name="Remarks" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{22926371-3F86-47A5-AAC0-948E5FF8B53A}" name="Remarks2" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E134095E-3A51-4411-AA4E-A7309047E07A}" name="Table12714" displayName="Table12714" ref="A39:G391" totalsRowShown="0" dataDxfId="18">
-  <autoFilter ref="A39:G391" xr:uid="{00000000-0009-0000-0100-00000C000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E134095E-3A51-4411-AA4E-A7309047E07A}" name="Table12714" displayName="Table12714" ref="A39:G393" totalsRowShown="0" dataDxfId="16">
+  <autoFilter ref="A39:G393" xr:uid="{00000000-0009-0000-0100-00000C000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{291468C8-FDC2-4D9B-A444-194B3C6EFF3C}" name="TI Model" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{28F275E1-BFCC-4FF5-9C11-521DB87DE68F}" name="Code" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{6B7D0885-7542-4368-A983-8D5BA7CDD68B}" name="Description" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{6BA7A254-0F46-4E60-9904-80E088865BAC}" name="Unit" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{52575437-1240-4117-849D-D4A2CDB3A6B3}" name="Quantity" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{DD56CF5C-CA1B-42E1-8AD5-8AC6C2E320C1}" name="Rules" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{F0C4064A-B968-42EE-B9E0-EF2B0CBF1C01}" name="Remarks" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{291468C8-FDC2-4D9B-A444-194B3C6EFF3C}" name="TI Model" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{28F275E1-BFCC-4FF5-9C11-521DB87DE68F}" name="Code" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{6B7D0885-7542-4368-A983-8D5BA7CDD68B}" name="Description" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{6BA7A254-0F46-4E60-9904-80E088865BAC}" name="Unit" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{52575437-1240-4117-849D-D4A2CDB3A6B3}" name="Quantity" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{DD56CF5C-CA1B-42E1-8AD5-8AC6C2E320C1}" name="Rules" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{F0C4064A-B968-42EE-B9E0-EF2B0CBF1C01}" name="Remarks" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4CD2CA86-7CEE-4CD0-B47C-C641CA0F181E}" name="Table3" displayName="Table3" ref="A394:G399" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
-  <autoFilter ref="A394:G399" xr:uid="{C921409B-4D8C-4615-9077-350B6EB96C40}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4CD2CA86-7CEE-4CD0-B47C-C641CA0F181E}" name="Table3" displayName="Table3" ref="A396:G401" totalsRowShown="0" headerRowDxfId="8" tableBorderDxfId="7">
+  <autoFilter ref="A396:G401" xr:uid="{C921409B-4D8C-4615-9077-350B6EB96C40}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{31A7B6B0-1197-4056-BDD3-94A5636411E4}" name="Add PR Line Item Model" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{CE2CF9A6-DD5F-4820-AEFE-953E73E863E2}" name="Code" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{2040AADD-8DE9-4F3D-A4BA-363DE5796B06}" name="Description" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{EA415442-6911-4DFE-9C10-B3D349AE27D4}" name="Unit" dataDxfId="5" dataCellStyle="常规 116"/>
-    <tableColumn id="5" xr3:uid="{B4571B37-35C9-408F-A519-45BF32359BAE}" name="Quantity" dataDxfId="4" dataCellStyle="常规 116"/>
-    <tableColumn id="6" xr3:uid="{1B1CCC05-126A-4CDF-A4EE-EFE8F7F19828}" name="Rules" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{CF984CE1-29CF-459A-85E5-C220F87AC4EE}" name="Remarks" dataDxfId="2"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6FE8D8A9-2777-48E3-9B64-F9F2BBA4F91A}" name="Table4" displayName="Table4" ref="A402:H471" totalsRowShown="0">
-  <autoFilter ref="A402:H471" xr:uid="{6FE8D8A9-2777-48E3-9B64-F9F2BBA4F91A}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{3330CE23-3AFE-41D7-B8D6-611EFE913851}" name="Jendela Model"/>
-    <tableColumn id="2" xr3:uid="{3E3B97D8-46C1-4372-A40D-B5F8DBB7A154}" name="Code"/>
-    <tableColumn id="3" xr3:uid="{53E90165-AA05-4EC1-AD62-48E6797BC1F5}" name="Description"/>
-    <tableColumn id="4" xr3:uid="{6F1F1C8E-2E6C-4102-84C3-4B051DC14973}" name="Unit" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{F49F2E89-596F-47D2-985D-392C5220F6CC}" name="Quantity" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{3A7340F3-DE23-4E2D-9566-CE8D16E69ABF}" name="Rules"/>
-    <tableColumn id="7" xr3:uid="{8C07F447-36CD-4AA5-9E86-A150307F366C}" name="Remarks"/>
-    <tableColumn id="8" xr3:uid="{91AC0ADD-EC3E-4BC9-A6A1-4483B2B59D37}" name="Phase"/>
+    <tableColumn id="1" xr3:uid="{31A7B6B0-1197-4056-BDD3-94A5636411E4}" name="Add PR Line Item Model" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{CE2CF9A6-DD5F-4820-AEFE-953E73E863E2}" name="Code" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{2040AADD-8DE9-4F3D-A4BA-363DE5796B06}" name="Description" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{EA415442-6911-4DFE-9C10-B3D349AE27D4}" name="Unit" dataDxfId="3" dataCellStyle="常规 116"/>
+    <tableColumn id="5" xr3:uid="{B4571B37-35C9-408F-A519-45BF32359BAE}" name="Quantity" dataDxfId="2" dataCellStyle="常规 116"/>
+    <tableColumn id="6" xr3:uid="{1B1CCC05-126A-4CDF-A4EE-EFE8F7F19828}" name="Rules" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{CF984CE1-29CF-459A-85E5-C220F87AC4EE}" name="Remarks" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7877,7 +7835,7 @@
   <sheetPr>
     <tabColor theme="5" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:H471"/>
+  <dimension ref="A1:H402"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
@@ -16225,78 +16183,78 @@
       </c>
       <c r="G391" s="21"/>
     </row>
+    <row r="392" spans="1:7">
+      <c r="A392" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B392" s="54">
+        <v>350000597850</v>
+      </c>
+      <c r="C392" s="55" t="s">
+        <v>169</v>
+      </c>
+      <c r="D392" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E392" s="57">
+        <v>1</v>
+      </c>
+      <c r="F392" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="G392" s="21" t="s">
+        <v>170</v>
+      </c>
+    </row>
     <row r="393" spans="1:7">
-      <c r="A393" s="7" t="s">
+      <c r="A393" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B393" s="54">
+        <v>350000597852</v>
+      </c>
+      <c r="C393" s="55" t="s">
+        <v>171</v>
+      </c>
+      <c r="D393" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E393" s="57">
+        <v>1</v>
+      </c>
+      <c r="F393" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="G393" s="21" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7">
+      <c r="A395" s="7" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="394" spans="1:7">
-      <c r="A394" s="43" t="s">
+    <row r="396" spans="1:7">
+      <c r="A396" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="B394" s="44" t="s">
+      <c r="B396" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="C394" s="44" t="s">
+      <c r="C396" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="D394" s="45" t="s">
+      <c r="D396" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E394" s="44" t="s">
+      <c r="E396" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="F394" s="44" t="s">
+      <c r="F396" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="G394" s="44" t="s">
+      <c r="G396" s="44" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="395" spans="1:7">
-      <c r="A395" s="46" t="s">
-        <v>159</v>
-      </c>
-      <c r="B395" s="47">
-        <v>350001000403</v>
-      </c>
-      <c r="C395" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="D395" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E395" s="49">
-        <v>1</v>
-      </c>
-      <c r="F395" s="50" t="s">
-        <v>77</v>
-      </c>
-      <c r="G395" s="51" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="396" spans="1:7">
-      <c r="A396" s="46" t="s">
-        <v>159</v>
-      </c>
-      <c r="B396" s="47">
-        <v>350001042321</v>
-      </c>
-      <c r="C396" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="D396" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E396" s="49">
-        <v>1</v>
-      </c>
-      <c r="F396" s="50" t="s">
-        <v>77</v>
-      </c>
-      <c r="G396" s="51" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="397" spans="1:7">
@@ -16304,10 +16262,10 @@
         <v>159</v>
       </c>
       <c r="B397" s="47">
-        <v>350001042322</v>
+        <v>350001000403</v>
       </c>
       <c r="C397" s="46" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D397" s="48" t="s">
         <v>19</v>
@@ -16318,19 +16276,19 @@
       <c r="F397" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="G397" s="50" t="s">
-        <v>164</v>
+      <c r="G397" s="51" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="398" spans="1:7">
       <c r="A398" s="46" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B398" s="47">
-        <v>350000592793</v>
+        <v>350001042321</v>
       </c>
       <c r="C398" s="46" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D398" s="48" t="s">
         <v>19</v>
@@ -16339,1675 +16297,99 @@
         <v>1</v>
       </c>
       <c r="F398" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="G398" s="50"/>
+        <v>77</v>
+      </c>
+      <c r="G398" s="51" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="399" spans="1:7">
       <c r="A399" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="B399" s="47">
+        <v>350001042322</v>
+      </c>
+      <c r="C399" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="D399" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E399" s="49">
+        <v>1</v>
+      </c>
+      <c r="F399" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="G399" s="50" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7">
+      <c r="A400" s="46" t="s">
         <v>165</v>
       </c>
-      <c r="B399" s="47">
+      <c r="B400" s="47">
+        <v>350000592793</v>
+      </c>
+      <c r="C400" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="D400" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E400" s="49">
+        <v>1</v>
+      </c>
+      <c r="F400" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="G400" s="50"/>
+    </row>
+    <row r="401" spans="1:7">
+      <c r="A401" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="B401" s="47">
         <v>350000592794</v>
       </c>
-      <c r="C399" s="46" t="s">
+      <c r="C401" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="D399" s="48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E399" s="49">
-        <v>1</v>
-      </c>
-      <c r="F399" s="50" t="s">
+      <c r="D401" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="E401" s="49">
+        <v>1</v>
+      </c>
+      <c r="F401" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="G399" s="50"/>
-    </row>
-    <row r="400" spans="1:7">
-      <c r="A400" s="52"/>
-      <c r="B400" s="16"/>
-      <c r="C400" s="9"/>
-      <c r="D400" s="12"/>
-      <c r="E400" s="24"/>
-      <c r="F400" s="14"/>
-      <c r="G400" s="53"/>
-    </row>
-    <row r="401" spans="1:8">
-      <c r="A401" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="402" spans="1:8">
-      <c r="A402" t="s">
-        <v>170</v>
-      </c>
-      <c r="B402" t="s">
-        <v>2</v>
-      </c>
-      <c r="C402" t="s">
-        <v>3</v>
-      </c>
-      <c r="D402" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E402" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F402" t="s">
-        <v>6</v>
-      </c>
-      <c r="G402" t="s">
-        <v>7</v>
-      </c>
-      <c r="H402" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="403" spans="1:8">
-      <c r="A403" t="s">
-        <v>172</v>
-      </c>
-      <c r="B403">
-        <v>350000597850</v>
-      </c>
-      <c r="C403" t="s">
-        <v>173</v>
-      </c>
-      <c r="D403" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E403" s="5">
-        <v>1</v>
-      </c>
-      <c r="F403" t="s">
-        <v>12</v>
-      </c>
-      <c r="G403" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="404" spans="1:8">
-      <c r="A404" t="s">
-        <v>172</v>
-      </c>
-      <c r="B404">
-        <v>350000597852</v>
-      </c>
-      <c r="C404" t="s">
-        <v>175</v>
-      </c>
-      <c r="D404" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E404" s="5">
-        <v>1</v>
-      </c>
-      <c r="F404" t="s">
-        <v>12</v>
-      </c>
-      <c r="G404" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="405" spans="1:8">
-      <c r="A405" t="s">
-        <v>177</v>
-      </c>
-      <c r="B405">
-        <v>350000589232</v>
-      </c>
-      <c r="C405" t="s">
-        <v>81</v>
-      </c>
-      <c r="D405" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E405" s="5">
-        <v>1</v>
-      </c>
-      <c r="F405" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="406" spans="1:8">
-      <c r="A406" t="s">
-        <v>177</v>
-      </c>
-      <c r="B406">
-        <v>350000589241</v>
-      </c>
-      <c r="C406" t="s">
-        <v>84</v>
-      </c>
-      <c r="D406" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E406" s="5">
-        <v>1</v>
-      </c>
-      <c r="F406" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="407" spans="1:8">
-      <c r="A407" t="s">
-        <v>177</v>
-      </c>
-      <c r="B407">
-        <v>350000589242</v>
-      </c>
-      <c r="C407" t="s">
-        <v>85</v>
-      </c>
-      <c r="D407" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E407" s="5">
-        <v>1</v>
-      </c>
-      <c r="F407" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="408" spans="1:8">
-      <c r="A408" t="s">
-        <v>177</v>
-      </c>
-      <c r="B408">
-        <v>350000589243</v>
-      </c>
-      <c r="C408" t="s">
-        <v>86</v>
-      </c>
-      <c r="D408" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E408" s="5">
-        <v>1</v>
-      </c>
-      <c r="F408" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="409" spans="1:8">
-      <c r="A409" t="s">
-        <v>177</v>
-      </c>
-      <c r="B409">
-        <v>350000589244</v>
-      </c>
-      <c r="C409" t="s">
-        <v>87</v>
-      </c>
-      <c r="D409" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E409" s="5">
-        <v>1</v>
-      </c>
-      <c r="F409" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="410" spans="1:8">
-      <c r="A410" t="s">
-        <v>177</v>
-      </c>
-      <c r="B410">
-        <v>350000589253</v>
-      </c>
-      <c r="C410" t="s">
-        <v>88</v>
-      </c>
-      <c r="D410" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E410" s="5">
-        <v>1</v>
-      </c>
-      <c r="F410" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="411" spans="1:8">
-      <c r="A411" t="s">
-        <v>177</v>
-      </c>
-      <c r="B411">
-        <v>350000589254</v>
-      </c>
-      <c r="C411" t="s">
-        <v>89</v>
-      </c>
-      <c r="D411" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E411" s="5">
-        <v>1</v>
-      </c>
-      <c r="F411" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="412" spans="1:8">
-      <c r="A412" t="s">
-        <v>177</v>
-      </c>
-      <c r="B412">
-        <v>350000589255</v>
-      </c>
-      <c r="C412" t="s">
-        <v>90</v>
-      </c>
-      <c r="D412" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E412" s="5">
-        <v>1</v>
-      </c>
-      <c r="F412" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="413" spans="1:8">
-      <c r="A413" t="s">
-        <v>177</v>
-      </c>
-      <c r="B413">
-        <v>350000589256</v>
-      </c>
-      <c r="C413" t="s">
-        <v>91</v>
-      </c>
-      <c r="D413" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E413" s="5">
-        <v>1</v>
-      </c>
-      <c r="F413" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="414" spans="1:8">
-      <c r="A414" t="s">
-        <v>177</v>
-      </c>
-      <c r="B414">
-        <v>350000589263</v>
-      </c>
-      <c r="C414" t="s">
-        <v>92</v>
-      </c>
-      <c r="D414" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E414" s="5">
-        <v>1</v>
-      </c>
-      <c r="F414" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="415" spans="1:8">
-      <c r="A415" t="s">
-        <v>177</v>
-      </c>
-      <c r="B415">
-        <v>350000589264</v>
-      </c>
-      <c r="C415" t="s">
-        <v>93</v>
-      </c>
-      <c r="D415" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E415" s="5">
-        <v>1</v>
-      </c>
-      <c r="F415" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="416" spans="1:8">
-      <c r="A416" t="s">
-        <v>177</v>
-      </c>
-      <c r="B416">
-        <v>350000589265</v>
-      </c>
-      <c r="C416" t="s">
-        <v>94</v>
-      </c>
-      <c r="D416" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E416" s="5">
-        <v>1</v>
-      </c>
-      <c r="F416" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="417" spans="1:6">
-      <c r="A417" t="s">
-        <v>177</v>
-      </c>
-      <c r="B417">
-        <v>350000589272</v>
-      </c>
-      <c r="C417" t="s">
-        <v>95</v>
-      </c>
-      <c r="D417" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E417" s="5">
-        <v>1</v>
-      </c>
-      <c r="F417" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="418" spans="1:6">
-      <c r="A418" t="s">
-        <v>177</v>
-      </c>
-      <c r="B418">
-        <v>350000589273</v>
-      </c>
-      <c r="C418" t="s">
-        <v>96</v>
-      </c>
-      <c r="D418" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E418" s="5">
-        <v>1</v>
-      </c>
-      <c r="F418" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="419" spans="1:6">
-      <c r="A419" t="s">
-        <v>177</v>
-      </c>
-      <c r="B419">
-        <v>350000589274</v>
-      </c>
-      <c r="C419" t="s">
-        <v>97</v>
-      </c>
-      <c r="D419" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E419" s="5">
-        <v>1</v>
-      </c>
-      <c r="F419" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="420" spans="1:6">
-      <c r="A420" t="s">
-        <v>177</v>
-      </c>
-      <c r="B420">
-        <v>350000589281</v>
-      </c>
-      <c r="C420" t="s">
-        <v>98</v>
-      </c>
-      <c r="D420" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E420" s="5">
-        <v>1</v>
-      </c>
-      <c r="F420" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="421" spans="1:6">
-      <c r="A421" t="s">
-        <v>177</v>
-      </c>
-      <c r="B421">
-        <v>350000589282</v>
-      </c>
-      <c r="C421" t="s">
-        <v>99</v>
-      </c>
-      <c r="D421" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E421" s="5">
-        <v>1</v>
-      </c>
-      <c r="F421" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="422" spans="1:6">
-      <c r="A422" t="s">
-        <v>177</v>
-      </c>
-      <c r="B422">
-        <v>350000589283</v>
-      </c>
-      <c r="C422" t="s">
-        <v>100</v>
-      </c>
-      <c r="D422" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E422" s="5">
-        <v>1</v>
-      </c>
-      <c r="F422" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="423" spans="1:6">
-      <c r="A423" t="s">
-        <v>177</v>
-      </c>
-      <c r="B423">
-        <v>350000589306</v>
-      </c>
-      <c r="C423" t="s">
-        <v>101</v>
-      </c>
-      <c r="D423" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E423" s="5">
-        <v>1</v>
-      </c>
-      <c r="F423" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="424" spans="1:6">
-      <c r="A424" t="s">
-        <v>177</v>
-      </c>
-      <c r="B424">
-        <v>350000589307</v>
-      </c>
-      <c r="C424" t="s">
-        <v>102</v>
-      </c>
-      <c r="D424" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E424" s="5">
-        <v>1</v>
-      </c>
-      <c r="F424" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="425" spans="1:6">
-      <c r="A425" t="s">
-        <v>177</v>
-      </c>
-      <c r="B425">
-        <v>350000589308</v>
-      </c>
-      <c r="C425" t="s">
-        <v>103</v>
-      </c>
-      <c r="D425" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E425" s="5">
-        <v>1</v>
-      </c>
-      <c r="F425" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="426" spans="1:6">
-      <c r="A426" t="s">
-        <v>177</v>
-      </c>
-      <c r="B426">
-        <v>350000589309</v>
-      </c>
-      <c r="C426" t="s">
-        <v>104</v>
-      </c>
-      <c r="D426" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E426" s="5">
-        <v>1</v>
-      </c>
-      <c r="F426" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="427" spans="1:6">
-      <c r="A427" t="s">
-        <v>177</v>
-      </c>
-      <c r="B427">
-        <v>350000589310</v>
-      </c>
-      <c r="C427" t="s">
-        <v>105</v>
-      </c>
-      <c r="D427" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E427" s="5">
-        <v>1</v>
-      </c>
-      <c r="F427" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="428" spans="1:6">
-      <c r="A428" t="s">
-        <v>177</v>
-      </c>
-      <c r="B428">
-        <v>350000589311</v>
-      </c>
-      <c r="C428" t="s">
-        <v>106</v>
-      </c>
-      <c r="D428" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E428" s="5">
-        <v>1</v>
-      </c>
-      <c r="F428" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="429" spans="1:6">
-      <c r="A429" t="s">
-        <v>177</v>
-      </c>
-      <c r="B429">
-        <v>350000589312</v>
-      </c>
-      <c r="C429" t="s">
-        <v>107</v>
-      </c>
-      <c r="D429" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E429" s="5">
-        <v>1</v>
-      </c>
-      <c r="F429" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="430" spans="1:6">
-      <c r="A430" t="s">
-        <v>177</v>
-      </c>
-      <c r="B430">
-        <v>350000589313</v>
-      </c>
-      <c r="C430" t="s">
-        <v>108</v>
-      </c>
-      <c r="D430" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E430" s="5">
-        <v>1</v>
-      </c>
-      <c r="F430" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="431" spans="1:6">
-      <c r="A431" t="s">
-        <v>177</v>
-      </c>
-      <c r="B431">
-        <v>350000589314</v>
-      </c>
-      <c r="C431" t="s">
-        <v>109</v>
-      </c>
-      <c r="D431" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E431" s="5">
-        <v>1</v>
-      </c>
-      <c r="F431" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="432" spans="1:6">
-      <c r="A432" t="s">
-        <v>177</v>
-      </c>
-      <c r="B432">
-        <v>350000589315</v>
-      </c>
-      <c r="C432" t="s">
-        <v>110</v>
-      </c>
-      <c r="D432" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E432" s="5">
-        <v>1</v>
-      </c>
-      <c r="F432" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="433" spans="1:8">
-      <c r="A433" t="s">
-        <v>177</v>
-      </c>
-      <c r="B433">
-        <v>350000589316</v>
-      </c>
-      <c r="C433" t="s">
-        <v>111</v>
-      </c>
-      <c r="D433" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E433" s="5">
-        <v>1</v>
-      </c>
-      <c r="F433" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="434" spans="1:8">
-      <c r="A434" t="s">
-        <v>177</v>
-      </c>
-      <c r="B434">
-        <v>350001095413</v>
-      </c>
-      <c r="C434" t="s">
-        <v>153</v>
-      </c>
-      <c r="D434" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E434" s="5">
-        <v>1</v>
-      </c>
-      <c r="F434" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="435" spans="1:8">
-      <c r="A435" t="s">
-        <v>177</v>
-      </c>
-      <c r="B435">
-        <v>350001095414</v>
-      </c>
-      <c r="C435" t="s">
-        <v>154</v>
-      </c>
-      <c r="D435" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E435" s="5">
-        <v>1</v>
-      </c>
-      <c r="F435" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="436" spans="1:8">
-      <c r="A436" t="s">
-        <v>177</v>
-      </c>
-      <c r="B436">
-        <v>350001095415</v>
-      </c>
-      <c r="C436" t="s">
-        <v>155</v>
-      </c>
-      <c r="D436" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E436" s="5">
-        <v>1</v>
-      </c>
-      <c r="F436" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="437" spans="1:8">
-      <c r="A437" t="s">
-        <v>177</v>
-      </c>
-      <c r="B437">
-        <v>350001095416</v>
-      </c>
-      <c r="C437" t="s">
-        <v>156</v>
-      </c>
-      <c r="D437" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E437" s="5">
-        <v>1</v>
-      </c>
-      <c r="F437" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="438" spans="1:8">
-      <c r="A438" t="s">
-        <v>178</v>
-      </c>
-      <c r="B438">
-        <v>350000214911</v>
-      </c>
-      <c r="C438" t="s">
-        <v>46</v>
-      </c>
-      <c r="D438" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E438" s="5">
-        <v>1</v>
-      </c>
-      <c r="F438" t="s">
-        <v>47</v>
-      </c>
-      <c r="G438" t="s">
-        <v>179</v>
-      </c>
-      <c r="H438" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="439" spans="1:8">
-      <c r="A439" t="s">
-        <v>178</v>
-      </c>
-      <c r="B439">
-        <v>350000214920</v>
-      </c>
-      <c r="C439" t="s">
-        <v>48</v>
-      </c>
-      <c r="D439" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E439" s="5">
-        <v>1</v>
-      </c>
-      <c r="F439" t="s">
-        <v>47</v>
-      </c>
-      <c r="G439" t="s">
-        <v>179</v>
-      </c>
-      <c r="H439" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="440" spans="1:8">
-      <c r="A440" t="s">
-        <v>178</v>
-      </c>
-      <c r="B440">
-        <v>350000214921</v>
-      </c>
-      <c r="C440" t="s">
-        <v>49</v>
-      </c>
-      <c r="D440" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E440" s="5">
-        <v>1</v>
-      </c>
-      <c r="F440" t="s">
-        <v>47</v>
-      </c>
-      <c r="G440" t="s">
-        <v>179</v>
-      </c>
-      <c r="H440" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="441" spans="1:8">
-      <c r="A441" t="s">
-        <v>178</v>
-      </c>
-      <c r="B441">
-        <v>350000214922</v>
-      </c>
-      <c r="C441" t="s">
-        <v>50</v>
-      </c>
-      <c r="D441" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E441" s="5">
-        <v>1</v>
-      </c>
-      <c r="F441" t="s">
-        <v>47</v>
-      </c>
-      <c r="G441" t="s">
-        <v>179</v>
-      </c>
-      <c r="H441" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="442" spans="1:8">
-      <c r="A442" t="s">
-        <v>178</v>
-      </c>
-      <c r="B442">
-        <v>350000214923</v>
-      </c>
-      <c r="C442" t="s">
-        <v>51</v>
-      </c>
-      <c r="D442" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E442" s="5">
-        <v>1</v>
-      </c>
-      <c r="F442" t="s">
-        <v>47</v>
-      </c>
-      <c r="G442" t="s">
-        <v>179</v>
-      </c>
-      <c r="H442" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="443" spans="1:8">
-      <c r="A443" t="s">
-        <v>178</v>
-      </c>
-      <c r="B443">
-        <v>350000475874</v>
-      </c>
-      <c r="C443" t="s">
-        <v>52</v>
-      </c>
-      <c r="D443" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E443" s="5">
-        <v>1</v>
-      </c>
-      <c r="F443" t="s">
-        <v>47</v>
-      </c>
-      <c r="G443" t="s">
-        <v>179</v>
-      </c>
-      <c r="H443" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="444" spans="1:8">
-      <c r="A444" t="s">
-        <v>178</v>
-      </c>
-      <c r="B444">
-        <v>350000475875</v>
-      </c>
-      <c r="C444" t="s">
-        <v>53</v>
-      </c>
-      <c r="D444" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E444" s="5">
-        <v>1</v>
-      </c>
-      <c r="F444" t="s">
-        <v>47</v>
-      </c>
-      <c r="G444" t="s">
-        <v>179</v>
-      </c>
-      <c r="H444" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="445" spans="1:8">
-      <c r="A445" t="s">
-        <v>178</v>
-      </c>
-      <c r="B445">
-        <v>350000475876</v>
-      </c>
-      <c r="C445" t="s">
-        <v>54</v>
-      </c>
-      <c r="D445" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E445" s="5">
-        <v>1</v>
-      </c>
-      <c r="F445" t="s">
-        <v>47</v>
-      </c>
-      <c r="G445" t="s">
-        <v>179</v>
-      </c>
-      <c r="H445" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="446" spans="1:8">
-      <c r="A446" t="s">
-        <v>178</v>
-      </c>
-      <c r="B446">
-        <v>350000475877</v>
-      </c>
-      <c r="C446" t="s">
-        <v>55</v>
-      </c>
-      <c r="D446" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E446" s="5">
-        <v>1</v>
-      </c>
-      <c r="F446" t="s">
-        <v>47</v>
-      </c>
-      <c r="G446" t="s">
-        <v>179</v>
-      </c>
-      <c r="H446" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="447" spans="1:8">
-      <c r="A447" t="s">
-        <v>178</v>
-      </c>
-      <c r="B447">
-        <v>350000214930</v>
-      </c>
-      <c r="C447" t="s">
-        <v>56</v>
-      </c>
-      <c r="D447" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E447" s="5">
-        <v>1</v>
-      </c>
-      <c r="F447" t="s">
-        <v>47</v>
-      </c>
-      <c r="G447" t="s">
-        <v>179</v>
-      </c>
-      <c r="H447" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="448" spans="1:8">
-      <c r="A448" t="s">
-        <v>178</v>
-      </c>
-      <c r="B448">
-        <v>350000214931</v>
-      </c>
-      <c r="C448" t="s">
-        <v>57</v>
-      </c>
-      <c r="D448" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E448" s="5">
-        <v>1</v>
-      </c>
-      <c r="F448" t="s">
-        <v>47</v>
-      </c>
-      <c r="G448" t="s">
-        <v>179</v>
-      </c>
-      <c r="H448" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="449" spans="1:8">
-      <c r="A449" t="s">
-        <v>178</v>
-      </c>
-      <c r="B449">
-        <v>350000214932</v>
-      </c>
-      <c r="C449" t="s">
-        <v>58</v>
-      </c>
-      <c r="D449" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E449" s="5">
-        <v>1</v>
-      </c>
-      <c r="F449" t="s">
-        <v>47</v>
-      </c>
-      <c r="G449" t="s">
-        <v>179</v>
-      </c>
-      <c r="H449" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="450" spans="1:8">
-      <c r="A450" t="s">
-        <v>178</v>
-      </c>
-      <c r="B450">
-        <v>350000214939</v>
-      </c>
-      <c r="C450" t="s">
-        <v>59</v>
-      </c>
-      <c r="D450" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E450" s="5">
-        <v>1</v>
-      </c>
-      <c r="F450" t="s">
-        <v>47</v>
-      </c>
-      <c r="G450" t="s">
-        <v>179</v>
-      </c>
-      <c r="H450" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="451" spans="1:8">
-      <c r="A451" t="s">
-        <v>178</v>
-      </c>
-      <c r="B451">
-        <v>350000214940</v>
-      </c>
-      <c r="C451" t="s">
-        <v>60</v>
-      </c>
-      <c r="D451" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E451" s="5">
-        <v>1</v>
-      </c>
-      <c r="F451" t="s">
-        <v>47</v>
-      </c>
-      <c r="G451" t="s">
-        <v>179</v>
-      </c>
-      <c r="H451" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="452" spans="1:8">
-      <c r="A452" t="s">
-        <v>178</v>
-      </c>
-      <c r="B452">
-        <v>350000214941</v>
-      </c>
-      <c r="C452" t="s">
-        <v>61</v>
-      </c>
-      <c r="D452" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E452" s="5">
-        <v>1</v>
-      </c>
-      <c r="F452" t="s">
-        <v>47</v>
-      </c>
-      <c r="G452" t="s">
-        <v>179</v>
-      </c>
-      <c r="H452" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="453" spans="1:8">
-      <c r="A453" t="s">
-        <v>178</v>
-      </c>
-      <c r="B453">
-        <v>350000298408</v>
-      </c>
-      <c r="C453" t="s">
-        <v>62</v>
-      </c>
-      <c r="D453" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E453" s="5">
-        <v>1</v>
-      </c>
-      <c r="F453" t="s">
-        <v>47</v>
-      </c>
-      <c r="G453" t="s">
-        <v>179</v>
-      </c>
-      <c r="H453" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="454" spans="1:8">
-      <c r="A454" t="s">
-        <v>178</v>
-      </c>
-      <c r="B454">
-        <v>350000298409</v>
-      </c>
-      <c r="C454" t="s">
-        <v>63</v>
-      </c>
-      <c r="D454" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E454" s="5">
-        <v>1</v>
-      </c>
-      <c r="F454" t="s">
-        <v>47</v>
-      </c>
-      <c r="G454" t="s">
-        <v>179</v>
-      </c>
-      <c r="H454" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="455" spans="1:8">
-      <c r="A455" t="s">
-        <v>178</v>
-      </c>
-      <c r="B455">
-        <v>350000298410</v>
-      </c>
-      <c r="C455" t="s">
-        <v>64</v>
-      </c>
-      <c r="D455" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E455" s="5">
-        <v>1</v>
-      </c>
-      <c r="F455" t="s">
-        <v>47</v>
-      </c>
-      <c r="G455" t="s">
-        <v>179</v>
-      </c>
-      <c r="H455" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="456" spans="1:8">
-      <c r="A456" t="s">
-        <v>178</v>
-      </c>
-      <c r="B456">
-        <v>350000212468</v>
-      </c>
-      <c r="C456" t="s">
-        <v>65</v>
-      </c>
-      <c r="D456" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E456" s="5">
-        <v>1</v>
-      </c>
-      <c r="F456" t="s">
-        <v>47</v>
-      </c>
-      <c r="G456" t="s">
-        <v>179</v>
-      </c>
-      <c r="H456" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="457" spans="1:8">
-      <c r="A457" t="s">
-        <v>178</v>
-      </c>
-      <c r="B457">
-        <v>350000212469</v>
-      </c>
-      <c r="C457" t="s">
-        <v>66</v>
-      </c>
-      <c r="D457" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E457" s="5">
-        <v>1</v>
-      </c>
-      <c r="F457" t="s">
-        <v>47</v>
-      </c>
-      <c r="G457" t="s">
-        <v>179</v>
-      </c>
-      <c r="H457" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="458" spans="1:8">
-      <c r="A458" t="s">
-        <v>178</v>
-      </c>
-      <c r="B458">
-        <v>350000212470</v>
-      </c>
-      <c r="C458" t="s">
-        <v>67</v>
-      </c>
-      <c r="D458" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E458" s="5">
-        <v>1</v>
-      </c>
-      <c r="F458" t="s">
-        <v>47</v>
-      </c>
-      <c r="G458" t="s">
-        <v>179</v>
-      </c>
-      <c r="H458" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="459" spans="1:8">
-      <c r="A459" t="s">
-        <v>178</v>
-      </c>
-      <c r="B459">
-        <v>350000212471</v>
-      </c>
-      <c r="C459" t="s">
-        <v>68</v>
-      </c>
-      <c r="D459" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E459" s="5">
-        <v>1</v>
-      </c>
-      <c r="F459" t="s">
-        <v>47</v>
-      </c>
-      <c r="G459" t="s">
-        <v>179</v>
-      </c>
-      <c r="H459" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="460" spans="1:8">
-      <c r="A460" t="s">
-        <v>178</v>
-      </c>
-      <c r="B460">
-        <v>350000212472</v>
-      </c>
-      <c r="C460" t="s">
-        <v>69</v>
-      </c>
-      <c r="D460" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E460" s="5">
-        <v>1</v>
-      </c>
-      <c r="F460" t="s">
-        <v>47</v>
-      </c>
-      <c r="G460" t="s">
-        <v>179</v>
-      </c>
-      <c r="H460" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="461" spans="1:8">
-      <c r="A461" t="s">
-        <v>178</v>
-      </c>
-      <c r="B461">
-        <v>350000212473</v>
-      </c>
-      <c r="C461" t="s">
-        <v>70</v>
-      </c>
-      <c r="D461" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E461" s="5">
-        <v>1</v>
-      </c>
-      <c r="F461" t="s">
-        <v>47</v>
-      </c>
-      <c r="G461" t="s">
-        <v>179</v>
-      </c>
-      <c r="H461" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="462" spans="1:8">
-      <c r="A462" t="s">
-        <v>178</v>
-      </c>
-      <c r="B462">
-        <v>350000358611</v>
-      </c>
-      <c r="C462" t="s">
-        <v>71</v>
-      </c>
-      <c r="D462" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E462" s="5">
-        <v>1</v>
-      </c>
-      <c r="F462" t="s">
-        <v>47</v>
-      </c>
-      <c r="G462" t="s">
-        <v>179</v>
-      </c>
-      <c r="H462" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="463" spans="1:8">
-      <c r="A463" t="s">
-        <v>178</v>
-      </c>
-      <c r="B463">
-        <v>350000212474</v>
-      </c>
-      <c r="C463" t="s">
-        <v>72</v>
-      </c>
-      <c r="D463" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E463" s="5">
-        <v>1</v>
-      </c>
-      <c r="F463" t="s">
-        <v>47</v>
-      </c>
-      <c r="G463" t="s">
-        <v>179</v>
-      </c>
-      <c r="H463" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="464" spans="1:8">
-      <c r="A464" t="s">
-        <v>178</v>
-      </c>
-      <c r="B464">
-        <v>350000212475</v>
-      </c>
-      <c r="C464" t="s">
-        <v>73</v>
-      </c>
-      <c r="D464" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E464" s="5">
-        <v>1</v>
-      </c>
-      <c r="F464" t="s">
-        <v>47</v>
-      </c>
-      <c r="G464" t="s">
-        <v>179</v>
-      </c>
-      <c r="H464" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="465" spans="1:8">
-      <c r="A465" t="s">
-        <v>178</v>
-      </c>
-      <c r="B465">
-        <v>350000212476</v>
-      </c>
-      <c r="C465" t="s">
-        <v>74</v>
-      </c>
-      <c r="D465" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E465" s="5">
-        <v>1</v>
-      </c>
-      <c r="F465" t="s">
-        <v>47</v>
-      </c>
-      <c r="G465" t="s">
-        <v>179</v>
-      </c>
-      <c r="H465" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="466" spans="1:8">
-      <c r="A466" t="s">
-        <v>178</v>
-      </c>
-      <c r="B466">
-        <v>350000589206</v>
-      </c>
-      <c r="C466" t="s">
-        <v>75</v>
-      </c>
-      <c r="D466" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E466" s="5">
-        <v>1</v>
-      </c>
-      <c r="F466" t="s">
-        <v>47</v>
-      </c>
-      <c r="G466" t="s">
-        <v>179</v>
-      </c>
-      <c r="H466" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="467" spans="1:8">
-      <c r="A467" t="s">
-        <v>178</v>
-      </c>
-      <c r="B467">
-        <v>350001095409</v>
-      </c>
-      <c r="C467" t="s">
-        <v>132</v>
-      </c>
-      <c r="D467" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E467" s="5">
-        <v>1</v>
-      </c>
-      <c r="F467" t="s">
-        <v>133</v>
-      </c>
-      <c r="G467" t="s">
-        <v>179</v>
-      </c>
-      <c r="H467" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="468" spans="1:8">
-      <c r="A468" t="s">
-        <v>178</v>
-      </c>
-      <c r="B468">
-        <v>350001095410</v>
-      </c>
-      <c r="C468" t="s">
-        <v>134</v>
-      </c>
-      <c r="D468" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E468" s="5">
-        <v>1</v>
-      </c>
-      <c r="F468" t="s">
-        <v>133</v>
-      </c>
-      <c r="G468" t="s">
-        <v>179</v>
-      </c>
-      <c r="H468" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="469" spans="1:8">
-      <c r="A469" t="s">
-        <v>178</v>
-      </c>
-      <c r="B469">
-        <v>350001095411</v>
-      </c>
-      <c r="C469" t="s">
-        <v>135</v>
-      </c>
-      <c r="D469" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E469" s="5">
-        <v>1</v>
-      </c>
-      <c r="F469" t="s">
-        <v>133</v>
-      </c>
-      <c r="G469" t="s">
-        <v>179</v>
-      </c>
-      <c r="H469" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="470" spans="1:8">
-      <c r="A470" t="s">
-        <v>178</v>
-      </c>
-      <c r="B470">
-        <v>350001095412</v>
-      </c>
-      <c r="C470" t="s">
-        <v>136</v>
-      </c>
-      <c r="D470" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E470" s="5">
-        <v>1</v>
-      </c>
-      <c r="F470" t="s">
-        <v>133</v>
-      </c>
-      <c r="G470" t="s">
-        <v>179</v>
-      </c>
-      <c r="H470" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="471" spans="1:8">
-      <c r="A471" t="s">
-        <v>181</v>
-      </c>
-      <c r="B471">
-        <v>350000499960</v>
-      </c>
-      <c r="C471" t="s">
-        <v>182</v>
-      </c>
-      <c r="D471" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E471" s="5">
-        <v>1</v>
-      </c>
-      <c r="F471" t="s">
-        <v>12</v>
-      </c>
-      <c r="G471" t="s">
-        <v>184</v>
-      </c>
-      <c r="H471" t="s">
-        <v>180</v>
-      </c>
+      <c r="G401" s="50"/>
+    </row>
+    <row r="402" spans="1:7">
+      <c r="A402" s="52"/>
+      <c r="B402" s="16"/>
+      <c r="C402" s="9"/>
+      <c r="D402" s="12"/>
+      <c r="E402" s="24"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="53"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="37" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
-  <tableParts count="4">
+  <tableParts count="3">
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
-    <tablePart r:id="rId6"/>
   </tableParts>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{3A4CF648-6AED-40f4-86FF-DC5316D8AED3}">
       <x14:slicerList xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-        <x14:slicer r:id="rId7"/>
+        <x14:slicer r:id="rId6"/>
       </x14:slicerList>
     </ext>
   </extLst>
